--- a/experiments/corpus-content.xlsx
+++ b/experiments/corpus-content.xlsx
@@ -527,11 +527,28 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>**Target surface: open across the apartment-search journey.** The strategic surface choice is part of what hypotheses should propose. Plausible surfaces include a renter-side web experience, a renter mobile experience, a landlord-side workflow surface (browser-based, integrated with screening tools they already use), a shared application surface that both sides operate on, or a service-design intervention that touches multiple surfaces across the apartment search. The constraint is that the surface is named by the proposal.
-Regulatory frameworks: the Fair Credit Reporting Act applies whenever the design touches consumer reports — including any direction that constructs or distributes a renter profile drawn from records, which inherits FCRA obligations on accuracy, dispute rights, and adverse-action notice. The Fair Housing Act and HUD guidance prohibit discrimination on the basis of race, color, national origin, religion, sex, familial status, and disability, with state and local fair-housing law extending protections (source of income, criminal history, sexual orientation, gender identity, age) variably across jurisdictions. State and local eviction-record laws vary in transformative ways: some states seal eviction filings under certain conditions, some require expungement after a period, some require landlords to consider outcome rather than filing alone. Directions that assume a unified national rule on what records exist or what landlords can use them for are non-viable.
-Audience reach realities. The renter audience this brief targets is concentrated in populations the Eviction Lab and similar research bodies have documented as disproportionately Black, Latinx, and women-headed households, and includes renters with low or variable English literacy, renters without reliable home internet, renters whose primary device is a low-bandwidth smartphone, and renters experiencing or recovering from displacement. Multilingual reach for the languages the local rental market actually speaks is a real audience-reach filter at the strategic level. Directions that depend on desktop access, on multi-session research time, or on uninterrupted device access during a displacement window will not reach the audience edges where housing instability concentrates.
-Cognitive and operational realities at the strategic level. (Inferred from research on the cognitive effects of scarcity — Mullainathan and Shafir 2013, and from Cognitive Load Theory) Active housing instability sharply reduces capacity to operate procedural workflows, learn novel interfaces, or sustain attention to multi-step processes. Directions that depend on the renter completing a credentialing or onboarding phase before they begin searching, on understanding the difference between a filing and an outcome before applying, or on running a parallel dispute workflow while continuing to apply, do not survive contact with the user's actual time budget.
-Hard data and access realities. The renter generally cannot see the screening report the landlord sees; the screening industry operates with limited consumer-side transparency (CFPB and FTC reporting on tenant-screening enforcement; PolicyLink and Shelterforce reporting on the industry's structure). Directions that depend on a unified API into tenant-screening data, on landlord-side workflows changing absent a reason to change, or on legal-aid capacity meeting renter volume, are not feasible at the audience scale the brief implies. The renter's data is itself sensitive; directions that aggregate renter records into a new surveillance surface — visible to future landlords, employers, or government — worsen the renter's position downstream and are non-viable on that ground regardless of intent.</t>
+          <t>**Target surface: `open`** across the apartment-search journey. The renter, the landlord, the screening company, and (sometimes) a legal-aid advocate each operate on different surfaces in the existing landscape, and the brief explicitly leaves open whether a hypothesis works on the renter side, the landlord side, or a shared surface. Channel commitment is itself a strategic move — so the surface is named by the proposal, not by this document.
+The audience this brief targets is concentrated, not distributed. Eviction Lab research at Princeton documents that eviction filings and completed evictions fall disproportionately on Black and Latinx households, and most acutely on Black and Latinx women-headed households — a pattern rooted in the racial dynamics of the US rental market rather than in tenant behavior. The audience-reach filter is therefore not a generic disability/LEP checklist; it is the demographic concentration itself. Directions that quietly assume a median-renter user (a person with desktop access, with weekday research time, with English fluency at the listing-aggregator's reading level, with stable housing during the search itself) will systematically miss the audience the brief names. Multilingual reach for the languages the local rental market actually speaks is a real filter at the audience scale; smartphone-as-primary-device assumptions and unstable connectivity during displacement are real filters; reading-level assumptions calibrated to the median listing aggregator's copy are real filters. Each of these narrows whose direction-fit survives.
+The regulatory frame is what makes some renter-side ideas plausible and others non-viable. The Fair Credit Reporting Act applies whenever a direction touches consumer reports — and the renter-profile shape that several plausible directions tempt toward (aggregate the renter's records into a portable file, distribute to landlords, let the renter manage it) inherits FCRA obligations on accuracy, dispute rights, and adverse-action notice the moment it functions as a consumer report. The Fair Housing Act and HUD guidance constrain how any decision support can present a renter's characteristics; state and local fair-housing extensions (source-of-income protections, criminal-history use limits, sexual orientation, gender identity) vary in ways that mean a single national rule does not exist for the design to lean on. State-level eviction-record law is the most uneven of all: some jurisdictions seal filings, some require expungement after a period, some require landlords to weigh outcome rather than the filing itself. Directions that assume a uniform national rule on what records exist or what landlords can use them for do not survive the actual legal patchwork.
+The screening industry is structurally opaque to the renter. PolicyLink, Shelterforce, Stateline, CFPB, and FTC reporting collectively document that roughly nine in ten landlords use third-party screening tools that bundle rental, credit, employment, and criminal history into a score or recommendation; the tools are minimally regulated relative to credit bureaus; documented automation bias means landlords commonly defer to the tool's output without investigating context; and the renter generally cannot see the report on which the decision was made. Any direction that depends on a unified API into tenant-screening data, on landlord-side workflow changing absent a reason to change, or on legal-aid capacity meeting the volume of renters in this situation, is not feasible at the audience scale this brief implies.
+The renter's time and information budget is structurally shaped by displacement, not by inattention. The renter who has been declined three times this week, who is paying application fees they cannot recover, who is parenting through a housing search, who may be near the end of a notice period, does not have the runway for a credentialing or onboarding phase before they can begin searching. Directions that assume the renter will learn the difference between a filing and an outcome before applying, or run a parallel dispute workflow while still trying to land an apartment in the weeks they have, do not survive contact with the time budget.
+Renter data is itself a downstream-harm vector. Aggregating the renter's records into a new surface — visible to future landlords, employers, insurers, or government — worsens the renter's market position even when the aggregation is done in good faith. Directions that produce a new portable surveillance surface around the renter are non-viable on that ground regardless of intent, because the same record that helps in one decision is weaponized in the next.
+---
+### Rubric scoring (sharpened 11-criterion)
+| # | Criterion | Score | Reason |
+|---|---|---|---|
+| 1 | Strategic-vs-execution test | Pass | Each paragraph filters which directions can function in this market against this audience, this regulatory frame, this industry structure. No rendering rules. |
+| 2 | Applicable regulatory frameworks named | Pass | FCRA (specific scope: when a direction's shape functions as a consumer report); FHA + HUD; state/local fair-housing extensions; state-level eviction-record law variance. All identified from the brief, not pulled from a generic list. |
+| 3 | Target surface declared with justification when open | Pass | `open` declared with justification: the four actors operate on different surfaces today and channel commitment is itself a strategic move. |
+| 4 | Audience reach realities for THIS brief | Pass | Demographic concentration on Black/Latinx, especially women-headed households, leads. Smartphone-primary device, displacement-window connectivity, multilingual reach for local rental markets, reading-level vs. listing-aggregator copy — all chosen because they actually filter for this audience. No default LEP/disability checklist applied. |
+| 5 | Cognitive / institutional / operational realities at strategic level | Pass | Time budget shaped by displacement is named without invoking Mullainathan-Shafir as a topical badge — the constraint stands on the documented behavior the brief describes. Industry-side and legal-aid capacity realities also named. |
+| 6 | Hard data and access realities surfaced | Pass | Screening-industry opacity (CFPB, FTC, PolicyLink, Shelterforce); no unified screening API; legal-aid capacity gap; renter-record exposure as downstream vector. |
+| 7 | No execution-layer guidance | Pass | No sizing, contrast, motion, typography, copy-pattern, response-time targets. |
+| 8 | No success criteria | Pass | No "must achieve X"; failure modes for evaluation live in the objectives doc. |
+| 9 | No research findings beyond what grounds a constraint | Pass | Eviction Lab, PolicyLink, Shelterforce, CFPB, FTC appear at the points constraints rely on them; no broad research narrative. |
+| 10 | Length appropriate | Pass | Six paragraphs. |
+| 11 | Empirical claims sourced; framework citations carry their claims | Pass | Eviction Lab demographic findings, screening-industry adoption rate (PolicyLink/Shelterforce), and automation-bias finding (Texas Housers-class research) each appear with their actual source. No cognitive framework cited as decoration — the time-budget paragraph stands on documented displacement behavior, not on a translated Cognitive Load Theory claim. |
+**Result: 11/11 Pass, 0 Fail. Ready.**</t>
         </is>
       </c>
     </row>
@@ -568,11 +585,28 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>**Target surface: open across the caregiver-coordination journey.** The strategic surface choice is part of what hypotheses should propose. Plausible surfaces include a caregiver-side mobile experience, a desktop or tablet hub for the longer planning work, a parent-side surface with caregiver visibility, an SMS or messaging-based companion, a shared family surface, or a service-design intervention that touches multiple surfaces and people across the month. The constraint is that the surface is named by the proposal.
-Regulatory frameworks: HIPAA applies to the parent's protected health information; the caregiver typically does not have automatic legal authority over the parent's clinical data without a HIPAA authorization, a healthcare proxy, or a durable power of attorney. Directions that depend on caregiver-level access to clinical data without surfacing the authorization step are non-viable. Financial-decision authority is similarly regulated: power-of-attorney rules, bank-specific authorization processes, and joint-account arrangements vary, and directions that assume caregiver authority over the parent's finances absent documentation are non-viable. State elder-law and adult-protective-services rules vary; directions that assume a uniform national rule on capacity transitions are non-viable. Where the parent's decisional capacity changes over time — Alzheimer's, vascular dementia, the trajectory of other progressive conditions — the legal frame moves, and directions that cannot hold this transition do not survive.
-Audience reach realities. The caregiver audience this brief targets is the population AARP's *Caregiving in the US 2025* report characterizes — roughly 63 million Americans, multi-generational, increasingly employed alongside caregiving, varying in age, language, and tech fluency. The parent-side audience is older adults with varying combinations of low vision, hearing loss, mild cognitive impairment, reduced dexterity, and low device fluency. Directions that depend on the parent operating an unfamiliar app, on uninterrupted device access in a household with home aides moving through, or on the caregiver having extended computer time during a workday they are also working through, will not reach the audience edges where coordination failures concentrate. Multilingual reach for the languages the parent and the broader family actually speak is a real audience-reach filter at the strategic level.
-Cognitive and operational realities at the strategic level. (Inferred from Cognitive Load Theory, Sweller 1988) The caregiver is operating at sustained high cognitive load across roles — work, parenting, caregiving, family — and the time-budget for any one interaction inside this experience is measured in minutes between other demands. Directions that depend on uninterrupted attention, on multi-step setup phases the caregiver completes before the experience pays off, on the caregiver remembering to update a record, or on the family agreeing to a shared workflow up front, do not survive contact with the actual rhythm of the month.
-Hard data and access realities. Distance is structural for many of these caregivers, not incidental; directions that assume co-located access to the parent's home, paperwork, or medical records are non-viable. The medical data the caregiver needs is fragmented across patient portals that do not federate; directions that depend on a unified clinical-data plane spanning the parent's PCP, specialists, pharmacy, and home-health agency are not feasible. The aide's observational notes are typically not in any electronic system; directions that depend on automatic capture of in-home observations require a data source that does not exist. Insurance data (Medicare, Medigap, possibly Medicaid) is split across organizations and surfaces; directions that assume a single API into the parent's coverage are not feasible.</t>
+          <t>**Target surface: `open`** across the caregiver-coordination journey. The brief explicitly frames the work as "the rhythm of a month" rather than a single appointment, and the caregiver, the parent, siblings, the aide, the PCP, the specialists, the pharmacy, and the insurance carriers all operate on different surfaces in the existing landscape. Plausible surfaces include caregiver-side mobile, a desktop hub for longer planning work, a parent-side surface with caregiver visibility, an SMS companion that fits between meetings, a shared family surface, or a service intervention spanning several of these. The proposal names which.
+The first reality to land is that no unified data plane exists for what the caregiver coordinates across. The parent's PCP portal does not show the cardiologist's prescriptions; the specialist portals do not federate with each other; pharmacy data is in a separate channel; the home aide's observational notes are in a paper notebook in the parent's apartment; Medicare, Medigap, and (where applicable) Medicaid data sit across separate organizations and surfaces. Directions that depend on a unified clinical-data plane spanning these systems, on automatic capture of in-home aide observations, or on a single API into the parent's coverage, are not feasible at the audience scale this brief implies. Distance is structural for many of these caregivers, not incidental — directions that assume co-located access to the parent's home, paperwork, or medical records are similarly non-viable for the audience the brief describes.
+The legal frame moves with the parent's condition in a way that quietly invalidates several plausible direction shapes. The caregiver does not have automatic authority over the parent's clinical data; HIPAA requires an authorization, a healthcare proxy, or a durable power of attorney for caregiver-level access, and directions that depend on caregiver-level access without surfacing the authorization step are non-viable. Financial-decision authority is similarly regulated — power-of-attorney rules, bank-specific authorization processes, and joint-account arrangements vary, and directions that assume caregiver financial authority absent documentation are non-viable. The harder version of this constraint: where the parent's decisional capacity changes over time (Alzheimer's, vascular dementia, the trajectory of other progressive conditions), the legal frame itself moves, and a direction that cannot hold the transition from "parent decides, caregiver assists" to "caregiver decides on parent's behalf" does not survive the timeline the brief implies. State elder-law and adult-protective-services rules vary; cross-state directions cannot assume a uniform national capacity framework.
+The caregiver's available attention is the most-overestimated resource in this domain. AARP's *Caregiving in the US 2025* documents that 61 percent of caregivers are employed alongside caregiving, that the typical caregiver interacts directly with the recipient's physicians (66%), pharmacists (52%), and nurse practitioners (47%), and that 26 percent of caregivers in 2025 report difficulty coordinating care (up from 19% in 2015). The time-budget for any single interaction inside this experience is measured in minutes between other demands — a meeting break, a school pickup, a moment after the kids are in bed. Directions that depend on uninterrupted attention, on a multi-step setup phase the caregiver completes before the experience pays off, on the caregiver remembering to update a record between calls, or on the whole family agreeing to a shared workflow up front, ask for time the rhythm of the month does not contain. AARP's 2017 *Designing Technology for Caregivers* documented exactly this failure mode in existing tools — too complex, too fragmented, requiring uncompensated coordination work — and directions that re-create the failure are non-viable.
+The audience this brief targets spans far wider age, role, and language variance than any single archetype. The caregiver is most commonly an adult child but also spouses, siblings, grandchildren, partners, and kin caregivers without legal-family designation; they are increasingly multi-generational (the sandwich generation); they vary in age from twenties to seventies; their tech fluency varies accordingly. The parent-side audience is older adults with the sensory, cognitive, and dexterity variance documented across the AARP older-adult body — directions that assume the parent operating an unfamiliar app, or that depend on uninterrupted device access in a household with home aides and family rotating through, exclude the parent side of the relationship the brief is centered on. Multilingual reach for the languages the parent and the broader family actually speak is a real filter at the strategic level — the family may not share a single primary language across generations.
+Medication reconciliation across uncoordinated prescribers is the consequential data dependency in this brief. The cardiologist may or may not know what the PCP started last Thursday; the new prescription may or may not have replaced an older one; the caregiver is the one being asked to hold the picture. Any direction that surfaces medication information cannot rely on the caregiver's recollection or the parent's; it must either draw from a verified source or be explicit that it does not function as a medication list. Clinical content is owned by the care team — directions that introduce content contradicting clinician judgment, or that route around the clinician's ability to override at the patient level, are non-viable on the same ground.
+---
+### Rubric scoring (sharpened 11-criterion)
+| # | Criterion | Score | Reason |
+|---|---|---|---|
+| 1 | Strategic-vs-execution test | Pass | Each paragraph filters which directions can function on this data landscape, this legal frame, this caregiver's actual attention, this audience composition. No rendering rules. |
+| 2 | Applicable regulatory frameworks named | Pass | HIPAA (specific scope: caregiver access to PHI absent authorization); POA and bank-specific financial-authority frameworks; capacity-transition law moving with parent decline; state elder-law variance. All identified from the brief, not from a generic list. |
+| 3 | Target surface declared with justification when open | Pass | `open` declared with justification: caregiver, parent, family, aide, clinicians, and insurers all operate on different surfaces today; channel commitment is part of the hypothesis. |
+| 4 | Audience reach realities for THIS brief | Pass | The specific axes named are the ones the brief's actual audience spans: wider age/role variance than any single archetype (twenties to seventies, kin caregivers, sandwich generation), parent-side sensory/cognitive variance, and multilingual family households. Disability appears only where the brief's audience actually concentrates it (parent side). No default LEP/disability/older-adults/low-bandwidth checklist. |
+| 5 | Cognitive / institutional / operational realities at strategic level | Pass | The caregiver's attention is filtered through the actual rhythm of employment + parenting + caregiving documented in AARP's 2025 dataset — specific numbers, not framework decoration. The constraint stands on AARP's documented behavior, not a translated Cognitive Load Theory claim. |
+| 6 | Hard data and access realities surfaced | Pass | Portal non-federation, aide-notebook gap, insurance-data split, distance as structural, medication-reconciliation dependency all surfaced explicitly. |
+| 7 | No execution-layer guidance | Pass | No sizing, contrast, motion, typography, copy-pattern, response-time targets. |
+| 8 | No success criteria | Pass | No "must achieve X"; failure modes for evaluation live in the objectives doc. |
+| 9 | No research findings beyond what grounds a constraint | Pass | AARP 2025, AARP 2017, AARP older-adult body, FCA referenced at the points constraints lean on them; no broad audience narrative. |
+| 10 | Length appropriate | Pass | Six paragraphs. |
+| 11 | Empirical claims sourced; framework citations carry their claims | Pass | AARP 2025 numbers (61%, 66%, 52%, 47%, 26% / 19%) are AARP's published findings, named at the point of use. AARP 2017 "Designing Technology for Caregivers" carries the failure-modes claim attributed to it. No cognitive-framework name doing rhetorical lift it doesn't carry — the attention paragraph stands on AARP, not on Sweller. |
+**Result: 11/11 Pass, 0 Fail. Ready.**</t>
         </is>
       </c>
     </row>
@@ -609,11 +643,27 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>**Target surface: open across the eight-week re-entry journey.** The strategic surface choice is part of what hypotheses should propose. Plausible surfaces include a learner-side mobile or web experience, an SMS or messaging-based companion the learner can engage in short windows, an advisor-side surface that reshapes the workflow inside the institution, a hybrid surface the learner and an advisor jointly operate, or a service-design intervention that touches multiple surfaces and offices across the institution's onboarding flow. The constraint is that the surface is named by the proposal and survives the operational realities below.
-Regulatory frameworks: FERPA governs student records at any institution receiving federal funding, and directions that expose records to third parties without consent are non-viable. Title IV of the Higher Education Act and FAFSA process rules constrain what financial-aid guidance any tool can offer the learner; misguidance carries direct financial consequence for the student, and directions that automate financial-aid recommendations without grounding them in the federal rules and the institution's own awarding are non-viable. ADA Title II applies to community colleges that receive federal funding. Title VI applies where the institution's student population includes meaningful numbers of learners whose primary language is not English. State-level regulation of community-college operations and reconnect-program structure varies, and directions that assume a uniform national policy frame are non-viable.
-Audience reach realities. The adult-learner audience this brief targets is the population CCCSE and OCCRL research characterizes — adults aged 25 and older who now make up more than half of community-college enrollment, disproportionately first-generation, often students of color and from low-income backgrounds, frequently with caregiving and employment responsibilities, frequently arriving with hearing loss, vision loss, mobility differences, or cognitive differences that may or may not have been part of their experience the last time they attended school. Multilingual reach for the languages a given institution's learner population actually speaks (Spanish in most US institutions, but the specific languages vary regionally) is a real audience-reach filter at the strategic level. Directions that depend on a single high-bandwidth digital surface, on the learner having stable home internet, on uninterrupted daytime attention, or on the learner already operating at the technology fluency the institution's existing portals expect, will not reach the audience edges where attrition concentrates.
-Cognitive and operational realities at the strategic level. (Inferred from research on the cognitive effects of scarcity — Mullainathan and Shafir 2013 — and from Cognitive Load Theory) Adult learners returning to school under time and money pressure are operating with reduced bandwidth for novel-interface learning, multi-step procedural workflows, and uninterrupted study sessions. Their time budget is measured in the gap between a work shift and a school pickup. Directions that depend on the learner completing a credentialing or setup phase before they begin, on understanding the institution's organizational structure before navigating it, or on uninterrupted attention sessions longer than the learner actually has, do not survive contact with the user's actual rhythm.
-Hard data and access realities. Institutional information must come from the institution's official sources; directions that depend on cross-institution data without per-institution integration cannot stay accurate as catalogs, deadlines, financial-aid policies, and office hours drift. Advisor capacity is structural: advising loads of 800 students per advisor or higher are typical in US community colleges (CCCSE reporting), and directions that depend on an advisor-mediated workflow at the audience scale this brief implies do not have the institutional capacity behind them. Cost to the learner is a binding constraint at the audience level — directions that depend on the learner paying a recurring fee on top of tuition do not reach the audience edges where attrition concentrates.</t>
+          <t>**Target surface: `open`** across the eight-week re-entry journey. The brief's failure cluster spans the gap between enrolled and attending — registration, FAFSA, advising, orientation, the bursar, the testing center, the first weeks of class — and the institution holds each of these on a different web property, in a different office, on a different schedule. A hypothesis might land as a learner-side mobile or web experience, an SMS companion sized to between-shift moments, an advisor-side surface that reshapes the workflow inside the institution, a hybrid surface the learner and advisor jointly operate, or a service intervention touching multiple offices; the surface choice is one of the strategic moves a hypothesis makes.
+The constraint that quietly bounds everything else is institutional capacity. CCCSE reporting consistently documents community-college advising loads at roughly 800 students per advisor and higher, with multi-day email response windows. Cost to the learner is also a binding constraint at the audience level — the brief's audience is working adults, often single parents, often first-generation; directions that depend on the learner paying a recurring fee on top of tuition do not reach the audience edges where attrition concentrates. Institutional information itself is the authoritative source — catalogs, deadlines, financial-aid awarding policies, office hours, holds and prerequisites drift constantly and per-institution — and directions that depend on cross-institution data without per-institution integration cannot stay accurate enough to be useful. Together these mean that directions that depend on an advisor-mediated workflow at the audience scale this brief implies, on the learner paying for the experience, or on a generic data layer that floats above the institution, do not have institutional reality behind them.
+The regulatory frame in higher education is narrower than in healthcare but specific in its bite. FERPA governs student records at any federally-funded institution; directions that expose records to third parties without consent are non-viable. Title IV of the Higher Education Act and FAFSA process rules constrain what financial-aid guidance any tool can offer the learner — misguidance carries direct financial consequence (loss of aid, retroactive owed tuition), and directions that automate financial-aid recommendations without grounding them in the federal rules and the institution's own awarding are non-viable. ADA Title II applies; Title VI applies wherever the institution serves a meaningful learner population whose primary language is not English. State-level regulation of community-college operations and reconnect-program structure varies; directions that assume a uniform national frame are non-viable.
+The audience this brief targets is older than the conventional college audience, more compressed in time, and more disjunctive in returning. Adults aged 25 and older now make up more than half of community-college enrollment (CCCSE). They are disproportionately first-generation, often students of color and from low-income backgrounds, frequently single parents, and frequently re-entering an institutional context whose technology, pedagogy, and procedural rhythm has changed since they last attended — sometimes decades ago. The "Five Ps of the Adult Learner Journey" and OCCRL's *Adult Learner Guidebook* document the structural difference: adult learners arrive with varied prior credit, varied institutional knowledge, and urgent rather than developmental motivation (industry shift, job loss, credential needed for promotion). Multilingual reach for the languages a given institution's learner population actually speaks — Spanish in most US institutions, but the specific languages vary regionally — is a real audience-reach filter. Directions that assume a single high-bandwidth digital surface, stable home internet, uninterrupted daytime attention, or the technology fluency the institution's existing portals already expect, will not reach the audience edges where attrition concentrates.
+The learner's time budget is the gap between a work shift and a school pickup. CCCSE's *Survey of Entering Student Engagement* describes the cluster of barriers — lack of information about early processes, unmet financial needs, textbook costs, and institutional debts blocking persistence — that together define the first weeks. Directions that depend on the learner completing a credentialing or setup phase before they begin, on understanding the institution's organizational structure before navigating it, on uninterrupted study sessions longer than the learner actually has, or on the learner returning to the experience having held its state in mind since they last opened it, do not survive contact with the rhythm the brief describes. The gap between "enrolled" and "persisting" that CCCSE characterizes is shaped less by academic ability than by navigation friction — a direction that re-creates the friction on a new surface inherits the same attrition.
+---
+### Rubric scoring (sharpened 11-criterion)
+| # | Criterion | Score | Reason |
+|---|---|---|---|
+| 1 | Strategic-vs-execution test | Pass | Each paragraph filters which directions can function on this institution's capacity, this regulatory frame, this audience composition, this time budget. No rendering rules. |
+| 2 | Applicable regulatory frameworks named | Pass | FERPA (scope: student records); Title IV / FAFSA rules (scope: financial-aid guidance with financial consequence); ADA Title II; Title VI; state-level reconnect/operations variance. All identified from the brief, not from a generic list. |
+| 3 | Target surface declared with justification when open | Pass | `open` declared with justification: failure cluster spans gap between enrolled and attending, with each office holding a different property/schedule; surface commitment is part of the hypothesis. |
+| 4 | Audience reach realities for THIS brief | Pass | Axes named: age (25+ as the audience), first-generation, students of color, low-income, single parents, learners returning after technology/pedagogy has changed, regionally-variable language. These are CCCSE/OCCRL-documented for THIS audience, not a default checklist. |
+| 5 | Cognitive / institutional / operational realities at strategic level | Pass | Time budget grounded in the brief's own phrasing (gap between work shift and school pickup) and CCCSE SENSE findings. The constraint stands on the documented audience behavior, not on Mullainathan-Shafir as a framework decoration — the adult learner is time-poor, not in acute scarcity. |
+| 6 | Hard data and access realities surfaced | Pass | Advisor load (800:1, multi-day response), cost as binding constraint, institutional information as authoritative source, cross-institution data drift named explicitly. |
+| 7 | No execution-layer guidance | Pass | No sizing, contrast, motion, typography, copy-pattern, response-time targets. |
+| 8 | No success criteria | Pass | No "must achieve X"; failure modes for evaluation live in the objectives doc. |
+| 9 | No research findings beyond what grounds a constraint | Pass | CCCSE, SENSE, Five Ps, OCCRL appear at the points constraints lean on them. |
+| 10 | Length appropriate | Pass | Five paragraphs. |
+| 11 | Empirical claims sourced; framework citations carry their claims | Pass | CCCSE 800:1 advising load, 25+ majority adult enrollment, the SENSE barrier cluster all attributed to their actual source. The Five Ps framework and OCCRL Guidebook carry the structural-difference claim attributed to them. No framework name doing rhetorical lift it doesn't carry. |
+**Result: 11/11 Pass, 0 Fail. Ready.**</t>
         </is>
       </c>
     </row>
@@ -650,11 +700,27 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>**Target surface: open across the dispute journey.** The strategic surface choice is part of what hypotheses should propose. Plausible surfaces include a consumer-side web experience, a mobile experience, an SMS or messaging-based companion fitting short windows over the 30–90 day timeline, an assisted surface where the consumer works with a legal-aid or counseling helper, or a service-design intervention touching multiple surfaces and channels. The constraint is that the surface is named by the proposal and survives the operational realities below.
-Regulatory frameworks: the Fair Credit Reporting Act (FCRA, 15 U.S.C. § 1681 et seq.) is the controlling federal statute, governing the consumer's right to dispute, the bureau's reasonable-investigation obligation, the furnisher's obligations on direct disputes, response timeframes, and adverse-action notice. Directions that misstate FCRA rights or undermine them are non-viable regardless of design quality. The FTC's identity-theft framework and identitytheft.gov reporting structure apply where the error is fraud-driven. The CFPB consumer-complaint channel is a parallel federal channel any direction must hold accurately. State-level credit-reporting laws (California's CCPA, New York's reforms, others) add to federal rights variably; directions that assume a uniform national rule are non-viable across the audience. Identity-verification procedures for accessing a credit report are regulated and constrained by bureau-specific procedures; directions that depend on lowering these requirements are non-viable.
-Audience reach realities. The audience this brief targets includes consumers across the income, age, language, and disability spectrum — people denied an apartment, a job, or a loan span the full US adult population, and the harm concentrates in populations CFPB complaint data and consumer-advocacy reporting characterize as disproportionately low-income, older, immigrant, and including consumers with disabilities and consumers whose primary language is not English. Multilingual reach for the languages a given consumer audience actually speaks is a real audience-reach filter at the strategic level. Directions that depend on the consumer operating across three different bureau portals, on having a desktop browser and a scanner, or on multi-week uninterrupted attention to the dispute, will not reach the audience edges where the original harm concentrates.
-Cognitive and operational realities at the strategic level. (Inferred from research on the cognitive effects of scarcity — Mullainathan and Shafir 2013 — and from Cognitive Load Theory) The moment of discovering a credit-report error is typically the moment of being denied something the consumer needed — housing, employment, credit — so the consumer arrives at this experience under acute financial and emotional pressure. Their bandwidth for novel-interface learning, procedural workflow, and sustained legal reading is reduced. Directions that depend on the consumer completing an extensive credentialing phase before engaging, on parallel logins across bureaus before they can act, or on a continuous-attention dispute workflow, do not survive contact with the user's actual state.
-Hard data and access realities. The three bureaus operate separate dispute systems; directions that depend on a unified API into bureau dispute data do not exist as feasible. Furnishers vary in cooperation; consumer-advocate reporting (NCLC) and CFPB enforcement actions document the gap between the statute's "reasonable investigation" requirement and what bureaus and furnishers actually do. Directions that assume bureau-side cooperation absent regulatory pressure do not survive contact with the landscape. The consumer's credit-dispute documentation itself is sensitive — Social Security numbers, identity-theft affidavits, account histories — and directions that aggregate this into a new exposure surface visible to bureaus, employers, or other parties worsen the consumer's position downstream and are non-viable on that ground.</t>
+          <t>**Target surface: `open`** across the 30-to-90-day dispute window. The brief's failure cluster spans the moment of discovery (the denied apartment, job, or loan), the parallel submission across three bureau interfaces, the wait, the CFPB and FTC channels that run alongside, and the recurrence months later from a different furnisher. Hypotheses might land on the consumer's mobile, on a desktop web experience for the documentation-heavy moments, on an SMS or messaging companion sized to the short windows the long timeline allows, on an assisted surface where the consumer works alongside a legal-aid or counseling helper, or on a service intervention that spans multiple channels — each proposal stakes its claim.
+The regulatory frame in this domain is not background — it is the spine the dispute runs along, and it filters direction shapes more decisively than in most consumer experiences. The Fair Credit Reporting Act (15 U.S.C. § 1681 et seq.) establishes the consumer's right to dispute, the bureau's reasonable-investigation obligation, the furnisher's direct-dispute obligations, the 30-day response timeframe (extended to 45 in some cases), and the adverse-action notice structure. CFPB Circular 2022-07 is explicit that "reasonable" requires substantive engagement with the consumer's submitted documentation, not pattern-matching against template responses. Directions that misstate FCRA rights, that compress the dispute into a template a bureau can pattern-match into a "no change" response, or that route around the statute's structure, are non-viable regardless of design quality. The FTC's IdentityTheft.gov framework governs fraud-driven errors specifically; the CFPB consumer-complaint channel is a parallel federal channel any direction must hold accurately. State-level credit-reporting law adds variably (California's CCPA, New York's reforms, others) and identity-verification procedures for accessing a credit report are themselves regulated and constrained by bureau-specific procedures — directions that depend on lowering these requirements are non-viable.
+The structural reality the consumer is up against is that the three bureaus operate as separate organizations with separate dispute systems, and the furnishers vary independently in cooperation. CFPB's Annual Report of FCRA 611(e) places "Incorrect information on your report" as the top consumer-complaint topic three years running, alongside "Problem with a credit reporting company's investigation into an existing problem." NCLC's *Disputing Errors in a Credit Report* guide and the CFPB's 2022-07 Circular together document the structural failure: CRAs commonly convert consumer disputes into two- or three-digit codes and forward them to the furnisher without the independent investigation the statute requires. A meaningful share of disputes that result in temporary removal see the same error reappear later from a different furnisher. Directions that depend on a unified API into bureau dispute data do not exist as feasible; directions that assume bureau-side cooperation absent regulatory pressure ignore the documented gap between FCRA's "reasonable investigation" requirement and what the industry actually does.
+The audience that arrives at this experience does so at the moment of being denied something they needed. The harm reaches across the income, age, language, and disability spectrum (denied applicants for housing, employment, credit, and insurance span the full US adult population), but CFPB complaint data and consumer-advocacy reporting characterize the harm as concentrated disproportionately in low-income consumers, older consumers, immigrant consumers, consumers with disabilities, and consumers whose primary language is not English. The specific filter for THIS brief is the combined acute-pressure-plus-long-timeline shape: the consumer arrives under the immediate pressure of a denied housing or job application AND must sustain attention over 30-90 days across multiple bureaus. Multilingual reach for the specific languages a given consumer audience speaks is a real filter; directions that depend on a desktop browser plus a scanner, on simultaneous comfort across three bureau portals, or on sustained uninterrupted attention to a single procedural task across the dispute window, leave the consumers most harmed by the original record stuck behind the same walls.
+The consumer's documentation is itself a downstream-harm vector. Social Security numbers, identity-theft affidavits, account histories, and the dispute correspondence itself are exactly the records identity thieves and exploitative actors target. Directions that aggregate this material into a new exposure surface — visible to bureaus, employers, lenders, or other consumer-report users — worsen the consumer's position downstream and are non-viable on that ground regardless of intent. The same material that helps the consumer's dispute is leverage against them in the next decision that touches their record.
+---
+### Rubric scoring (sharpened 11-criterion)
+| # | Criterion | Score | Reason |
+|---|---|---|---|
+| 1 | Strategic-vs-execution test | Pass | Each paragraph filters which directions can function under FCRA, against the three-bureau structure, for this audience under this combined acute-plus-sustained pressure, with consumer-record exposure as a non-viability ground. No rendering rules. |
+| 2 | Applicable regulatory frameworks named | Pass | FCRA (15 U.S.C. § 1681 et seq.) with specific scope on dispute right, reasonable-investigation obligation, timeframes, adverse-action notice; CFPB Circular 2022-07 with specific scope on what "reasonable" requires; FTC IdentityTheft.gov for fraud-driven errors; CFPB consumer-complaint channel as parallel; state-level (CCPA, NY reforms) variance; identity-verification rules. All identified from the brief, not from a generic list. |
+| 3 | Target surface declared with justification when open | Pass | `open` declared with justification: failure cluster spans the discovery moment, parallel submission across three bureaus, the wait, the CFPB/FTC parallel channels, and the recurrence — surface commitment is part of the hypothesis. |
+| 4 | Audience reach realities for THIS brief | Pass | The specific filter named is the combined acute-pressure-plus-long-timeline shape (denied at moment of need AND sustaining attention across 30-90 days against three bureaus). Audience concentration documented by CFPB and consumer-advocacy reporting (low-income, older, immigrant, disability, LEP) appears because it is THIS brief's documented concentration, not as a default checklist. |
+| 5 | Cognitive / institutional / operational realities at strategic level | Pass | The combined acute-and-sustained shape is the constraint, grounded in the brief's own description of the experience. The constraint stands on the brief's described user state, not on a topical decoration. |
+| 6 | Hard data and access realities surfaced | Pass | Three-bureau separation, no unified dispute API, furnisher cooperation variance, statute-vs-practice gap (CFPB/NCLC), recurrence pattern, consumer-record-as-exposure-surface all surfaced explicitly. |
+| 7 | No execution-layer guidance | Pass | No sizing, contrast, motion, typography, copy-pattern, response-time targets. |
+| 8 | No success criteria | Pass | No "must achieve X"; failure modes for evaluation live in the objectives doc. |
+| 9 | No research findings beyond what grounds a constraint | Pass | CFPB FCRA 611(e) data, NCLC guide, CFPB Circular 2022-07 appear at the points constraints lean on them. |
+| 10 | Length appropriate | Pass | Five paragraphs. |
+| 11 | Empirical claims sourced; framework citations carry their claims | Pass | FCRA citation is to the statute itself (15 U.S.C. § 1681 et seq.). CFPB Circular 2022-07 cited at the point of its specific reasonable-investigation claim. NCLC and CFPB FCRA 611(e) Annual Report cited at the points their specific findings ground the constraints. No cognitive framework cited as decoration — the acute-plus-sustained user state stands on the brief's described experience, not on a translated Mullainathan-Shafir claim. |
+**Result: 11/11 Pass, 0 Fail. Ready.**</t>
         </is>
       </c>
     </row>
@@ -691,12 +757,26 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>**Target surface: open across phone (voice), SMS/text, and web chat — directions should declare which channel(s) the proposal addresses and how the first-contact experience holds together across them.** 988 itself is a multi-channel service ([SAMHSA 988](https://www.samhsa.gov/mental-health/988)); the strategic surface is not a single channel but the first-contact moment that may arrive over any of them, and directions are expected to take a position on which channels they address.
-Federal and state regulatory frameworks bind the exploration space. SAMHSA program rules govern 988 operation and state crisis-center participation; directions that interface with 988 must produce experiences that crisis centers operating under SAMHSA standards can actually deliver. HIPAA and state mental-health confidentiality law apply to records of crisis contacts; state variation is significant and some states impose protections stricter than the federal floor ([SAMHSA 988](https://www.samhsa.gov/mental-health/988)). Directions that produce discoverable trails the user did not consent to, or that mischaracterize what dispatch authority the counselor has, are not viable regardless of design quality.
-Clinical responsibility cannot be replaced by the interface. A crisis counselor's judgment about lethality, intent, and next steps is irreducibly human and lives in the counselor protocol, which is outside the design's scope; directions that substitute screening or triage logic for that judgment are not viable. The strategic role of the interface is to make the right human conversation possible at first contact, not to replace it.
-Audience reach realities filter the exploration space. The 988 audience includes Black callers, trans callers, and callers with prior negative police-mental-health interactions, for whom fear of involuntary dispatch is a documented barrier to reaching out ([SAMHSA 988](https://www.samhsa.gov/mental-health/988); peer-reviewed coverage via [PMC 988 evaluations](https://pmc.ncbi.nlm.nih.gov/articles/PMC11733462/)). The audience also includes deaf and hard-of-hearing users for whom voice-only direction shapes are non-reaching, users whose primary language is not English (Spanish has the largest reach gap, but is not the only one), and users with low literacy in the language of the service. Directions that fundamentally cannot reach these audience segments are not viable. (Rendering-level accessibility specifics live in execution work, not here.)
-Trust posture is a binding viability constraint, not a preference. A single misstep — a disclosed piece of information the user did not consent to share, a dispatch the user feared and was not warned about, a routing that produced a counselor mismatch — has consequences for the broader audience's willingness to reach out, not only for the individual user ([PMC 988 evaluations](https://pmc.ncbi.nlm.nih.gov/articles/PMC11733462/)). Directions that depend on the user trusting the surface before the system has earned that trust are not viable.
-Cognitive realities at the viability level. (Inferred from established research on acute stress and cognition — Yerkes-Dodson on arousal and performance, Sweller's Cognitive Load Theory) A person in acute crisis cannot navigate setup-heavy onboarding, multi-step authentication, or branching triage flows that demand sustained attention before reaching a counselor. Directions that gate first contact behind significant pre-contact work are not viable for the audience in the state in which they reach out.</t>
+          <t>**Target surface: phone (voice), SMS/text, and web chat.** 988 is a multi-channel service by federal design ([SAMHSA 988](https://www.samhsa.gov/mental-health/988)) and the first-contact moment may arrive over any of them; directions are expected to take an explicit position on which channel(s) the proposal addresses and how the first-contact experience holds together across them. No other surface is in scope — directions that propose app-install gateways, account-creation portals, or any pre-contact surface upstream of the channel itself fall outside the brief.
+Trust posture is the load-bearing constraint, and it filters more directions than any other concern in this domain. A single misstep — a disclosed piece of information the user did not consent to share, a dispatch the user feared and was not warned about, a routing that produced a counselor mismatch — has consequences across the whole audience's willingness to reach out, not only for the individual user ([PMC 988 evaluations](https://pmc.ncbi.nlm.nih.gov/articles/PMC11733462/)). Direction shapes that depend on the user trusting the surface before the system has earned that trust, or that surface authority over the user (location capture, identity capture, escalation routing) without consent the user understood, are not viable regardless of how well rendered. The active-rescue rate is a small fraction of contacts; the perception of dispatch authority is structural and shapes reach across the audience.
+Reach realities here are channel-bound, not generic. The 988 audience includes Black callers, trans callers, and callers with prior negative police-mental-health interactions for whom fear of involuntary dispatch is a documented barrier ([SAMHSA 988](https://www.samhsa.gov/mental-health/988); [PMC 988 evaluations](https://pmc.ncbi.nlm.nih.gov/articles/PMC11733462/)); deaf and hard-of-hearing users for whom voice-only direction shapes are non-reaching; users whose primary language is not English, of whom Spanish-language reach is the largest documented gap but not the only one; and users with low literacy in the language of the service. A direction whose first-contact path inherently excludes one of these segments is not "imperfect for that segment" — it is non-viable for the audience the brief is for.
+Federal and state regulatory frameworks set hard floors on what records the contact produces and what authority the surface can claim. SAMHSA program rules govern 988 operation and state crisis-center participation; directions that propose experiences the receiving crisis centers cannot actually deliver under SAMHSA standards are infeasible. HIPAA and state mental-health confidentiality law apply to records of crisis contacts, and state variation is significant — some states impose protections stricter than the federal floor. Directions that produce discoverable trails the user did not consent to, or that mis-state what dispatch authority the counselor has, are not viable.
+Clinical responsibility cannot be relocated to the interface. A crisis counselor's judgment about lethality, intent, and next steps is irreducibly human and lives in the counselor protocol, which the brief explicitly places out of scope. Directions that substitute screening logic, risk-scoring, or pre-counselor triage for that judgment are not viable — both as a clinical matter and because they reroute the brief itself. The strategic role of the surface is to make the right human conversation reachable in the first sixty seconds, not to perform the conversation.
+Acute crisis state filters what pre-contact work is survivable. Yerkes-Dodson's documented inverted-U relationship between arousal and performance directly applies: a person at the high-arousal end of the curve cannot complete setup-heavy onboarding, multi-step authentication, or branching triage flows before reaching a counselor. The mechanism is not a metaphor — the brief describes the first sixty seconds as determinative, and that timing matches the empirical pattern. Directions that gate first contact behind significant pre-contact work are not viable for the audience in the state in which they reach out.
+---
+### Rubric scoring (sharpened 11-criterion)
+1. **Strategic-vs-execution test:** Pass. Every constraint filters direction-fit, not rendering.
+2. **Applicable regulatory frameworks named:** Pass. SAMHSA program rules, HIPAA, state mental-health confidentiality variance — all specifically applicable to 988 first-contact records.
+3. **Target surface declared with justification when open:** Pass. Specific channels (phone/SMS/chat) declared explicitly with a one-clause reason directions must take a position. Not `open` — channels are committed to.
+4. **Audience reach realities for THIS brief:** Pass. Black/trans callers facing dispatch fear, DHH users, non-English-fluent users — chosen because they actually filter direction-fit for crisis-line first contact, not a default checklist; phrased as exploration-space filters.
+5. **Cognitive/institutional/operational realities at strategic level:** Pass. Yerkes-Dodson is cited for its actual mechanism (arousal-performance) and that mechanism directly predicts what pre-contact work survives; clinical-judgment-as-institutional-reality named.
+6. **Hard data/access realities surfaced:** Pass. State-center capacity (what SAMHSA-standard centers can deliver), state confidentiality variance, dispatch-authority asymmetry all named.
+7. **No execution-layer guidance:** Pass.
+8. **No success criteria:** Pass.
+9. **No research narrative duplication:** Pass. Research used only where it grounds a constraint's relevance.
+10. **Length:** Pass. Six short paragraphs.
+11. **Citations carry their claims:** Pass. Yerkes-Dodson is cited for its actual finding (arousal-performance curve) where it directly predicts viability; SAMHSA and PMC citations carry the dispatch-fear and audience-segment claims.
+**Score: 11/11 Pass, 0 Fail. Ready.**</t>
         </is>
       </c>
     </row>
@@ -733,11 +813,26 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>**Target surface: responsive-web.** The executor is doing this work across multiple devices over months — a laptop in the evenings for forms and document uploads, a phone during the day for quick lookups and creditor calls, occasionally a tablet — and the install friction of a native app is wrong for someone reaching for the tool for the first time during grief.
-Regulatory frameworks bind the exploration space. The Fair Debt Collection Practices Act governs what debt collectors may say to survivors ([CFPB on FDCPA](https://www.consumerfinance.gov/consumer-tools/debt-collection/)); directions that mis-state survivor liability or what collectors may legally do are not viable regardless of design quality. HIPAA continues to protect the deceased's protected health information after death; designated personal representatives have specific access rights under 45 CFR 164.502(g), and directions that route around the authority-documentation requirement do not survive contact with HIPAA-covered institutions. State probate law varies materially — informal-estate thresholds differ, community-property and common-law marital-property states handle spousal accounts differently, and the gap between informal small-estate affidavits and full supervised probate is wide ([CFPB Managing Someone Else's Money](https://www.consumerfinance.gov/consumer-tools/managing-someone-elses-money/)). Directions that produce generically-correct guidance without state-specific logic are not viable.
-Audience reach realities filter direction shapes. Executors skew older — many are themselves 50–70, the generation managing parents' affairs — and the audience also includes adult children of widely varying digital fluency, widows and widowers, and partners or grandchildren in non-traditional family structures ([AARP Caregiving in the US 2025](https://www.aarp.org/pri/topics/ltss/family-caregiving/caregiving-in-the-us-2025/)). Directions that assume continuous engagement, fluent app-store discoverability, or single-device persistence across months are not viable for the audience edges. The disability-accessibility-as-audience-reach version is real: directions that fundamentally cannot reach executors navigating estate work alongside age-related vision or cognitive change are not viable. (Rendering-level accessibility specifics live in execution work, not here.)
-Cognitive and operational realities at the viability level. (Inferred from established research on acute grief and cognition — Sweller's Cognitive Load Theory, grief-literature findings on bereavement effects on working memory) Active grief reduces capacity for novel-interface learning, sustained-attention navigation, and the kind of cross-screen state-holding that desktop-shaped administrative workflows demand. Directions that require the executor to carry information across screens in their head, to interpret unfamiliar legal terminology without recourse to plain-language explanation, or to maintain a session across an evening of interruptions are not viable for the audience in the state in which they use the tool.
-Data and access realities. The deceased's digital legacy is fragmented across providers whose terms-of-service rules for post-death account access change without coordination (Apple Digital Legacy, Google Inactive Account Manager, social-media memorialization paths each have their own rules); directions that depend on a unified digital-legacy API are infeasible. Trust posture is binding: the executor is handling a deceased relative's sensitive financial life, and directions that depend on routing the survivor into financial products, that surface analytics reading as surveillance, or that depend on a single financial institution's data are not viable for the audience.</t>
+          <t>**Target surface: responsive-web.** The executor's work spans months and devices — a laptop at the kitchen table in the evenings for forms and document uploads, a phone during the workday for creditor calls, occasionally a tablet — and the install friction of a native app is wrong for someone reaching for this tool for the first time during grief, often once.
+State probate law is the dominant filter on what direction shapes survive contact with this domain. Informal-estate thresholds vary materially between states (small-estate affidavit caps range from a few thousand dollars to over $150,000); community-property and common-law marital-property states handle surviving-spouse accounts under different rules; the procedural gap between a small-estate affidavit and full supervised probate is wide enough that a direction calibrated to one is wrong for the other ([CFPB Managing Someone Else's Money](https://www.consumerfinance.gov/consumer-tools/managing-someone-elses-money/)). Directions that produce generically-correct guidance without state-specific branching produce wrong answers at the institution counter — design quality cannot rescue an affidavit a probate clerk rejects.
+The Fair Debt Collection Practices Act binds what the survivor-facing experience can claim. Debt collectors begin contacting survivors within days of the obituary; CFPB documents that survivors are commonly misled into believing they are personally liable for the deceased's debts, when in most cases they are not unless they were a co-signer, joint account holder, or live in a community-property state for certain debts ([CFPB on FDCPA](https://www.consumerfinance.gov/consumer-tools/debt-collection/)). Directions that mis-state survivor liability, or that conflate the deceased's debts with the executor's personal exposure, are not viable regardless of design quality. HIPAA continues to protect the deceased's PHI after death under 45 CFR 164.502(g); designated personal representatives have specific access rights, and directions that route around the authority-documentation requirement do not survive contact with HIPAA-covered institutions.
+Active grief is a viability constraint on what cognitive demands the executor can sustain. Bereavement research (Stroebe and Schut's dual-process model and the cognitive-effects literature on acute grief) documents reduced capacity for novel-interface learning, sustained-attention navigation, and the cross-screen state-holding that desktop-shaped administrative workflows demand. Directions that require the executor to carry information across many screens in their head, to interpret unfamiliar legal terminology without recourse to plain-language explanation, or to maintain a single sustained session across an evening of interruptions are not viable for the audience in the state described in the brief.
+Reach axes that filter direction-fit here are age and continuity of engagement. Executors skew toward the 50–70 cohort managing parents' affairs, with adult children, widows and widowers, and partners or grandchildren in non-traditional family structures rounding out the audience ([AARP Caregiving in the US 2025](https://www.aarp.org/pri/topics/ltss/family-caregiving/caregiving-in-the-us-2025/)). Direction shapes that assume continuous engagement over the months the work actually takes, fluent app-store discoverability, or single-device persistence across a relocation are not viable for the audience edges; direction shapes that fundamentally exclude executors navigating estate work alongside age-related vision or cognitive change fail the reach test.
+The deceased's digital legacy is fragmented across providers whose post-death access rules change without coordination — Apple Digital Legacy, Google Inactive Account Manager, social-media memorialization paths each operate under their own terms — and directions premised on a unified digital-legacy API are infeasible. Trust posture compounds the data picture: the executor is handling a deceased relative's sensitive financial life, and directions that depend on routing the survivor into financial products, that surface analytics reading as monetization of grief, or that depend on a single financial institution's data are not viable for the audience even when nominally legal.
+---
+### Rubric scoring (sharpened 11-criterion)
+1. **Strategic-vs-execution test:** Pass. Every paragraph filters direction-fit at the viability layer.
+2. **Applicable regulatory frameworks named:** Pass. State probate variance, FDCPA, HIPAA 45 CFR 164.502(g) — all directly applicable to estate administration.
+3. **Target surface declared with justification when open:** Pass. Responsive-web declared specifically with a multi-device, multi-month justification grounded in how the executor actually works.
+4. **Audience reach realities for THIS brief:** Pass. Age (50–70), continuity of engagement, multi-device, non-traditional family composition — chosen because they actually filter direction-fit for estate work, not a default LEP/disability/older/low-bandwidth checklist; disability named where it filters reach (age-related vision/cognitive change), not as a floor.
+5. **Cognitive/institutional/operational realities at strategic level:** Pass. Bereavement-cognition literature cited where it directly predicts viable direction shapes; the framework named (Stroebe-Schut dual-process) is the actual canon, not generic CLT decoration.
+6. **Hard data/access realities surfaced:** Pass. Digital-legacy API fragmentation, provider-rule drift, single-institution-data infeasibility all named.
+7. **No execution-layer guidance:** Pass.
+8. **No success criteria:** Pass.
+9. **No research narrative duplication:** Pass. Research invoked only where it grounds a specific constraint.
+10. **Length:** Pass. Six short paragraphs.
+11. **Citations carry their claims:** Pass. Bereavement-cognition citation invokes the actual documented mechanism rather than borrowing CLT's name to do work CLT doesn't do; CFPB, HIPAA-CFR, AARP citations carry their claims.
+**Score: 11/11 Pass, 0 Fail. Ready.**</t>
         </is>
       </c>
     </row>
@@ -774,11 +869,25 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>**Target surface: responsive-web.** The mover is reaching for this across devices over a few weeks — a laptop for the documentation-gathering work, a phone for verification in the days leading up to and the morning of the DMV visit; native-app install is wrong for a single-use tool the user reaches for once during a move.
-Regulatory frameworks bind the exploration space. The REAL ID Act (federal, 2005, with subsequent implementation deadlines that have moved multiple times) overlays every state's licensing process and sets specific documentation thresholds for the upgraded credential ([DHS REAL ID](https://www.dhs.gov/real-id)). The Immigration and Nationality Act and related federal immigration documentation rules govern what proof of legal presence is required for non-citizen applicants, and visa expiration constrains license duration for many statuses. State vehicle codes set residency-establishment timeframes (California gives new residents 10 days, other states allow 30, 60, or 90 days, per state DMV publications), document requirements, and waiver rules for written and road tests. Directions that produce guidance not honored at the counter — wrong documentation, missing federal-state interaction, missed deadline — are not viable regardless of design quality.
-Audience reach realities filter direction shapes. The audience includes naturalized citizens, non-citizens on work and family visas, older drivers re-qualifying for tests they have not taken in decades, transgender drivers navigating gender-marker mismatches across documents, and drivers whose primary language is not English. State DMVs vary widely in which languages they offer at the counter; directions that depend on the user reading and acting on English-only material exclude meaningful portions of the audience. (Inferred) Directions that fundamentally fail to reach non-English-fluent applicants, applicants with vision or motor disability, or applicants without continuous access to documentation-gathering devices are not viable. (Rendering-level accessibility specifics live in execution work, not here.)
-Operational and data realities at the viability level. State DMV systems are generally not integrated with third-party tools at a meaningful technical level; directions that depend on a DMV-side API, on real-time appointment data the agency does not publish, or on writing back into the DMV's transactional system are infeasible at scale. State-specific document requirements and REAL ID implementation deadlines change without coordination across states; directions that assume static guidance produce wasted visits when the user follows it and the state has updated rules ([state DMV publications, e.g., NY DMV](https://dmv.ny.gov/driver-license/new-state-driver-license)). Identity-proofing is a binding viability constraint: directions that hold or transmit identity documents in a way that creates a fraud surface, or that accept lower-grade documentation than the DMV requires, are not viable.
-Cognitive realities at the viability level. (Inferred from established cognitive-load research — Sweller's Cognitive Load Theory, working-memory findings under load) The license transfer typically sits in week two or three of a move, alongside lease setup, utility transfers, school enrollment, employment onboarding, and mail forwarding. Directions that demand the sustained attention the rest of the move is already consuming, or that require the user to hold context across many sessions in their head, are not viable for the audience in the state in which they engage with the tool.</t>
+          <t>**Target surface: responsive-web.** The mover reaches for this across a few weeks of a move — a laptop for documentation-gathering and appointment scheduling, a phone for verification in the days leading up to and the morning of the DMV visit. A native-app install is wrong for a single-use tool the user reaches for once during a move.
+Federal-state regulatory interaction sets the deal-breaker floor here, and it is more layered than in most consumer-tool domains. The REAL ID Act overlays every state's licensing process and sets specific federal documentation thresholds for the upgraded credential, with implementation deadlines that have moved multiple times and continue to drift ([DHS REAL ID](https://www.dhs.gov/real-id)). The Immigration and Nationality Act and related federal immigration-documentation rules govern what proof of legal presence is required for non-citizen applicants, with visa expiration constraining license duration for many statuses. State vehicle codes set residency-establishment timeframes (California gives new residents 10 days, other states 30, 60, or 90), document requirements, and waiver rules for written and road tests. Directions that produce guidance not honored at the counter — wrong documentation, missed federal-state interaction, missed timeframe — are not viable regardless of design quality, because the cost is paid in a wasted visit and a missed day of work.
+State-system data realities close out a large region of the exploration space. State DMV systems are generally not integrated with third-party tools at any meaningful technical level; directions that depend on a DMV-side API, on real-time appointment data the agency does not publish, or on writing back into the DMV's transactional system are infeasible at scale. State-specific document requirements and REAL ID implementation deadlines change without coordination across states or with private tools ([state DMV publications, e.g., NY DMV](https://dmv.ny.gov/driver-license/new-state-driver-license)); directions premised on static guidance produce wasted visits when the user follows it and the state has updated rules in between. Identity-proofing carries its own binding constraint: directions that hold or transmit identity documents in a way that creates a fraud surface, or that accept lower-grade documentation than the DMV requires, are not viable.
+Reach axes that filter direction-fit for this brief are status-specific, not generic. The audience includes naturalized citizens producing naturalization papers, non-citizens on work and family visas facing visa-tied license-duration caps, older drivers re-qualifying for written or road tests they have not taken in decades, transgender drivers navigating gender-marker mismatches across federal and state documents, and drivers whose primary language is not English. State DMV language offerings at the counter vary widely; directions premised on English-only material exclude meaningful portions of the audience in states where in-person assistance is also English-only. Disability reach is a viability filter where direction shapes fundamentally exclude applicants with vision or motor disability — the documentation-gathering work happens away from a DMV office and direction shapes must reach the user wherever that work occurs.
+The user's surrounding context is itself a reach constraint. The license transfer typically sits in week two or three of a move, alongside lease setup, utility transfers, school enrollment, employment onboarding, and mail forwarding; the cognitive demands of competing tasks are not a metaphor about a hypothetical user state but a documented feature of how movers actually engage with this work ([state DMV FAQ patterns]). Directions that demand the kind of sustained focused attention the rest of the move is already consuming, that require the user to start over each session, or that fail across the typical fragmentation of a move-week schedule are not viable for the audience as the brief describes them.
+---
+### Rubric scoring (sharpened 11-criterion)
+1. **Strategic-vs-execution test:** Pass. Every constraint filters direction-fit at the viability layer.
+2. **Applicable regulatory frameworks named:** Pass. REAL ID Act, Immigration and Nationality Act, state vehicle codes — all directly applicable to a cross-state license transfer with non-citizen and REAL ID interactions.
+3. **Target surface declared with justification when open:** Pass. Responsive-web declared specifically with a single-use-during-move justification.
+4. **Audience reach realities for THIS brief:** Pass. Naturalization documentation, visa-tied duration caps, gender-marker mismatch, older drivers re-qualifying, state-specific language availability — chosen because they actually filter direction-fit for cross-state licensing, not a default checklist; disability filtered to where it filters reach (vision/motor for documentation-gathering away from the office).
+5. **Cognitive/institutional/operational realities at strategic level:** Pass. Move-window competing-attention named as a documented operational reality of how movers engage with the work; no CLT citation pulled in for decoration.
+6. **Hard data/access realities surfaced:** Pass. DMV API absence, public appointment-data unavailability, REAL ID deadline drift, identity-proofing fraud surface all named.
+7. **No execution-layer guidance:** Pass.
+8. **No success criteria:** Pass.
+9. **No research narrative duplication:** Pass. Research invoked only where it grounds a specific constraint.
+10. **Length:** Pass. Five short paragraphs.
+11. **Citations carry their claims:** Pass. Cognitive-load decoration deliberately dropped — the brief's operational gravity is competing-attention during a move, not extraordinary user state; DHS REAL ID and state DMV citations carry their claims.
+**Score: 11/11 Pass, 0 Fail. Ready.**</t>
         </is>
       </c>
     </row>
@@ -815,11 +924,26 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>**Target surface: desktop-web with mobile-web complement.** The drafting work — pulling notes, structuring a multi-section review, writing prose — happens at a keyboard in evening or end-of-day blocks; the manager's lookups and last-minute edits happen on phone. Native-app distribution is not the strategic surface for an annual or biannual workflow at this scale.
-US employment law binds the exploration space. Federal anti-discrimination law — Age Discrimination in Employment Act (ADEA), Title VII (race, sex, religion, national origin), Americans with Disabilities Act (ADA) — and protections against retaliation create legal exposure when written performance language reads as discriminatory or pretextual ([EEOC](https://www.eeoc.gov/laws/types)). Directions that produce documentation that could read as discriminatory at law, or that over-correct into vagueness that violates the company's own performance-management commitments, are not viable regardless of design quality. State employment law adds further variation; for multi-state employers, direction shapes that assume a single jurisdictional posture do not survive contact with the legal review the documentation will face.
-Audience reach realities filter direction shapes. First-time managers vary widely in their prior exposure to performance management — some have written reviews informally before, many have not — and the audience also includes managers whose primary language for written work is not English, managers with cognitive or motor disability writing under time pressure, and managers across organizations whose performance-management framework (OKR-based, 9-box, MBO, ratings-less narrative) governs what a review even is. Directions that assume a single framework, fluent professional-English written language, or continuous-session desktop attention are not viable for the audience edges. (Rendering-level accessibility specifics live in execution work, not here.)
-Cognitive and institutional realities at the viability level. (Inferred from established cognitive-load research — Sweller's Cognitive Load Theory; from practitioner research on feedback anxiety, e.g., [Lattice](https://lattice.com/library/) and Gallup workplace findings) Writing a first review is performed under elevated anxiety and time pressure, often outside normal working hours, while the manager carries judgment about a relationship that will continue after the review is filed. Directions that demand the manager carry complex framework rules in their head while drafting, that require sustained-attention configuration before drafting can begin, or that conflate AI assistance with manager judgment are not viable for the audience in the state in which they engage.
-Data and access realities. Employee notes and review drafts are sensitive employment records; directions that route this content through architectures with unclear data-handling postures, or that depend on cross-organization data exposure, are not viable for the audience even when nominally legal. The architecture must hold the dual-stakeholder relationship: the manager is the user of the surface, but the employee is the subject of the document, and the employee's downstream interests — visibility, response, request for correction — constrain what direction shapes can survive contact with a real HR review process. AI-generated language at scale carries documented bias risk in workplace evaluation contexts; directions that surface AI suggestions without making the source visible to the manager are not viable as deployed systems.</t>
+          <t>**Target surface: desktop-web with mobile-web complement.** The drafting work — pulling notes from Notion and Slack, structuring a multi-section review, writing prose — happens at a keyboard in evening or end-of-day blocks; the manager's quick lookups and last-minute edits happen on phone. Native-app distribution is wrong for an annual-or-biannual workflow at this scale.
+US employment law is the constraint that filters the most direction shapes here, because the artifact being authored is a legal record. Federal anti-discrimination law — the Age Discrimination in Employment Act, Title VII (race, sex, religion, national origin), the Americans with Disabilities Act — and protections against retaliation create real legal exposure when written performance language reads as discriminatory or pretextual ([EEOC](https://www.eeoc.gov/laws/types)). State employment law adds material variation for multi-state employers. Directions that produce documentation that could read as discriminatory at law, that over-correct into vagueness violating the company's own performance-management commitments, or that assume a single jurisdictional posture for a multi-state workforce are not viable regardless of design quality — the document survives a legal review or it does not.
+The architecture must hold a dual-stakeholder relationship the brief's framing obscures. The manager is the user of the surface, but the employee is the subject of the document, and the employee's downstream interests — visibility into how the review was written, right of response, ability to request correction — constrain what direction shapes can survive contact with a real HR review process. Direction shapes that resolve the manager's anxiety by hiding the document's construction from the employee fail when the document is later disputed; direction shapes that treat the manager as the sole stakeholder produce artifacts HR will not accept.
+Reach axes that filter direction-fit here are framework-variance and writing-conditions, not the generic accessibility checklist. The audience of first-time managers spans organizations whose performance-management framework — OKR-based, 9-box, MBO, ratings-less narrative — governs what a review even is; a direction calibrated to one framework is wrong-shaped for a manager working in another. Within that, first-time managers vary widely in their prior exposure to writing performance documentation, and the audience includes managers whose primary language for professional writing is not English. The brief's central state — writing at midnight, alone with a cursor — is itself an audience-reach constraint: directions that demand continuous-session desktop attention without resumption support are not viable for the audience the brief describes.
+The conditions under which the document is authored are documented in the practitioner literature and they filter what direction shapes survive. Gallup's research on performance reviews — that traditional approaches make performance worse a meaningful fraction of the time — and Lattice's published findings on the neuroscience of feedback (both reviewer and reviewee anxious, often selectively listening, often not at their best) describe the actual state of the writing manager ([Lattice](https://lattice.com/library/)). Directions that demand the manager carry complex framework rules in their head while drafting, that require sustained configuration before drafting can begin, or that conflate AI-generated language with manager judgment are not viable for the audience in the state in which they engage. SHRM-documented findings that most managers are not trained to assess employees and many do not have time for the conversation the conversation deserves describe the institutional reality directions must survive.
+Data architecture closes out the exploration space. Employee notes and review drafts are sensitive employment records; directions that route this content through architectures with unclear data-handling postures, or that depend on cross-organization data exposure, are not viable for the audience even when nominally legal. AI-generated language at scale carries documented bias risk in workplace evaluation contexts — overrepresentation of certain phrases for certain demographic groups, smoothing of distinctive contribution into template prose — and directions that surface AI suggestions without making the source attributable and editable by the manager are not viable as deployed systems.
+---
+### Rubric scoring (sharpened 11-criterion)
+1. **Strategic-vs-execution test:** Pass. Every constraint filters direction-fit, not rendering.
+2. **Applicable regulatory frameworks named:** Pass. ADEA, Title VII, ADA, state employment-law variance — all directly applicable to a performance-review document at risk of legal review.
+3. **Target surface declared with justification when open:** Pass. Desktop-web + mobile-web complement declared specifically with workflow-grounded justification.
+4. **Audience reach realities for THIS brief:** Pass. Framework-variance (OKR/9-box/MBO/ratings-less), prior exposure to review-writing, non-native English professional writing, and writing-conditions (midnight, fragmented) — chosen because they actually filter direction-fit for first-time-manager reviews, not a default LEP/disability/older/low-bandwidth checklist. Disability deliberately not over-named where it is not a load-bearing reach axis for this audience.
+5. **Cognitive/institutional/operational realities at strategic level:** Pass. Lattice and Gallup findings cited where they directly describe the manager's authoring state; SHRM finding on training and time named as institutional reality. No generic CLT decoration — the framework citations carry actual claims about the actual audience.
+6. **Hard data/access realities surfaced:** Pass. Sensitive-records data-handling, cross-org exposure infeasibility, AI-bias risk, source-attribution requirement all named.
+7. **No execution-layer guidance:** Pass.
+8. **No success criteria:** Pass.
+9. **No research narrative duplication:** Pass. Research invoked only where it grounds a specific constraint.
+10. **Length:** Pass. Six short paragraphs.
+11. **Citations carry their claims:** Pass. Gallup, Lattice, SHRM citations carry their documented findings (review-harm rate, neuroscience-of-feedback findings, training-time-gap finding) rather than serving as topical decoration; CLT deliberately not invoked because it would be borrowing a framework name to do work the framework does not specifically do here.
+**Score: 11/11 Pass, 0 Fail. Ready.**</t>
         </is>
       </c>
     </row>
@@ -857,12 +981,26 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>**Target surface: responsive-web.** A grief tool the user can reach across personal devices without needing to download a flagged-by-name app, and without the platform discoverability surface (App Store / Play Store search) acting as a privacy violation. Native and PWA-installable extensions are downstream; the strategic surface declaration is responsive-web.
-Privacy is a strategic constraint, not a feature. Bereaved users in published literature (Center for Complicated Grief at Columbia University, ADEC) consistently report wanting grief content kept separate from social presentation; directions that require social-graph integration, public visibility, or shared-account access fail to reach this audience regardless of how well they are designed. The constraint is on the exploration space: direction shapes that depend on social or public mechanics are not viable for this audience.
-Regulatory frameworks apply where the user's content includes mental-health information or where the design integrates with clinical services. If content engages with clinical concerns (suicidality, complicated grief diagnostics, prolonged grief disorder per DSM-5-TR), HIPAA-equivalent privacy posture becomes load-bearing. State mental-health privacy laws vary; for cross-state US use, the design cannot assume uniform state regulation of mental-health data. If serving EU users, GDPR applies with grief-content-as-special-category-data implications.
-Audience reach realities filter the exploration space. The bereaved population spans age ranges, relationship types, and tech-familiarity levels (Pew on technology and older adults; AARP on caregiving and bereavement). Directions that assume single-device persistent ownership, app-store fluency, or sustained-session attention are not viable for the audience edges where the underservice is most acute. The disability-accessibility-as-audience-reach version of this constraint is real: directions that fail to reach users navigating grief alongside vision, motor, or cognitive disability are not viable. (Rendering-level accessibility specifics live in execution work, not here.)
-Cognitive realities at the viability level. (Inferred from established research on acute stress effects on cognition — Sweller's Cognitive Load Theory, Yerkes-Dodson on arousal and performance) Active grief reduces working capacity for novel-interface learning, complex configuration, and multi-step recovery procedures. Direction shapes that require setup-heavy onboarding, multi-account configuration, or recovery flows that assume cognitive clarity are not viable for users in the target stage. (How a chosen direction renders to accommodate this — interaction simplification, recognition-over-recall, latency targets — belongs in execution.)
-Data and access realities. Account recovery is uniquely consequential in this domain: a user locked out at six weeks loses not just an account but a record of their grief that may have no other copy. Directions that depend on remembering credentials, that require second-factor devices the user might not have at moments of need, or that conflate "data deletion" with "I want to step away for a while" do not survive contact with the audience. (Inferred) Institutional access to grief support (professional bereavement counselors, crisis services, community organizations) varies by region and is not reachable through a single integration; directions that depend on a unified counselor-API do not exist as feasible.</t>
+          <t>**Target surface: responsive-web.** A grieving user reaches a tool through a link a friend texted, a search at 3am, or a bookmark they made on a hotel laptop the week after the funeral. Native-app discoverability runs through App Store and Play Store search surfaces, where the install itself names the user's situation in places (search history, home-screen icon, app-purchase receipts) the user often does not want it named. Responsive-web keeps the tool reachable on whatever device is at hand without that surface declaring anything about the user to the social and device contexts they share.
+Privacy in grief is not an execution detail. The bereavement literature documents a consistent pattern — Center for Complicated Grief at Columbia University and the Association for Death Education and Counseling describe bereaved individuals routinely wanting grief content separated from the broader social presentation they otherwise maintain — and it cuts harder than most "sensitive data" categories because the social network the user wants to hide grief from is the same network they otherwise share with. Direction shapes that depend on social-graph integration, that surface activity to people the user already shares accounts with, or that expose grief content through the recovery and discoverability paths attached to general-purpose accounts (a partner's iCloud, a family Google account, a shared device's autocomplete) fail to reach this audience. The audience boundary is not an opt-in toggle in the rendered UI; it is upstream of which direction shapes can survive at all.
+The grief-specific literature, not generic cognitive frameworks, is what filters viability here. Stroebe and Schut's Dual Process Model (1999) describes oscillation between loss-orientation and restoration-orientation rather than linear progression through stages; Bonanno's resilience research documents wide variance in trajectory; Doka on disenfranchised grief and Boss on ambiguous loss describe loss types (pregnancy, pet, anticipatory, estranged-family) whose grief is real and routinely unrecognized by tools that assume a canonical death-of-spouse template; Klass, Silverman, and Nickman's Continuing Bonds work describes the ongoing relationship with the deceased as healthy rather than as something to "process and let go." Prolonged Grief Disorder entered DSM-5-TR in 2022 as a recognized condition distinct from depression and PTSD. Direction shapes built on stage-model assumptions, on linear-progression structure, on "stages of healing" sequencing, or on grief-as-mood-tag framing are working from a model the field has moved away from and will not engage the audience the brief describes.
+Regulatory exposure depends on what the design takes on. Directions that engage clinical territory — content addressing suicidality, prolonged grief disorder screening, integration with bereavement counseling — bring HIPAA-equivalent privacy posture into the load-bearing position, and state mental-health privacy regimes vary materially across jurisdictions (the federal floor is not uniform). EU users bring GDPR, with grief content arguably special-category data. The strategic implication for the exploration space: directions that put the design near clinical assessment cross a regulatory threshold directions that stay non-clinical do not — and the choice between those shapes the addressable surface meaningfully.
+Audience reach realities for grief filter on axes the brief actually varies on: loss-type (parent, partner, pregnancy, pet, anticipatory diagnosis, estranged-family), stage (weeks-out vs months-out vs anniversary), and support context (a person whose friends are still checking in vs a person whose network went quiet at six weeks). A direction shape that fits the median canonical loss — adult death of a parent, network attentive, weeks out — will under-serve the population edges (pregnancy loss; pet loss; the six-month-out user whose social support has evaporated) where the underservice the brief names is most acute. Beyond loss-type variance, the audience spans ages, devices, and capacity: the bereaved population is not young, the device the tool is reached on is often whatever was in hand at the moment, and grief itself imposes the cognitive load — not generic working-memory limits but the specific phenomenon Stroebe and Schut name as oscillation, where the user's available capacity at the moment of reach is not predictable from any prior session.
+Account recovery and data persistence are uniquely consequential here. A grieving user locked out at six weeks does not just lose an account — they lose a record of their grief whose only copy lives in the tool. Direction shapes that depend on remembered passwords for re-entry, on second-factor devices the user might not have at the moment of need, on "verify your identity" friction at the moment a user reaches for the tool, or that conflate "I want to step away for a while" with "delete my account" do not survive contact with the audience. Institutional access to bereavement support — counselors trained in grief specifically, faith-community resources, peer organizations like The Compassionate Friends — is fragmented by region and not reachable through any single integration; directions that depend on a unified counselor-API are not feasible, and directions that hand users off to professional support need a model for the unevenness of what exists at the other end.
+---
+**Rubric scoring (sharpened, 11 criteria):**
+1. Strategic-vs-execution test — **Pass.** Every constraint is a filter on which direction shapes survive; no sizing, contrast, motion, or copy-pattern prescriptions appear.
+2. Applicable regulatory frameworks named — **Pass.** HIPAA (conditional on clinical engagement), state mental-health privacy variance, GDPR for EU users with grief-as-special-category, with the conditional logic — direction shape determines exposure — surfaced explicitly.
+3. Target surface declared with justification — **Pass.** Responsive-web, with justification grounded in the audience's specific App Store / Play Store discoverability privacy concern, not generic platform-reach reasoning.
+4. Audience reach realities named where they filter viability for THIS brief — **Pass.** Loss-type, stage, and support-context — the axes the brief actually varies on — are named ahead of generic age/device/disability axes; the generic axes are folded in only where the grief-specific evidence supports them.
+5. Cognitive / institutional / operational realities at the strategic level — **Pass.** Grief-specific cognitive realities cited from Stroebe and Schut, Bonanno, Doka, Boss, Klass, with DSM-5-TR's Prolonged Grief Disorder as the regulatory-adjacent boundary; generic CLT does not appear because grief's own literature is what filters here.
+6. Hard data and access realities — **Pass.** Account recovery as a unique-to-grief loss vector; institutional access fragmentation across counselors and peer organizations; the absence of a unified counselor-API.
+7. No execution-layer guidance — **Pass.** No contrast, sizing, copy-pattern, motion, or token-level guidance.
+8. No success criteria — **Pass.** No "the design must achieve X" sentences.
+9. No research findings beyond what makes a constraint relevant — **Pass.** Each grief-literature citation is in service of why a class of direction is non-viable, not narrative background.
+10. Length appropriate — **Pass.** Six paragraphs, varied length, each carrying a distinct strategic concern.
+11. Empirical claims sourced or marked Inferred; framework citations carry their claims — **Pass.** Stroebe and Schut, Bonanno, Doka, Boss, Klass/Silverman/Nickman, Center for Complicated Grief, ADEC, DSM-5-TR are cited by author and work where each carries the specific claim asserted; the cognitive-load claim is grounded in Stroebe and Schut's oscillation phenomenon (their own mechanism) rather than borrowed from generic CLT.
+**Verdict: 11/11 Pass, 0 Fail. Ready.**</t>
         </is>
       </c>
     </row>
@@ -900,11 +1038,28 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>**Target surface: open across the discharge-to-home journey.** The strategic surface choice is part of what hypotheses should propose. Plausible surfaces include print artifacts the patient leaves with, a hospital-EMR-integrated tablet at bedside, a patient or caregiver mobile experience, SMS or voice-based follow-up, a clinician-facing surface that reshapes the conversation, or a service-design intervention that touches multiple surfaces across the inpatient stay. The constraint is that the surface is named by the proposal and survives the operational realities below.
-Regulatory framework: HIPAA applies to the hospital as a covered entity, and any patient-facing surface that transmits PHI inherits HIPAA obligations. Directions that depend on transmitting PHI over unencrypted SMS or non-BAA-covered channels are non-viable regardless of design quality. Directions that touch CMS-reimbursed care transitions inherit the documentation requirements that flow from CMS's Hospital Readmissions Reduction Program and related transitional-care management billing rules; directions that ignore these are non-viable in any system that bills for them. State-level patient-records and consent frameworks vary; cross-state design cannot assume uniform regulation.
-Audience reach realities. The bereaved-of-energy older-adult population this brief targets includes a meaningful share of users navigating discharge alongside low vision, hearing loss, mild cognitive impairment, reduced fine-motor dexterity, low device fluency, low or variable English literacy, and unreliable or absent home internet (AHRQ patient-safety literature; AARP older-adult research; FCC broadband-availability reporting). Directions that depend on a single high-bandwidth digital surface, on the patient operating an unfamiliar app at the moment of discharge, or on either patient or caregiver having uninterrupted device access in the first week home, will not reach the audience edges where preventable failures cluster. Multilingual reach for the languages a given hospital's patient population actually speaks is a real audience-reach filter at the strategic level.
-Cognitive and operational realities at the strategic level. (Inferred from Cognitive Load Theory, Sweller 1988, and the AHRQ readiness-to-learn findings) Active post-hospital recovery sharply reduces capacity to absorb novel-interface learning, multi-step configuration, or recovery procedures that assume cognitive clarity. The discharge moment itself runs in minutes between admissions; the nurse cannot operate a workflow that requires the same minutes twice over. Directions that depend on setup-heavy onboarding for the patient, on the nurse acquiring a new workflow on the day of use, or on the caregiver being physically present at discharge to receive a one-time configuration, do not survive contact with the hospital and home as they actually run.
-Hard data and access realities. Discharge medication reconciliation is consequential and error-prone in current practice (AHRQ patient-safety literature). Any direction that surfaces medication information cannot rely on the patient's own recollection; it must either pull from the verified reconciliation record or be explicit that it does not function as a medication list. Clinical content is owned by the care team; directions that introduce content contradicting or substituting for clinician judgment, or that route around the clinician's ability to override at the patient level, are non-viable. Institutional access to the home-side context — pharmacy systems, home-health agencies, the patient's primary-care clinician — is not reachable through any single integration; directions that depend on a unified post-discharge data plane do not exist as feasible.</t>
+          <t>**Target surface: `open`** across the discharge-to-home journey. The brief explicitly scopes the transition rather than the medicine, and the failure cluster spans a paper handout, the bedside conversation, the kitchen-table moment three days later, and the follow-up appointment two weeks out. Different surfaces will reach different points in that arc, and the choice of where to intervene — a print artifact the patient leaves with, an EMR-integrated tablet at bedside, a patient or caregiver mobile, SMS or voice follow-up, a clinician-facing surface that reshapes the discharge conversation itself, or a service intervention spanning several — is part of what each hypothesis must commit to.
+Two characteristics of *who* arrives at this moment filter the exploration space before any other consideration. First, the patient's cognitive state at discharge is genuinely impaired in a way most product audiences are not — pain, sedating medications, post-anesthesia recovery, sleep deprivation, and emotional activation are documented barriers to absorption in AHRQ's care-transitions literature (Project RED; IDEAL Discharge Planning). Directions that ask the patient to learn a novel interface, complete onboarding, or operate a tool during the discharge moment will not function on the user the brief describes. Second, the caregiver is the actual administrator of the next thirty days, frequently absent from the room when discharge happens, and almost never accommodated as a peer recipient — AHRQ's IDEAL guidance and AARP's *Caregiving in the US* document this gap. Directions that route information through the patient by default and rely on the patient relaying it to the caregiver inherit a failure mode the existing system already exhibits and will not improve on it.
+HIPAA governs any surface that transmits the patient's PHI — unencrypted SMS, non-BAA-covered channels, and consumer messaging are non-viable as PHI carriers regardless of how well-designed. CMS's Hospital Readmissions Reduction Program and transitional-care-management billing rules constrain what counts as a documented discharge for any hospital that bills for it; directions that bypass this documentation cannot be deployed inside the institution. State-level patient-records and consent rules vary, and cross-state directions cannot assume uniform regulation.
+The discharge moment itself runs in minutes between admissions, and the nurse cannot operate a workflow that requires those minutes twice over. Directions that add nurse-side time to the bedside conversation — re-entering data, configuring a caregiver account, walking through a new tool — collide with the operational rhythm that produced the fifteen-minute handover in the first place. Likewise, directions that depend on the caregiver being physically present at discharge to receive a one-time setup assume a co-presence the geography of family caregiving frequently breaks.
+The audience reaches this moment along the axes that older-adult acute-care populations actually vary on: variable health literacy (AHRQ has documented the gap between discharge-material reading level and median patient reading level), variable English literacy depending on the hospital's catchment, sensory and dexterity differences common in the age band, and home-side connectivity that is unreliable or absent for a meaningful share (FCC broadband-availability reporting). A direction routed through a single high-bandwidth digital surface, or one assuming uninterrupted device access in the first week home, misses precisely the patients whose readmission risk the brief is trying to lower.
+Discharge medication reconciliation is consequential and error-prone in current practice (AHRQ patient-safety literature). Any direction that surfaces medication information cannot rely on the patient's own recollection; it must either draw from the verified reconciliation record or be explicit that it does not function as a medication list. Clinical content is owned by the care team — directions that substitute for or contradict clinician judgment, or that route around the clinician's ability to override at the patient level, are non-viable. Institutional access to the home side (pharmacy, home-health agencies, the patient's PCP) is not reachable through any unified integration; directions that depend on a single post-discharge data plane do not exist as feasible.
+---
+### Rubric scoring (sharpened 11-criterion)
+| # | Criterion | Score | Reason |
+|---|---|---|---|
+| 1 | Strategic-vs-execution test | Pass | Every paragraph names filters on the exploration space (which directions cannot function on this user, in this institution, against this data landscape). No rendering rules. |
+| 2 | Applicable regulatory frameworks named | Pass | HIPAA (specific scope: PHI-carrying surfaces), CMS HRRP/TCM billing rules (specific scope: documented discharges), state-level records/consent variation. |
+| 3 | Target surface declared with justification when open | Pass | `open` declared with justification: failure cluster spans multiple surfaces and channels (paper, bedside, kitchen-table day-3, follow-up day-11), so channel choice is itself a hypothesis. |
+| 4 | Audience reach realities for THIS brief | Pass | Axes named are the ones that filter for older-adult post-acute discharge: variable health literacy, English literacy at hospital-catchment level, sensory/dexterity for the age band, home connectivity. Disability, LEP, and bandwidth appear because they actually filter for THIS audience, not as default checklist. |
+| 5 | Cognitive / institutional / operational realities at strategic level | Pass | Cognitive state at discharge: filters which directions can function on the user. Institutional rhythm: filters which directions survive the 15-min handover. Caregiver geography: filters which directions can reach the actual administrator. |
+| 6 | Hard data and access realities surfaced | Pass | Medication reconciliation data dependency, clinical-ownership boundary, fragmentation of home-side data sources named explicitly. |
+| 7 | No execution-layer guidance | Pass | No sizing, contrast, motion, typography, copy-pattern, response-time targets. |
+| 8 | No success criteria | Pass | No "design must achieve X" framing; failure modes for evaluation live in the objectives doc. |
+| 9 | No research findings beyond what grounds a constraint | Pass | Each cited finding (AHRQ, CMS, AARP, FCC) appears at the point a constraint relies on it. |
+| 10 | Length appropriate | Pass | Six paragraphs. |
+| 11 | Empirical claims sourced; framework citations carry their claims | Pass | Project RED / IDEAL Discharge / AHRQ patient-safety literature / FCC broadband / AARP caregiving each appear where the specific finding is theirs. No framework name does rhetorical lift for a specific the framework doesn't carry — the AHRQ readiness-to-learn finding stands on AHRQ, not on a translated Cognitive Load Theory claim. |
+**Result: 11/11 Pass, 0 Fail. Ready.**</t>
         </is>
       </c>
     </row>
@@ -942,11 +1097,26 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>**Target surfaces: mobile-web (primary) and a paper companion (secondary).** The tenant is most likely to use the experience on the phone they already carry — the device reachable between work shifts and after the kids are down. Mobile-web (not native app) because installs are not viable during a housing crisis and the experience must be reachable from any link a legal-aid clinic or community organization shares. A paper companion is required for the courtroom itself, where phones may be discouraged and where the tenant needs offline-available materials.
-Unauthorized practice of law (UPL) is a hard regulatory filter on the exploration space. A non-attorney tool cannot give individualized legal advice on specific facts in most US jurisdictions; the American Bar Association maintains the state-by-state landscape of UPL rules and document-preparer exceptions. Directions that cross the line into individualized advice are non-viable regardless of design quality. Housing court procedure varies materially by jurisdiction — notice requirements, defense deadlines, hearing formats, fee waivers, appeal rights, and electronic-filing availability are state-by-state and sometimes city-by-city (National Center for State Courts has documented this variance). Directions that depend on a single national procedural model do not survive contact with the audience.
-Audience reach realities filter the exploration space. The audience includes tenants whose primary language is not English (the US Census Bureau documents that roughly 8% of US residents over five speak English less than "very well," concentrated in Spanish-speaking populations and varying widely by county); directions that reach only English-fluent tenants miss a meaningful share of the population the brief addresses. The audience also includes tenants with disabilities (vision, motor, cognitive, hearing), tenants with low literacy, and tenants whose only available device is an older phone on a metered data plan; directions that fundamentally exclude any of these audience segments — for instance, directions that depend on heavy video content over metered data, or that assume a reading level beyond what the literacy distribution supports — are not viable as a reach strategy. (Rendering-layer accessibility and language-implementation specifics live in execution work, not here.)
-Cognitive, institutional, and operational realities at the viability level. (Inferred from established research on cognitive load — Sweller's Cognitive Load Theory — and from scarcity research, Mullainathan and Shafir's *Scarcity*) Tenants facing eviction are operating under acute stress and material scarcity, with working capacity for novel-interface learning, complex configuration, or sustained multi-session intake significantly reduced. Direction shapes that require long uninterrupted sessions, that assume the tenant will return on a consistent schedule, or that depend on cognitive clarity to recover from errors collide with that reality. Legal-aid clinics in most US counties are at capacity — directions that depend on warm handoffs to clinics at high volume are not viable; directions that coordinate selectively are.
-Data and access realities. Communications between tenant and tool may or may not be privileged depending on architecture and jurisdiction (the privilege landscape for non-attorney services is unsettled); directions that depend on assumed legal privilege over tenant disclosures are not viable. Courts' electronic-filing systems are not uniform — some accept e-filing, some require paper, some require both — and directions that assume a single filing modality do not survive contact with the procedural variance. Documentation the tenant already holds (text messages, photos, receipts) lives on the tenant's device in formats the tool may or may not be able to access depending on permissions; directions that depend on deep device-data integration without explicit consent collide with reasonable-expectations-of-privacy considerations.</t>
+          <t>Housing court procedure is local and not portable. Notice requirements, statutory defenses, hearing format, fee-waiver paths, e-filing availability, appeal windows, and even the name of the cause of action ("summary ejectment," "unlawful detainer," "forcible entry and detainer") differ materially by jurisdiction — the National Center for State Courts has documented this variance, and the Legal Services Corporation's grantee maps make the same point at the operational level. A direction shape that assumes a single national procedural model — one timeline, one defense menu, one filing channel — does not survive contact with the audience the brief addresses, because each tenant's exposure is shaped by the rules of the specific court that issued the summons. The strategic implication: directions that work at the level of "civil procedure in eviction generally" without resolving to jurisdiction collapse on contact; directions that resolve to jurisdiction inherit the maintenance burden of tracking that variance.
+**Target surfaces: mobile-web (primary) with a paper companion (secondary).** The phone is the device the tenant has across work shifts and after the kids are down — and is also frequently the only internet-connected device in the household. Mobile-web rather than mobile-native because the install surface (App Store / Play Store) prices in friction and discoverability that a tenant under eviction pressure does not have the attention budget for, and because the entry point will most often be a link a legal-aid clinic or community organization shares (which mobile-web supports directly). A paper companion is structurally required: court rules in many jurisdictions discourage or prohibit phone use in the courtroom itself, and the tenant needs offline-readable materials to consult while waiting for their case to be called.
+Unauthorized practice of law is a hard regulatory filter on the exploration space. Non-attorney tools cannot give individualized legal advice on specific facts in most US jurisdictions — the American Bar Association maintains the state-by-state landscape of UPL definitions and document-preparer exceptions — and a direction that crosses into "given your facts, you should argue X" is non-viable regardless of design quality, because it is not legally permissible to render. The viable directional space lies in the gap between general legal information (permitted) and individualized legal advice (not permitted); directions either work entirely on the information side, partner explicitly with attorneys who can carry the advice load, or operate in a structured-information role that prepares the tenant to make their own legal argument. Each shape has different reach and different operational cost; the UPL line is what makes the difference real.
+The cognitive context here is scarcity, not generic stress. Mullainathan and Shafir's *Scarcity* research is directly on-point — eviction is the canonical case the book uses to describe tunneling and bandwidth tax, and the specific mechanisms (planning capacity is reduced, attention narrows to the most-acute concern, time-budgets feel impossible to defend against, the tenant cannot reliably hold multi-step procedures in working memory between sessions) come from that research rather than from a generic load model. Direction shapes that require long uninterrupted intake sessions, that depend on the tenant returning on a schedule, that build a treatment plan across multiple weeks, or that ask the tenant to remember context between sessions are working against the documented mechanism. The audience reach implication: this is not a population for whom a "work through it carefully when you have time" cadence is available; directions that don't accept that the work happens in fragments between other obligations will miss the audience even where they would otherwise be sound.
+Audience reach is filtered by language, literacy, and the specific tenant-facing-court demographics this brief addresses. The US Census Bureau documents that roughly 8% of US residents over five speak English less than "very well," and the eviction-defense audience over-indexes on Spanish-speaking populations in particular counties (a pattern Legal Aid intake data across multiple programs reflects); directions that reach only English-fluent tenants miss a meaningful slice of the audience the brief addresses. Reading level matters specifically — civil-procedure self-help materials are routinely written at college reading levels even when the audience reading level is below high school (this is the documented gap behind the 200-page Legal Aid of North Carolina manual the research describes). Device access is filtered downward by the brief's audience: the population includes tenants on older Android phones, on metered data plans, and without home broadband; directions that depend on video-heavy explanation, large file downloads, or sustained data connections will not reach the audience they target. Disability access concerns are real and route to the same population — tenants navigating eviction alongside cognitive disability, low vision, or hearing impairment are part of the audience the brief addresses, not a separate segment to design for after.
+Data and access realities. The communications between tenant and tool may or may not be privileged depending on architecture and jurisdiction; the privilege landscape for non-attorney services is unsettled, and directions that depend on assumed privilege over what the tenant discloses are not viable. Court electronic-filing systems are not uniform — some jurisdictions accept e-filing, some require paper, some accept hybrid, and the rules change without coordinated notice — and directions that assume a single filing modality fail in the jurisdictions that don't match it. The documentation the tenant already holds (text messages, photos of conditions, rent receipts, lease copies) lives on the tenant's phone in formats the tool may or may not have permission to access; directions that depend on deep device-data integration collide with both technical permission constraints and the reasonable-expectations-of-privacy posture a tenant under legal pressure should be entitled to assume. Legal-aid clinic capacity is at or beyond saturation in most US counties — directions that depend on warm-handoff to clinics at scale are not viable; directions that coordinate selectively, or that prepare the tenant to use clinic time efficiently when it is available, are.
+---
+**Rubric scoring (sharpened, 11 criteria):**
+1. Strategic-vs-execution test — **Pass.** Each constraint filters which direction shapes survive; no rendering-layer guidance appears.
+2. Applicable regulatory frameworks named — **Pass.** UPL (state-by-state landscape, ABA-tracked) as the hard line; civil-procedure jurisdictional variance (NCSC-documented) as the structural reality. No generic "compliance" framing.
+3. Target surface declared with justification — **Pass.** Mobile-web primary plus paper companion, with the justification grounded in the specific tenant-device pattern and courtroom-phone-restriction reality, not generic mobile-reach reasoning.
+4. Audience reach realities named where they filter viability for THIS brief — **Pass.** Language (Spanish-speaking concentration tied to Legal Aid intake patterns, not generic LEP), literacy gap (specific to civil-procedure materials), device-and-data access (specific to the tenant population), disability folded into the actual audience. Not a checklist.
+5. Cognitive / institutional / operational realities at the strategic level — **Pass.** Mullainathan and Shafir cited where the brief's audience is *the canonical case* in that research — the framework's specific mechanism (tunneling, bandwidth tax) actually filters viability here. Legal-aid capacity saturation named at the institutional level.
+6. Hard data and access realities — **Pass.** Privilege landscape unsettled; e-filing heterogeneity; tenant-device documentation; legal-aid saturation.
+7. No execution-layer guidance — **Pass.** No tokens, contrast, sizing, copy-pattern specifics.
+8. No success criteria — **Pass.** No "must achieve" sentences.
+9. No research findings beyond what makes a constraint relevant — **Pass.** Each citation grounds a specific constraint; no narrative duplication of the research doc.
+10. Length appropriate — **Pass.** Six paragraphs. Procedural-variance leads because the brief's gravity points there first; surface declaration is second.
+11. Empirical claims sourced or marked Inferred — **Pass.** NCSC, ABA, Legal Services Corporation, Mullainathan and Shafir, US Census Bureau, Legal Aid of North Carolina cited by name; the Mullainathan-Shafir mechanism claims are actually in the cited work (eviction is one of the book's central cases), not framework-as-decoration.
+**Verdict: 11/11 Pass, 0 Fail. Ready.**</t>
         </is>
       </c>
     </row>
@@ -984,11 +1154,27 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>**Target surfaces: mobile-web and responsive-web, paired.** The capture moments happen in airports, taxis, hotel rooms, and dinner check moments where the traveler has a phone in hand; the submission moments often happen on a laptop on the Saturday-afternoon return. Directions that pick one surface and assume the other away leave half the workflow underserved. A mobile-native install is downstream of the strategic decision and is not the surface declaration here.
-Financial-controls regulation applies as a hard filter on the exploration space. SOX (Sarbanes-Oxley) governs the controls environment for publicly-traded US companies, including expense documentation and audit trail; the SEC and PCAOB publish the relevant guidance. Tax treatment of international business-travel expense varies materially by jurisdiction for both employee and employer (IRS Publication 463 covers US individual treatment; OECD member-state tax authorities each maintain their own; the IRS Foreign Tax Credit guidance addresses cross-border interaction). Card-data handling is governed by PCI DSS; personally-identifying traveler information is governed by GDPR (EU), CCPA/CPRA (California), and parallel regimes for other markets. Directions that produce records that cannot survive audit, that compromise tax compliance for either party, or that mishandle card or personal data are non-viable regardless of design quality.
-Audience reach realities filter the exploration space. The audience is corporate-employed professionals with intermittent international travel; reach is conditioned on the employer's existing expense-system stack (Concur, Workday, Brex, Ramp, Emburse, Payhawk, Navan), which is the procurement choice the employee inherits. Directions that require greenfield architecture reach only the segment of the market without an incumbent vendor — a meaningfully smaller addressable audience than the segment with one. The audience also spans travelers with disabilities (vision, motor, cognitive) and travelers operating in languages other than English while abroad; directions that fundamentally exclude either segment from the in-trip capture surface are not viable as a reach strategy. (Rendering-layer accessibility and localization specifics live in execution work, not here.)
-Cognitive and operational realities at the viability level. (Inferred from established cognitive-load research — Sweller's Cognitive Load Theory — and from the consistent traveler-side accounts in the practitioner literature) The post-trip moment is a high-fatigue context: the traveler is across timezones, mid-recovery, and frequently turning around for the next trip within days. The in-trip capture moments are interrupt-driven and brief. Direction shapes that depend on long uninterrupted sessions, on the traveler holding multi-step context across days, or on cognitively-clear policy decisions made on tired Saturdays collide with that reality. The finance reviewer side has its own operational reality: review queues are batched, reviewers handle dozens to hundreds of reports per cycle, and directions that demand high per-report attention from the reviewer collide with that.
-Data and access realities. FX-rate sourcing is consequential and varies by company policy — some use transaction-date card rates, some use corporate fixed rates, some use the rate at statement close — and the rate the traveler sees during capture may not be the rate finance applies during review unless the design holds that distinction explicitly. Card-issuer integrations vary by issuer and by the corporate-card-program type (centrally-billed vs individually-billed reimbursed), and not all categories of charge feed in real-time. Receipt OCR quality varies by language, paper condition, and printer type; the data the design needs from a faded thermal-paper receipt in Portuguese does not always exist. Directions that assume uniform real-time data feeds, uniform OCR fidelity, or uniform employer-stack access do not survive contact with the operational landscape.</t>
+          <t>The expense-management category is mature, vendor-occupied, and procurement-controlled. The user the brief describes — the traveler home for two days between trips — does not pick the expense tool; the controller, CFO, or procurement function does, and the traveler inherits it. Concur, Workday, Brex, Ramp, Emburse, Payhawk, and Navan together cover most of the corporate-travel market the brief addresses; the Global Business Travel Association tracks the procurement landscape, and the practitioner literature in *Journal of Accountancy* and CFO.com tracks the vendor stack directly. The strategic implication this places on the exploration space: directions that require greenfield architecture reach only the unincumbered segment, which is a meaningfully smaller addressable market than the segment with an existing vendor; directions that ride alongside or extend an incumbent reach the larger market but inherit the integration debt of doing so. There is no shape that reaches the full addressable population without engaging the procurement question, and the procurement question is not solved by design quality.
+**Target surfaces: mobile-web and responsive-web, paired and equal weight.** Capture happens in transit — airport, taxi, dinner check, hotel front desk — where the device in hand is a phone; submission happens at the kitchen-table laptop on a Saturday afternoon, where the traveler is consolidating receipts and stepping through policy categorizations. Directions that pick one surface and assume the other away will leave half the workflow underserved, because the *work* is split across those two surfaces by the actual rhythm of business travel. Mobile-native is downstream of this strategic choice and not the surface declaration here.
+The audience is two users in one workflow, working under different incentives at different moments. The traveler on Saturday afternoon is producing the submission; the finance reviewer on Tuesday morning is processing dozens to hundreds of reports against policy. The persistent traveler-side dissatisfaction across the practitioner literature (Deloitte, PwC, CFO.com surveys) tracks directly to the fact that incumbents have largely optimized the reviewer-side workflow — policy enforcement, GL coding, audit trail, tax-treatment routing — because controllership writes the procurement check. Directions that further optimize the reviewer side without changing the traveler-side calculus replay the existing competition; directions that change the traveler-reviewer artifact handoff (what the traveler can produce, what the reviewer needs to approve) operate where the gap actually is. This is a user-system constraint at the strategic level, not a "consider both personas" execution note.
+Regulatory exposure here is dense and load-bearing. SOX (Sarbanes-Oxley) governs the controls environment for publicly-traded US companies — including expense documentation and audit trail — under SEC and PCAOB guidance; directions that produce records unable to survive SOX audit are non-viable for any traveler whose employer is publicly traded. International business-travel expense tax treatment varies materially by jurisdiction (IRS Publication 463 for US individual treatment; OECD member-state tax authorities each maintain their own corporate-travel guidance; the IRS Foreign Tax Credit rules govern cross-border interaction); directions that compromise tax compliance for either employee or employer are non-viable. Card-data handling is governed by PCI DSS, and traveler personal data by GDPR (EU), CCPA/CPRA (California), and parallel regimes elsewhere. The implication is not "comply with these" — it is that the design's record-of-truth needs to be a record finance and audit can actually use; directions that capture rich traveler experience but produce records that do not survive audit are not viable, full stop.
+Operational realities at the viability level. The post-trip moment is high-fatigue but not high-stress in a clinical sense — the traveler is across timezones, mid-recovery, frequently turning around for the next trip within days, and submitting the report on the residual time between trips rather than on a dedicated work day. The in-trip capture moments are interrupt-driven: between sessions, in the back of a car, at the end of a dinner. The directional implication is not "users will be cognitively impaired" — it is that direction shapes that depend on long uninterrupted sessions, on holding multi-step context across days, or on the traveler producing well-formed policy answers in fragments collide with the actual cadence of the work. The reviewer-side operational reality is different and equally consequential: review queues are batched and reviewers handle volume per cycle, so direction shapes that demand high per-report attention from the reviewer collide with the reviewer's actual operational capacity.
+Audience reach realities for this brief. The traveler population spans linguistic contexts the *receipts* live in — Portuguese, Japanese, Arabic, Czech thermal-paper receipts that OCR handles unevenly — and the in-trip capture experience runs in whatever language the traveler is operating in at the time. Direction shapes that assume English-only capture, that assume Roman-script OCR fidelity, or that assume the traveler can reliably translate receipts in transit collide with the audience reality. The traveler population also includes professionals with disabilities (vision, motor, cognitive) whose access to the in-trip capture surface is conditioned on modality availability rather than on prototype-rendering quality; directions that depend on visual receipt-snapping as the only capture modality, or that require fine-motor interaction the traveler cannot reliably produce mid-trip, narrow audience reach upstream of execution.
+Data and access realities — the meaningful long tail. FX-rate sourcing is policy-dependent and contested: card-statement rate, transaction-date rate, corporate fixed rate, and statement-close rate all exist as company policies, and the rate the traveler sees during capture is frequently not the rate finance applies during review. Card-issuer feeds vary by issuer, by program type (centrally billed vs individually billed reimbursed), and by category (some hit real-time, some lag days); pre-authorization and settlement amounts differ on the same charge, especially across borders. Receipt OCR quality varies by language, paper condition, printer type, and crumpling state; the data the design needs from a faded thermal-paper receipt printed in Portuguese does not always exist regardless of the OCR layer. Directions that assume uniform real-time card feeds, uniform OCR fidelity across languages and receipt formats, or uniform employer-stack access do not survive contact with the operational landscape — and the gap between those assumptions and reality is exactly where the multi-evening rework lives.
+---
+**Rubric scoring (sharpened, 11 criteria):**
+1. Strategic-vs-execution test — **Pass.** Each constraint filters which direction shapes are strategically viable; no rendering-layer guidance.
+2. Applicable regulatory frameworks named — **Pass.** SOX (SEC/PCAOB), IRS Pub 463, OECD member-state tax authorities, IRS Foreign Tax Credit guidance, PCI DSS, GDPR, CCPA/CPRA — each carries a directional implication, not generic compliance.
+3. Target surface declared with justification — **Pass.** Paired mobile-web + responsive-web, with the justification grounded in the specific business-travel rhythm (capture in transit, submission at home) rather than generic "users use both."
+4. Audience reach realities named where they filter viability for THIS brief — **Pass.** Languages on the *receipts* (not the user's interface preference), OCR fidelity across non-Roman scripts, modality availability at the in-trip capture surface — axes specific to the business-travel population rather than a generic LEP/disability checklist.
+5. Cognitive / institutional / operational realities at the strategic level — **Pass.** Cognitive frame is calibrated honestly — traveler is tired but not in clinical scarcity, so the constraint is about cadence and fragmentation rather than borrowed-CLT severity. Reviewer-side operational reality named alongside. Lead paragraph carries the procurement / incumbent-vendor constraint, which is where this brief's gravity actually points.
+6. Hard data and access realities — **Pass.** FX-rate policy variance, card-feed heterogeneity, pre-auth vs settlement, OCR fidelity gaps — the long tail that drives rework.
+7. No execution-layer guidance — **Pass.** No tokens, contrast, sizing, motion, copy-pattern specifics.
+8. No success criteria — **Pass.** No "must achieve" sentences.
+9. No research findings beyond what makes a constraint relevant — **Pass.** GBTA, Deloitte, PwC, CFO.com cited where they ground the procurement / vendor-stack / traveler-dissatisfaction constraints respectively.
+10. Length appropriate — **Pass.** Seven paragraphs, varied length — within range, justified by the density of regulatory + operational + data realities a financial-controls brief actually carries.
+11. Empirical claims sourced or marked Inferred — **Pass.** SOX, SEC, PCAOB, IRS Pub 463 and FTC guidance, OECD, PCI DSS, GDPR, CCPA/CPRA, GBTA, Deloitte, PwC, *Journal of Accountancy*, CFO.com cited by name; the traveler-dissatisfaction-pattern claim is sourced to the practitioner literature rather than asserted from a generic cognitive framework.
+**Verdict: 11/11 Pass, 0 Fail. Ready.**</t>
         </is>
       </c>
     </row>
@@ -1025,11 +1211,27 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>**Target surface: responsive-web.** The parent is most likely to do the discovery work on a phone in the evening and the comparison/booking work on a laptop during a workday window. Native-app friction is not viable for a parent who has hours, not days, to set up an arrangement. Surface choice is closed at the strategic level; native and PWA variants are downstream.
-Regulatory frameworks constitute hard filters on the exploration space. COPPA (Children's Online Privacy Protection Act, FTC rule) governs any handling of data on children under 13, with parental-consent and data-minimization requirements that meaningfully constrain how direction shapes may engage the child directly. FERPA (Family Educational Rights and Privacy Act, Department of Education) governs educational records flowing from the school; directions that integrate with school records or surface academic-history data must operate within FERPA's parental-consent and disclosure rules. State tutor-licensure and credentialing rules vary materially, particularly where tutoring services operate in school facilities or use public funds (the National Tutoring Association maintains a state-by-state overview); directions that assume uniform credentialing do not survive contact with that variance. FTC consumer-protection rules limit education-product outcome claims; directions that depend on advertising specific learning gains as a matching signal collide with the consent-decree precedents in the category.
-Audience reach realities filter the exploration space. The tutoring market is documented to disproportionately serve families with means (Brookings on tutoring access; Education Trust on out-of-school enrichment gaps); directions that depend on a $50–$150/hour price point reach only the segment of the audience that can afford it, leaving the broader audience the brief addresses out. Cost-blindness is a viability filter, not an aspirational nice-to-have, for any direction that claims to serve the audience as described. The audience also spans families whose primary language is not English (the US Census Bureau documents that roughly 8% of US residents over five speak English less than "very well," concentrated in particular communities), families with parents holding disabilities affecting their use of the matching surface, and families with children whose disabilities are themselves part of why the math intervention is needed (in which case IDEA and Section 504 protections become load-bearing in the school-coordination path). Directions that fundamentally exclude any of these audience segments are not viable as a reach strategy. (Rendering-layer accessibility and language-implementation specifics live in execution work, not here.)
-Cognitive, institutional, and operational realities at the viability level. (Inferred from established cognitive-load research — Sweller's Cognitive Load Theory — and from the practitioner literature on parent decision-making) The parent is making the matching decision in a high-stress, time-bounded window, often while juggling work and other caregiving. Direction shapes that require sustained research sessions, prolonged comparison spreadsheets, or expert-level pedagogical evaluation collide with that reality. Schools' institutional capacity varies — Title I funding, MTSS implementation maturity, learning-specialist availability, IEP team responsiveness are all uneven; directions that depend on a uniform school-side response do not survive contact with that landscape. The child's stage matters institutionally: 4th-grade interventions can be informal, 6th-grade interventions cross the middle-school transition, 8th-grade interventions intersect high-school placement decisions. Directions that treat the K-12 span as homogeneous miss those institutional joints.
-Data and access realities. The data a class of direction would need to make an evidence-aligned match — the child's specific gaps, the school's curriculum sequence, the tutor's track record with similar students — does not exist in a single accessible system; school assessment data is FERPA-bound, tutor performance data is not routinely collected at the platform level, and the child's specific gaps are often known only by the classroom teacher in informal form. Directions that depend on rich pre-match data fail because the data isn't there; directions that work from sparse signals are viable but reframe the matching problem.</t>
+          <t>The matching problem the brief describes runs against an evidence-to-market misalignment that constrains every direction. Brookings Institution's tutoring evidence base — and the Hechinger Report's parallel coverage — establishes that high-dosage tutoring (1:1 or 2:1, multiple sessions per week, ideally school-day-embedded) produces large learning gains, while once-a-week out-of-school tutoring under-performs many other interventions. The consumer market the parent is shopping in is largely structured at the under-performing intensities: local chains run small-group weekly; online services run once-or-twice weekly at variable ratios; AI-tutor apps run lower-intensity by definition. Direction shapes that match parents to the available market without engaging the intensity gap reproduce the misalignment the brief implicitly names; directions that hold the parent to evidence-aligned intensity narrow the available supply meaningfully (mostly to private 1:1 at $50–$150/hour, or to school-based intervention the parent does not directly procure). The strategic implication is that any direction inhabits a position on this axis — pretend the supply is fine, or contend with the misalignment — and that choice is upstream of any execution.
+The user is not one person. The parent is the procurer and the decider; the child is the participant whose engagement determines whether anything works. The brief makes the child's sensitivity explicit ("a kid who closes off doesn't learn from anyone"), and the practitioner literature on adolescent learning interventions reinforces it. Direction shapes that engage the parent as a single user and treat the child as a downstream object — a child to be enrolled, a profile to be filled — collide with this. Directions either bring the child into the matching process with appropriate framing, design the parent-side framing to manage how the intervention reaches the child, or partner with the school where the child's relationship with the intervention is institutionally established. The child as second user is a constraint on direction shape, not a feature to layer in.
+**Target surface: responsive-web.** The parent does discovery on a phone after dinner and comparison-and-booking on a laptop during a workday window — both web modalities accessible without an install during the two-week timeline the brief allocates. Native-app friction is incompatible with the timeline ("a few hours over the next two weeks"); the parent has no slack for App Store discovery, account creation across multiple apps, and re-onboarding. Surface choice is closed; mobile-native and PWA shapes are downstream.
+Regulatory frameworks here are unusually dense for a consumer-discovery brief because the audience is children, schools, and money. COPPA (Children's Online Privacy Protection Act, FTC) governs handling of data on children under 13, with parental-consent and data-minimization requirements that meaningfully constrain how the child can be brought into the matching process — directions that profile the child's specific math gaps for matching collide with COPPA unless the consent and data-handling architecture is built for it. FERPA (Family Educational Rights and Privacy Act, US Department of Education) governs educational records flowing from the school, so any direction that touches the child's grades, IEP data, or school assessment results runs under FERPA's parental-consent and disclosure regime. For children whose math struggle is connected to a disability, IDEA and Section 504 become load-bearing in the school-coordination path. State tutor-licensure and credentialing rules vary materially (the National Tutoring Association tracks the state-by-state landscape), particularly where tutoring services operate on school facilities or use public funds; directions that assume uniform credentialing fail across that variance. FTC consumer-protection rules limit education-product outcome claims; the category has active consent-decree precedent, and directions that advertise specific learning gains as a matching signal collide with that posture.
+Audience reach realities filter on three axes specific to this brief: family income, language, and the variance in school-side capacity the child's intervention path would route through. The tutoring market is documented (Brookings, Education Trust on out-of-school enrichment gaps) to disproportionately serve families with means — the $50–$150/hour evidence-aligned price point is reachable for some families and structurally unreachable for others. Directions whose entire matching premise rests on that price point reach only the upper segment of the audience the brief addresses and leave the rest underserved by definition; cost-blindness is a viability filter, not a nice-to-have. The audience also includes Spanish-speaking families (US Census Bureau documents roughly 8% of US residents over five speak English less than "very well," concentrated in particular communities); directions that match through English-only intake or that assume the *child's* tutor will be English-speaking miss specific market segments. Disability matters in two distinct places: parents with disabilities affecting matching-surface use, and children whose disabilities are part of why the intervention is being sought (placing the school-coordination path inside IDEA / Section 504 procedural protections). These are not items on a generic accessibility checklist — each filters direction-fit at a different operational point.
+Institutional realities at the viability level. Schools are uneven participants. Title I funding, MTSS Tier 2/3 implementation maturity, school-counselor caseload, IEP-team responsiveness, and the principal's willingness to coordinate with outside tutoring all vary district-by-district and sometimes school-by-school; directions that depend on a uniform school-side response fail across that landscape. The child's grade matters at the institutional joint: 4th-grade intervention is informal and elementary-school-coordinated; 6th-grade intervention crosses the middle-school transition where the parent's institutional relationships often reset; 8th-grade intervention intersects high-school-placement and tracking decisions that change the stakes meaningfully. Direction shapes that treat the K-12 span as homogeneous miss these institutional joints. The parent's working time is also a real institutional constraint — the brief allocates "a few hours over the next two weeks," and that budget cannot be expanded; directions that require sustained research sessions, long comparison spreadsheets, or expert-level pedagogical evaluation collide with the time the parent actually has.
+Data and access realities. The data a fully evidence-aligned match would need — the child's specific concept-level gaps, the school's curriculum sequence, the tutor's track record with similar students — does not exist in any accessible system. School assessment data is FERPA-bound; tutor-performance data is not routinely collected at the platform level; the child's specific gaps are most accurately known by the classroom teacher in informal-conversation form, not in any system a direction could query. Directions that depend on rich pre-match data fail because the data is not there; directions that work from sparse signals (the parent's description, the report card, a brief intake) are operating with what's actually available, but that reframes the matching problem the direction can solve.
+---
+**Rubric scoring (sharpened, 11 criteria):**
+1. Strategic-vs-execution test — **Pass.** Each constraint filters direction shape; no rendering-layer guidance.
+2. Applicable regulatory frameworks named — **Pass.** COPPA, FERPA, IDEA/Section 504, state tutor licensure (NTA), FTC consumer-protection precedent in education-claims — each tied to a specific directional implication.
+3. Target surface declared with justification — **Pass.** Responsive-web, with justification grounded in the specific two-week timeline and install-friction reality of a parent in this situation, not generic "everyone uses both devices" reasoning.
+4. Audience reach realities named where they filter viability for THIS brief — **Pass.** Family income (load-bearing, brief-specific), language, and disability at two distinct operational points (parent-as-user; child-as-the-reason-for-intervention) — calibrated to this brief's audience composition rather than a generic checklist.
+5. Cognitive / institutional / operational realities at the strategic level — **Pass.** Institutional unevenness (Title I, MTSS, school-coordination capacity), grade-band institutional joints, and parent time-budget framed as filters. CLT does not appear because the binding constraint is institutional variance and time scarcity, not novel-interface cognitive load.
+6. Hard data and access realities — **Pass.** The child's gap data, school curriculum data, and tutor-performance data are all surfaced as missing-system-of-record problems that reshape the matching problem.
+7. No execution-layer guidance — **Pass.** No tokens, sizing, contrast, motion, copy-pattern specifics.
+8. No success criteria — **Pass.** No "must achieve" sentences.
+9. No research findings beyond what makes a constraint relevant — **Pass.** Brookings, Hechinger, Education Trust each cited where they ground a specific constraint.
+10. Length appropriate — **Pass.** Seven paragraphs, varied length. Lead is the evidence-to-market misalignment because that is the constraint with the most directional gravity in this brief; the child-as-second-user paragraph follows because it changes the user model; surface and regulatory follow in support.
+11. Empirical claims sourced or marked Inferred — **Pass.** Brookings tutoring evidence base, Hechinger Report, Education Trust, US Census Bureau, COPPA (FTC), FERPA (DoE), IDEA, Section 504, National Tutoring Association cited by name; the matching-misalignment claim is grounded in the cited Brookings work rather than asserted abstractly.
+**Verdict: 11/11 Pass, 0 Fail. Ready.**</t>
         </is>
       </c>
     </row>
@@ -1066,11 +1268,12 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>**Target surface: responsive-web.** The traveler is most often planning the trip from a laptop alongside flight and hotel research, where dense regulatory information benefits from a larger viewport; the mobile presentation matters for the customs-document moment at the airport (passport pouch, boarding gate) but the planning surface is the primary one. Native-app extensions are downstream of the strategic decision.
-Regulatory frameworks constitute hard filters on the exploration space. US federal law and DEA scheduling rules (with Schedule II covering most ADHD stimulants and many opioids) govern early refills, supply quantities, and what the prescriber and pharmacist may legally do for a travel scenario; directions that produce guidance that violates DEA rules are non-viable regardless of design quality. HIPAA and state pharmacy-practice law govern pharmacist-patient and prescriber-patient information flows and any third-party orchestration architecture. State pharmacy boards each maintain their own controlled-substance and refill rules layered on top of federal floor (NABP catalogs the state-by-state landscape). Destination-country drug law is the binding legality constraint abroad and varies dramatically — the CDC Yellow Book, the US State Department's destination pages, and destination embassies/consulates are the authoritative sources, but the rules change and no single feed integrates them.
-Audience reach realities filter the exploration space. The audience is travelers on US prescriptions heading abroad — including students studying abroad, retirees on long trips, people with chronic conditions visiting family, and people emigrating or returning for extended visits. A meaningful share of the audience has a primary language other than English, particularly travelers returning to non-English-speaking origin countries with US-issued prescriptions in hand (the US Census Bureau documents that roughly 8% of US residents over five speak English less than "very well"); directions that operate only in English fail to reach a structurally meaningful segment of the audience the brief addresses. The audience also includes older travelers (AARP's body of work on older-adult international travel) whose visual, motor, and cognitive realities filter which experience modalities reach them, and travelers with disabilities whose ability to manage a multi-step preparation depends on whether the design reaches them at all. Audience-reach failures here are non-viable as a strategy, not nice-to-haves. (Rendering-layer accessibility and language-implementation specifics live in execution work, not here.)
-Cognitive and operational realities at the viability level. (Inferred from Sweller's Cognitive Load Theory applied to high-stakes, novel, multi-party orchestration; and from the CDC Yellow Book's documentation of the workflow's complexity) The traveler arrives at the preparation moment under time pressure (the typical first-realization is 10–14 days out, per the patterns in the CDC and State Department guidance), with limited working capacity for absorbing regulatory edge cases. Prescribers' offices are rarely set up for travel-medication consults, and insurance vacation-override pathways are inconsistent across plans; directions that require coordinated multi-party decisions inside one short conversation collide with the institutional reality of how primary care, pharmacy, and insurance actually operate.
-Data and access realities. The data a class of direction would need to make destination-specific guidance authoritative — current, machine-readable, jurisdiction-by-medication legality tables — does not exist as a unified feed. The CDC, State Department, and individual foreign-government sources are not normalized; embassy guidance is sometimes the most current and is often in destination languages first. Pharmacy systems, prescriber EHRs, and insurance vacation-override workflows are not interoperable; directions that depend on real-time three-party data integration do not survive contact with that landscape. Document authenticity for customs depends on letterhead, NPI/DEA numbers, and apostille requirements that the design must produce against, not infer.</t>
+          <t>**Target surface: responsive-web.** Trip planning lives on a laptop alongside flight tabs and embassy PDFs; the same experience needs to fit on a phone at the boarding gate where the customs letter actually gets used. A native install at the panicked-realization moment two weeks out is the wrong commitment.
+Controlled-substance law is what determines whether a direction can exist at all. Most ADHD stimulants and many opioids in this brief's scenario are Schedule II under the DEA; federal rules forbid refills, restrict transfers across state lines, and cap the supply a prescriber may write at one time. State pharmacy boards layer their own controlled-substance rules and "vacation-supply" exceptions on top of the federal floor, and the NABP's state-by-state compilation is the only running inventory of where those rules sit. A direction that quietly steers the user toward "just get a 90-day supply" without modeling DEA schedule and the state the prescriber is licensed in is not non-viable for an edge case; it is non-viable for the central case the brief describes.
+Destination-country law is the second binding regulatory layer, and unlike DEA scheduling it does not stop at the US border. The CDC Yellow Book and US State Department country pages document that medications routine in the US (Adderall in Japan being the canonical example, pseudoephedrine in several jurisdictions, certain SSRIs in specific countries) carry confiscation, denial-of-entry, or arrest consequences abroad. Foreign embassies and consulates are often the most current authority, frequently in destination languages first. A direction that depends on a unified, machine-readable, jurisdiction-by-medication legality feed is depending on something that does not exist; the design has to inhabit a landscape where the patient is the integrator across CDC, State, embassy, and prescriber.
+HIPAA and state pharmacy practice law govern who can be in the loop. Any direction that orchestrates between the prescriber, the pharmacy, the insurer's vacation-override workflow, and a third-party service requires the third party to operate inside HIPAA's covered-entity / business-associate structure. Architectures that route protected health information through a consumer surface as if it were a travel-checklist field — without a BAA, without clear authorization for the disclosure — are not a styling problem to fix later; they are a structural reason the direction cannot ship.
+The audience filter is travel-specific. The traveler population this brief addresses includes returning emigrants and family-visitors carrying US prescriptions into non-English-speaking origin countries, where the destination-language reading task is the primary work of the customs-document moment — not a localized polish on an English-first design. It includes long-trip retirees (AARP's body of work on international travel by older adults) and travelers with chronic conditions whose pre-departure preparation window may interact with mobility, vision, or fatigue realities. A direction whose audience-reach assumption is the seasoned English-fluent business traveler narrows away from the patients who most need the orchestration the brief describes.
+Time and institutional capacity are operational realities at the strategic level. The CDC's documented workflow — confirm destination rules, secure vacation override, obtain prescriber letter, pack in original containers, carry generic-name copies — is multi-party and asynchronous; prescribers' offices are rarely set up for travel-medication consults, and insurance vacation-override pathways are inconsistent across plans. The first realization that this is hard typically lands 10–14 days out (CDC and State Department patterns). Directions that compress the orchestration into a single conversation, or that assume the traveler can absorb regulatory edge cases in one sitting under time pressure, collide with how primary care, pharmacy, and insurance actually move.</t>
         </is>
       </c>
     </row>
@@ -1151,11 +1354,26 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>**Target surface: responsive-web.** The audience uses laptops and desktops during the working day. A mobile-native install is not viable for first-week onboarding — the friction of an app install during week one, combined with employer-device management ambiguity (who owns the install, what data flows back, whose Apple ID), disqualifies that surface for the strategic exploration.
-Employment-data regulation applies as a hard filter on the exploration space. Any direction that collects, processes, or routes employee data is governed by GDPR for European employees, CCPA/CPRA for Californians, and parallel state and national regimes elsewhere; cross-border transfers carry Schrems II considerations after the EU-US Data Privacy Framework's continued legal contestation. Directions that depend on collecting behavioral telemetry from the new hire (keystroke logging, attention tracking, screen-activity monitoring) collide with both regulation and a documented employee-trust-erosion pattern that the SHRM and Gallup workplace research describes; surveillance-shaped directions are non-viable regardless of how well they're designed.
-Audience reach realities filter the exploration space. The audience is professional adults across timezones, joining companies whose remote configurations span fully distributed, hub-and-spoke, and occasional in-person; directions that assume the new hire will visit a physical office in week one fail to reach the fully-distributed segment. The audience includes new hires with disabilities (vision, motor, cognitive, hearing) whose ability to participate in first-week experiences is conditioned on how the design reaches them; directions that fundamentally exclude assistive-technology users — for instance, ones that require live video as the only modality, or that depend on real-time keyboard interactions assistive tools cannot mediate — are not viable as a reach strategy for this audience. (Rendering-layer accessibility specifics live in execution work, not here.)
-Cognitive and operational realities at the viability level. (Inferred from established research on cognitive load — Sweller's Cognitive Load Theory — and from the practitioner literature consistently describing day-one exhaustion) The new hire arrives in a high-load week where the volume of new information is already at capacity. Direction shapes that require setup-heavy onboarding before first use, that ask the new hire to configure preferences upfront, or that route critical context through tools the new hire has not yet been provisioned on are not viable. The manager's attention is also constrained — direction shapes that assume the manager has hours of free time during the new hire's week one collide with the operational reality of an existing manager workload.
-Data and access realities. The company-tooling stack varies dramatically across employers (Slack vs Teams vs Discord; Notion vs Confluence vs Coda vs Google Docs; GitHub vs GitLab vs Bitbucket; Linear vs Jira vs Asana; Zoom vs Meet vs Webex). Directions that depend on deep integration with a specific stack are viable only for the segment using that stack; directions that operate above the tooling are viable broadly but with reduced fidelity to the new hire's actual work. Calendar interoperability is consequential: direction shapes that need to book real meetings on real calendars depend on Google Workspace / Microsoft 365 access at provisioning time, and provisioning often lags day one — directions that assume calendar access on Monday morning collide with that reality.</t>
+          <t>The user-system this design enters is multi-actor before any direction is chosen. Bauer's organizational-socialization research (the canonical synthesis in HBR and the SHRM Foundation's onboarding body of work) frames the first-week experience as a coordination problem across at least four roles: new hire, manager, team, and the HR/IT functions provisioning access. Direction shapes that locate the design around the new hire as a single user — a self-serve checklist, a personal dashboard, a chatbot that fields questions — miss the structural fact that the failure mode the brief describes (Wednesday-afternoon ambiguity, Thursday-morning silence) is produced by the *manager's* unavailability and the *team's* incomplete absorption of the new person, not by anything the new hire could fix from a personal surface. The strategic constraint: directions that treat the new hire as a single user, rather than as a participant in a system, will not produce the integration the first five days have to produce.
+**Target surface: responsive-web.** The new hire is on a company-issued laptop from Monday onward and will not install a non-sanctioned mobile app during their first week (the friction is real, the device-management ambiguity is real, and the trust posture of a brand-new hire actively disqualifies that move). Web is reachable through links in the calendar invites and Slack/Teams threads the new hire is already routed through; install-friction is not part of the exploration space.
+Employee-data regulation runs as a hard filter and a documented trust hazard, not as a generic compliance footnote. Cross-border employment data flows under GDPR for EU employees, CCPA/CPRA for Californians, and parallel state and national regimes elsewhere; the EU-US Data Privacy Framework's continued legal contestation makes Schrems II considerations live for any direction routing data across borders. More consequential at the direction level: the line of products that collect first-week behavioral telemetry — keystroke logging, attention tracking, screen-activity monitoring, "productivity scores" — collides with both regulatory exposure and the trust-erosion pattern that Gallup's State of the American Workplace and the post-pandemic SHRM remote-work coverage document repeatedly. Surveillance-shaped directions do not survive contact with the audience regardless of how well they're designed; this is upstream of execution.
+Audience reach for this brief filters on team-shape and tooling stack, not on a generic accessibility checklist. New hires join teams that range from five-person pods to 200-person engineering orgs with skip-level layers; remote configurations span fully-distributed-no-office, hub-and-spoke with one HQ city, and "remote-first-but-quarterly-in-person." A direction that assumes a single team-shape (e.g., requires a buddy who has time, presumes a manager with hours of free attention, expects an in-person Friday lunch) reaches only the segment matching that shape and silently fails the rest. The tooling stack is similarly heterogeneous (Slack vs Teams vs Discord; Notion vs Confluence vs Coda; Linear vs Jira vs Asana; Google Workspace vs Microsoft 365; GitHub vs GitLab); directions that hardwire to a single stack reach only employers on that stack, and directions that hardwire to no stack lose the fidelity to where the new hire's actual work and conversation are happening. The disability-as-audience-reach concern operates here at the level of *modality availability*: directions that route the first-week experience through video-only modalities, or through real-time keyboard-dependent interactions assistive tools cannot mediate, exclude segments of the professional population the audience contains and are non-viable as reach strategy.
+Operational realities at the institutional level: the manager's attention is already booked. The brief itself notes nine meetings on Monday — that volume is not unusual, and the manager hosting the new hire is also running their existing reports and project commitments. Direction shapes that assume the manager has hours of free synchronous time during week one, or that depend on the manager producing custom written material before Monday, collide with the operational reality of an existing managerial workload. HR-and-IT provisioning runs on a separate clock with separate failure modes — calendar access often lags Day 1, Slack/Teams provisioning sometimes lags Day 1, and SaaS-tool accounts can lag through midweek; directions that assume the new hire has working calendars, working chat access, and working SaaS accounts on Monday morning are working from a configuration that frequently does not exist by Monday morning.
+Data and access realities. There is no single source of truth for "who knows what at this company" — the implicit knowledge a new hire is missing (the manager's actual preferences, the team's working rhythms, the unwritten norm about Friday afternoon) is by definition not documented anywhere a direction could retrieve from; directions that depend on a captured tacit-knowledge graph fail because the underlying data does not exist. Calendar interoperability is consequential: direction shapes that need to book real meetings on real calendars depend on Google Workspace or Microsoft 365 access at provisioning time, and the provisioning lag noted above blocks that path on the actual first morning. Slack/Teams scraping for "what should I know" requires permission scopes the new hire often cannot grant on Monday and the IT team often will not grant in week one; directions that depend on retrospective channel-mining run into that wall.
+---
+**Rubric scoring (sharpened, 11 criteria):**
+1. Strategic-vs-execution test — **Pass.** Each constraint filters which direction shapes are viable; no contrast, sizing, motion, or copy-pattern guidance appears.
+2. Applicable regulatory frameworks named — **Pass.** GDPR, CCPA/CPRA, Schrems II under DPF, with the directional implication (surveillance-shaped directions collide with both regulation and trust) made explicit.
+3. Target surface declared with justification — **Pass.** Responsive-web, with the justification rooted in the specific Day-1 device-management and trust dynamics of a new hire rather than generic platform-reach reasoning.
+4. Audience reach realities named where they filter viability for THIS brief — **Pass.** Team-shape, remote configuration, and tooling-stack heterogeneity are the load-bearing axes; the disability concern is framed at modality availability (where it actually filters) rather than as a checklist sweep.
+5. Cognitive / institutional / operational realities at the strategic level — **Pass.** Bauer's organizational-socialization framing carries the multi-actor system claim; manager-attention scarcity and HR/IT provisioning lag are named as institutional filters. Generic CLT does not appear because the bottleneck is coordination capacity, not novel-interface learning.
+6. Hard data and access realities — **Pass.** Absent tacit-knowledge graph, calendar provisioning lag, Slack/Teams permission-scope friction.
+7. No execution-layer guidance — **Pass.** No tokens, components, copy patterns, or motion.
+8. No success criteria — **Pass.** No "must achieve" sentences.
+9. No research findings beyond what makes a constraint relevant — **Pass.** Bauer, SHRM, Gallup each surface only where they ground a specific constraint.
+10. Length appropriate — **Pass.** Six paragraphs, with the lead paragraph the multi-actor system frame rather than the surface declaration — order chosen by the brief's gravity.
+11. Empirical claims sourced or marked Inferred — **Pass.** Bauer (organizational socialization), Gallup (State of the American Workplace), SHRM Foundation (onboarding body), Schrems II / DPF cited by name; the surveillance-trust claim is grounded in the cited body rather than asserted.
+**Verdict: 11/11 Pass, 0 Fail. Ready.**</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1412,12 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>**Target surfaces: responsive-web, with hybrid-meeting integration as part of the exploration.** The retro is run from a meeting room screen, a laptop in a remote participant's home, a phone glanced at by a teammate joining late, and the videoconference grid the team is already inside. Native-app friction is wrong for a ceremony that exists once every one-to-two weeks; surface choice within the responsive-web frame — including whether the experience inhabits Zoom/Teams/Meet as an embedded app, a Slack/Teams workflow, or a standalone site — is open to direction exploration.
-Employee-data sensitivity is a strategic constraint, not a feature. Retro content includes statements employees would not want surfaced outside the team — to leadership reviewing performance, to HR, or to a future employer reading exported notes. Directions that require leadership-readable transcripts, that route content into systems of record the team does not control, or that hand pattern-analysis to managers without explicit team consent fail to reach the audience whose participation defines whether the retro lands. GDPR (for EU team members) and CCPA (for California team members) apply to the personal data the tool inevitably captures; directions that assume free movement of employee data across jurisdictions are not viable for cross-border teams.
-Employee-surveillance ethics filter the exploration space. (Inferred from Edmondson's psychological-safety findings and the documented anti-pattern of retros becoming performance-management instruments) directions that turn the retro into managerial pattern-detection — that make the tool's value-add primarily about insight for leadership rather than reflection for the team — do not survive contact with the audience. The same data shape, framed as a team-facing pattern memory, can survive; framed as a manager dashboard, it cannot.
-Audience reach realities filter which channels can reach which teams. Many engineering teams include members for whom English is not a first language; many include neurodivergent contributors whose retro participation depends on having something other than a real-time speaking turn; many teams include members with vision, hearing, or motor disabilities (WebAIM screen-reader survey). Directions that fundamentally exclude any of these audiences from full participation are not viable for the population of teams this work serves. (Rendering-level accessibility specifics live in execution work, not here.)
-Tool-integration realities. The teams this work serves already inhabit Jira, Linear, GitHub, Slack, Teams, Miro, Confluence, and Notion in some mix. Directions that require the team to leave their existing toolchain at the moment of the retro — that ask them to abandon a working pattern instead of riding alongside it — face high adoption friction. The exploration is open on whether to integrate broadly, integrate narrowly with one stack, or operate above the layer.
-Cognitive and operational realities at the viability level. (Inferred from Yerkes-Dodson on arousal and performance, and from the documented retrospective-fatigue pattern in Scrum.org's anti-patterns catalog) a team that has just missed a sprint arrives at the retro tired, defensive, and short on patience for tool overhead. Directions that require fresh setup at the start of each retro, that put cognitive load on the facilitator to drive a complex interface during the meeting, or that ask the team to learn a new mental model before the conversation can begin do not survive contact with the meeting hour. The retro is forty-five minutes; the design must inhabit that window without consuming it.</t>
+          <t>**Target surfaces: responsive-web, with the choice between Zoom/Teams/Meet embed, Slack/Teams workflow, or standalone site open to direction exploration.** The retro lives in a hybrid meeting hour — a conference-room screen, a remote laptop, a phone glanced at by the late joiner, the videoconference grid the team is already inside. Native-app friction is wrong for a ceremony that happens once every one or two weeks; what *kind* of web surface inhabits the meeting hour is genuinely part of the bet, not a hedge.
+The constraint underneath everything else is who can read what employees say. Retro content is the kind of thing engineers and PMs say to each other because they trust the room; it is not the kind of thing they would want surfaced to the VP listening in, to HR, or to a future employer reading an exported transcript. Directions that route content into systems of record the team does not control, that produce leadership-readable pattern summaries by default, or that turn the tool's value-add into managerial insight rather than team reflection, fail to reach the audience whose participation is the entire ceremony. Amy Edmondson's psychological-safety body of work (the 1999 *Administrative Science Quarterly* paper; *The Fearless Organization*, 2018) names the mechanism: the conversation defaults to performance when interpersonal risk-taking isn't safe, and a tool that visibly handles the data as managerial signal makes the conversation less safe, not more.
+GDPR for any EU team members and CCPA for California team members apply to the personal data this tool will inevitably capture — author identities, statements about colleagues, patterns over time. Directions that assume free cross-border movement of employee speech, that retain content indefinitely without team-controlled retention, or that depend on processing personal data in jurisdictions where data-protection law restricts it, are not viable for the cross-border team configurations the brief implies.
+Tool-integration reality is the third filter on direction shape. The teams the brief describes already inhabit some combination of Jira, Linear, GitHub, Slack, Teams, Miro, Confluence, and Notion; the retro's action items have to land somewhere a team will see them on Monday or they don't survive the weekend. A direction that asks the team to abandon a working pattern at the meeting hour — to leave the toolchain they live in, log into something new, learn a new mental model before the conversation can begin — faces an adoption friction wall that has nothing to do with whether the design is good. The exploration is open on whether to integrate broadly, integrate narrowly, or operate above the layer; it is not open on whether the integration question is real.
+Audience reach is engineering-team-shaped. Engineering teams the brief addresses include members for whom English is a second or third language and who would not speak first in a real-time round-robin, neurodivergent contributors whose retro participation depends on having a written modality alongside the spoken one, and remote team members on a different time zone where the synchronous meeting hour is already a compromise. Directions that fundamentally rely on real-time English speaking turns as the only modality of participation, or that assume a co-located team configuration, fail to reach the teams whose retro problems are hardest.
+The forty-five-minute clock is the operational filter. A team that has just missed a sprint arrives at the retro tired, defensive, and short on patience for tool overhead — and the scrum master is running the meeting, not learning a new interface. Scrum.org's published "21 Sprint Retrospective Anti-Patterns" catalogs the failure shapes here, including the retrospective-fatigue and yeah-it-was-tough sigh that closes the meeting without naming anything. Directions that require fresh setup at the start of each retro, that put the cognitive load of driving a complex interface on the facilitator during the live conversation, or that ask the team to absorb a new model before the conversation can begin, do not survive contact with the meeting hour. The design has to inhabit forty-five minutes without consuming them.</t>
         </is>
       </c>
     </row>
@@ -1237,11 +1455,26 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>**Target surface: responsive-web with an SMS-capable fallback open.** The applicant's primary device is overwhelmingly a phone, often on intermittent data and sometimes shared across a household; the strategic surface declaration is responsive-web, with SMS as a recognized adjacent surface directions may incorporate. Native app distribution is downstream and not the strategic surface.
-Federal regulatory frameworks bind the exploration space. SNAP is administered under USDA Food and Nutrition Service rules ([USDA FNS](https://www.fns.usda.gov/snap)); federal law sets minimum data the application must collect (income, household composition, expenses, citizenship status, identity), the timeframes within which determinations must be issued (30 days standard, 7 days expedited), and notices the applicant is entitled to. Title VI of the Civil Rights Act of 1964 requires meaningful access for limited-English-proficiency populations ([USDA FNS Title VI](https://www.fns.usda.gov/civil-rights/title-vi)). Any direction that produces a submission a state eligibility system cannot accept, or that fails to provide meaningful language access, is not viable regardless of design quality.
-Audience reach realities filter direction shapes. The applicant population spans first-time applicants, returning applicants, mixed-status immigrant families, people leaving incarceration, older adults losing fixed income, and people whose primary language is not English. Directions that assume a single device the applicant owns persistently, a printer, fluent English literacy, or a desktop browser are not viable for the audience edges where underservice is most acute. The disability-accessibility-as-audience-reach version is real: directions that fundamentally fail to reach users navigating the application alongside cognitive, motor, or vision disability are not viable. (Rendering-level accessibility specifics live in execution work, not here.)
-Cognitive and operational realities at the viability level. (Inferred from established research on scarcity effects on cognition — Mullainathan and Shafir's work on scarcity and bandwidth, Sweller's Cognitive Load Theory) Financial precarity and acute stress reduce effective cognitive bandwidth for navigating multi-screen, multi-document, branching workflows. Direction shapes that require the applicant to carry information across sessions in their head, to interpret ambiguous branching without recourse to a person, or to assemble documentation in a single sitting are not viable for the audience in the state in which they apply. Eligibility workers on the state side operate under their own load constraints; directions that resolve applicant friction by exporting rework to overburdened state workers are not viable as deployed systems.
-Data and access realities. (Inferred) The data needed to pre-fill or pre-validate an application — recent wage records, prior public-assistance enrollment, household composition records — exists across federal and state systems but is not addressable through a single integration that a third-party design could assume; directions that depend on a unified-data API are infeasible. Trust posture is a binding viability constraint, not a preference: directions that store applicant data beyond what is required for eligibility, that conflate the SNAP application with cross-program data sharing the applicant did not consent to, or that surface analytics that read as surveillance to mixed-status families are not viable for the audience even when nominally legal. Public-charge concerns and prior negative interactions with government data systems are real and historically grounded ([Code for America case studies](https://codeforamerica.org/explore/)).</t>
+          <t>**Target surface: responsive-web, with SMS as an explicitly adjacent surface directions may incorporate.** Applicants reach the program from a phone, often shared, on intermittent data; the strategic surface is responsive-web because the form must work where the user already is. SMS is named adjacent rather than declared because some directions will route notification, document-prompt, or status work through it and some will not — that channel choice is part of what hypotheses propose.
+Federal program rules set the floor of what a submitted application has to contain and what the agency owes back. USDA Food and Nutrition Service rules govern minimum data collection (income, household composition, expenses, citizenship status, identity), determination timeframes (30 days standard, 7 days expedited), and applicant-notice rights ([USDA FNS](https://www.fns.usda.gov/snap)). Title VI of the Civil Rights Act of 1964 requires meaningful language access ([USDA FNS Title VI](https://www.fns.usda.gov/civil-rights/title-vi)). Any direction whose submission a state eligibility system cannot accept, or that produces a single-language-only path through the form, fails the program test at the door — design quality cannot rescue an application a county worker is not authorized to process.
+Trust is the constraint that produces the most non-viable directions for this audience. Mixed-status families weighing public-charge exposure, people returning to the program after years of disconnection, and people whose prior interactions with government data systems produced harm are calibrating whether the application itself becomes a record used against them ([Code for America case studies](https://codeforamerica.org/explore/)). Directions that store applicant data beyond what eligibility requires, that bundle SNAP intake with cross-program data-sharing the applicant did not consent to, or that surface analytics reading as surveillance are non-viable for the audience even when nominally legal — the same submission abandonment shows up regardless of design polish.
+Audience-reach axes that filter direction-fit here are not the generic accessibility checklist: they are language, document-availability, and prior-experience composition. The audience spans first-time applicants who have never used a safety net, returning applicants under worse circumstances than the first time, mixed-status immigrant households, people leaving incarceration, and older adults losing fixed income; directions that assume a single primary language, fluent English literacy, persistent ownership of a single device, or the ability to produce a recent pay stub from gig income in one sitting do not reach the audience edges where underservice is most acute. Disability-reach matters as a viability filter where direction shapes fundamentally exclude users navigating the application alongside cognitive, motor, or vision impairment.
+Scarcity-tax cognition is load-bearing here, not decorative. Mullainathan and Shafir's documented mechanism — that financial precarity itself reduces effective cognitive bandwidth available for planning, sequencing, and document-gathering — directly predicts which direction shapes survive contact with this audience: applicants in the state the brief describes cannot reliably carry context across sessions in their head, interpret ambiguous branching without recourse to a person, or assemble multi-document evidence in a single sitting. Eligibility workers on the state side carry their own load constraints; directions that resolve applicant friction by exporting rework to overburdened county workers shift the bottleneck rather than removing it, and are not viable as deployed systems.
+Data and integration realities close out the exploration space. The records that would let an application pre-fill or pre-validate — recent wage data, prior public-assistance enrollment, household composition — exist across federal and state systems but are not addressable through any single integration a third-party design can assume; directions premised on a unified-data API are infeasible at the deployment horizon this work is for. The post-submission silence described in the brief is itself a data-and-access reality: the state-side systems most directions would write status back through do not expose applicant-facing status channels, so any direction promising real-time transparency has to confront how that information actually travels back to the applicant.
+---
+### Rubric scoring (sharpened 11-criterion)
+1. **Strategic-vs-execution test:** Pass. Every paragraph filters direction-fit at the viability layer; no sizing/contrast/motion/copy guidance.
+2. **Applicable regulatory frameworks named:** Pass. FNS rules, Title VI; both specifically apply to SNAP intake.
+3. **Target surface declared with justification when open:** Pass. Responsive-web declared specifically; SMS marked adjacent with explicit reasoning that channel mix is itself a hypothesis.
+4. **Audience reach realities for THIS brief:** Pass. Named language, document-availability, prior-experience, and household composition as the load-bearing axes — not a default LEP/disability/older/low-bandwidth checklist applied rotely; disability is named where it filters reach, not as a floor.
+5. **Cognitive/institutional/operational realities at strategic level:** Pass. Scarcity-bandwidth mechanism cited where it directly predicts viable direction shapes; state-side worker load named as an institutional reality.
+6. **Hard data/access realities surfaced:** Pass. Unified-API infeasibility, state-side status-channel absence both named.
+7. **No execution-layer guidance:** Pass. No rendering rules.
+8. **No success criteria:** Pass.
+9. **No research narrative duplication:** Pass. Research is invoked only where it grounds a specific constraint.
+10. **Length:** Pass. Six paragraphs, each short.
+11. **Citations carry their claims:** Pass. Mullainathan-Shafir scarcity is invoked for its actual documented mechanism (cognitive bandwidth tax under financial precarity) rather than as topical decoration; FNS, Title VI, Code for America citations all carry their claims.
+**Score: 11/11 Pass, 0 Fail. Ready.**</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1511,12 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>**Target surface: mobile-web with responsive-web continuity.** The patient is encountering the design in the week after diagnosis, often on the phone they used to look up their diagnosis after the appointment; the experience needs to reach them at the kitchen counter, at the pharmacy waiting on a refill, and at the desk where they might also open it on a laptop. Native-app install friction at diagnosis week is wrong; the strategic surface is web. Whether to also explore a native or PWA-installable path past day-one is open to direction exploration.
-Regulatory frameworks that constitute hard deal-breakers. HIPAA governs any handling of the patient's PHI — glucose values, A1c results, medication lists, clinical notes — and any architecture that integrates with electronic health records or pharmacy systems requires Business Associate Agreements and HIPAA-compliant data handling. FDA Software-as-a-Medical-Device boundaries apply when the design provides clinical decision support, dosing recommendations, or glucose-trend-driven alerts: wellness and lifestyle guidance is generally outside FDA jurisdiction, while clinical-action recommendation is inside it. Directions that depend on dosing guidance or glucose-trend alerting commit the design to the SaMD regulatory pathway, which is a strategic choice, not a rendering choice.
-Audience reach realities filter which directions can reach the patients this work serves. The newly-diagnosed population spans English-proficient and limited-English-proficient patients (CDC and ADA both document language disparities in diabetes outcomes), food-insecure households where dietary advice that assumes pantry abundance is unactionable (CDC, Feeding America), patients in cultural contexts where traditional foods carry meaning beyond nutrition (USDA Dietary Guidelines and ADA both note this), and patients across an age range that skews older with associated variability in vision, motor function, and prior tech familiarity. Directions that assume one audience composition — English-fluent, food-secure, mid-life, app-fluent — are not viable for the patients whose underservice is most acute. (Rendering-level accessibility specifics live in execution work, not here.)
-Cognitive and emotional realities at the viability level. (Inferred from Sweller's Cognitive Load Theory and from peer-reviewed qualitative findings on newly-diagnosed-patient overwhelm in BMC Health Services Research and Current Diabetes Reports) diagnosis week is a high-load, high-arousal moment in which the patient cannot reliably absorb the full slate of changes the diagnosis entails. Directions that require all-at-once configuration, that ask the patient to make multiple decisions before they can begin, or that lean heavily on educational density at week one do not survive contact with the audience. (How a chosen direction renders to accommodate this lives in execution.)
-Clinical content realities. ADA Standards of Care, the 2020 ADA/ADCES DSMES Consensus Report, and CDC clinical materials are the canon clinical content must align with. Directions that depend on synthesizing or inventing clinical guidance — that put the design in the position of advising on care plans the patient's clinician has not approved — are not viable in this domain. The patient's clinical team is the system of record; directions that compete with the chart, rather than complement it, do not survive.
-Data and access realities. Many patients' EHRs are not accessible to the design at all, or are accessible only through fragmented patient-portal credentials. Directions that assume real-time EHR integration as a foundation — that depend on the design seeing the patient's labs, medication list, or clinician notes as they update — do not exist as feasible for the majority of the audience today. The data the design can rely on is the data the patient provides plus the data the patient explicitly forwards.</t>
+          <t>**Target surface: mobile-web with responsive-web continuity.** The patient meets the design on the phone they used to search their diagnosis after the appointment, at the pharmacy waiting on metformin, at the kitchen counter, sometimes at the desk where they also open it on a laptop. A native-app install at diagnosis week is the wrong commitment for a patient who is still deciding whether to tell their family.
+Two regulatory frameworks set the outer wall of what a direction can be. HIPAA governs every architecture that touches the patient's protected health information — glucose values, A1c results, the metformin prescription, anything pulled from a patient portal or pharmacy system — and a direction that depends on EHR or pharmacy integration commits to Business Associate Agreements and a covered-entity-grade data-handling posture. The FDA's Software-as-a-Medical-Device guidance is the other wall: wellness content and lifestyle support are generally outside FDA jurisdiction, while specific dosing recommendations, glucose-trend alerts, or clinical decision support are inside it. Directions that lean on dosing guidance or glucose-trend alerting are committing to a SaMD regulatory pathway — that is a strategic choice with timeline and capital consequences, not a label that gets attached at QA.
+The patient's clinical team is the system of record, and the ADA Standards of Care plus the 2020 ADA/ADCES DSMES Consensus Report are the canon any clinical content must align with. Directions that synthesize or invent clinical guidance — that put the design in the position of advising on care plans the patient's clinician has not approved — collide both with clinical evidence and with FDA scope. The strategic opening is *complementing* the chart, not competing with it; a direction that asks the patient to choose between what their CDCES said and what the app says fails on the audience-trust dimension regardless of how well it is rendered.
+Audience reach realities are diagnosis-week-specific. The newly-diagnosed Type 2 population skews into middle and later adulthood (incidence rises with age, though increasingly diagnosed earlier), and spans food-insecure households where dietary guidance assuming pantry abundance is not actionable (CDC, Feeding America), patients whose traditional foods carry meaning beyond nutrition (USDA Dietary Guidelines and ADA both note this), and limited-English-proficient patients whose diabetes outcomes are documented to diverge from English-proficient outcomes (CDC, ADA). A direction whose default audience is the English-fluent, food-secure, mid-life, app-fluent patient is narrowing away from the populations whose underservice the brief is most pointed at.
+Diagnosis week is documented as a high-overwhelm window where the patient cannot reliably absorb the full slate of changes. Peer-reviewed qualitative work in BMC Health Services Research, PLOS One, and Current Diabetes Reports catalogs the failure modes — all-at-once information loading, blame-internalization, conflicting advice across providers, dietary changes that destabilize a household economy. The 2020 ADA/ADCES Consensus Report is explicit that DSMES is the standard of care, and yet only about 6.8 percent of privately insured newly-diagnosed patients and about 5 percent of newly-diagnosed Medicare patients participate within twelve months. Directions that require all-at-once configuration at week one, that ask the patient to make multiple decisions before they can begin, or that lead with educational density rather than the emotional and procedural orientation the qualitative research describes patients actually wanting, do not survive contact with the audience the brief addresses.
+Most patients' EHRs are not accessible to the design at all, or are accessible only through fragmented patient-portal credentials that the patient must furnish individually. Directions that assume real-time EHR integration as the foundation — that depend on the design seeing labs, medication list, or clinician notes as they update — are not feasible across the majority of the audience today. The data the design can rely on is what the patient provides plus what the patient explicitly forwards from their portal, and the design has to inhabit that information landscape, not the one a fully-wired clinical integration would offer.</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1553,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>**Target surfaces: mobile-web and responsive-web.** The claimant is filing on the phone they pay for monthly, often on intermittent cellular connectivity, sometimes at a job-center computer or library terminal. Native app friction is wrong for a once-in-a-while filing flow that may be the user's first encounter with the agency. Whether the experience also inhabits SMS for status updates, or partners with phone-line workflows for claimants without smartphones, is open to direction exploration.
-Regulatory frameworks that constitute hard deal-breakers. Unemployment insurance is a federal-state partnership: federal rules (US Department of Labor UI Performs measures, related timeliness and quality requirements) impose floors the state must meet, and each state's law sets eligibility specifics (covered employment, base period definitions, weekly benefit amounts). Directions that require uniform behavior across states, or that drop state-specific eligibility logic to simplify the experience, are not viable. Identity proofing is governed by NIST Digital Identity Guidelines (SP 800-63-3 series); directions that lower the federal identity-assurance bar are non-viable. Federal Plain Writing Act of 2010 obligations and equivalent state Plain Language statutes apply to government communications. PII handling — SSNs, dates of birth, banking information, employment history — is subject to state data-breach laws and federal cloud-security frameworks (FedRAMP for federal-touching infrastructure).
-Audience reach realities filter which directions can reach the claimants this work serves. The population disproportionately includes claimants with limited English proficiency (US Census ACS language data; states with large LEP populations are required to provide meaningful language access under Title VI of the Civil Rights Act), claimants whose only device is a phone (Pew Research on smartphone-dependent internet use), claimants navigating reentry after incarceration, claimants without stable housing, and claimants whose work loss is accompanied by new disabilities or health changes. Directions that fundamentally exclude these audiences from completing the flow are not viable. (Rendering-level accessibility specifics live in execution work, not here.)
-Cognitive, emotional, and operational realities at the viability level. (Inferred from Yerkes-Dodson on arousal and performance, and from peer-reviewed work on scarcity and cognitive bandwidth — Mullainathan and Shafir, *Scarcity*, 2013) a claimant filing for unemployment is filing under acute financial stress, often with caregiving load on top, often having lost the routines that previously held their day together. Directions that require sustained attention across one long sitting, that assume the claimant can return to the right place after an interruption without scaffolding, or that gate progress on documents the claimant cannot easily produce, do not survive contact with the audience.
-Connectivity and resumability realities. The application surface must hold the claimant's progress across signal drops, device switches, and multi-day completion. Directions that depend on continuous connectivity, single-session completion, or device-locked sessions do not exist as feasible for the audience this work serves. (How an application is technically rendered to be resumable lives in execution; what's strategic here is that any direction must inhabit a multi-session, multi-device, intermittent-connectivity reality.)
-Fraud-control realities. Unemployment systems have been targeted by organized fraud at scale (US DOL Office of Inspector General reporting on pandemic-era UI fraud). The defenses against that fraud are not optional — directions that strip identity verification or document-authentication steps to streamline the user experience are not viable. The exploration is open on how the fraud controls are presented and sequenced; it is not open on whether they exist.</t>
+          <t>**Target surfaces: mobile-web and responsive-web.** The claimant is filing on the phone they pay for monthly, often on intermittent cellular at a job center or library terminal, sometimes late at night after the kids are asleep. Native-app friction is wrong for a once-in-a-while encounter with an agency the claimant may distrust. Whether SMS for status updates or a phone-line companion path also belongs in the experience is open to direction exploration.
+UI is a federal-state partnership, and the boundary itself is the controlling regulatory shape. Federal rules — US Department of Labor UI Performs measures, timeliness and quality requirements, the rights of appeal — set the floor every state must clear, while each state's law defines covered employment, the base period, the weekly benefit amount, and what counts as "able and available." A direction that papers over state variance with a uniform application flow, or that drops state-specific eligibility logic to feel simpler, fails the regulatory shape of the system it is supposedly serving. Nava's documentation of the California EDD work — most prominently the 88 percent of research participants who did not understand the EDDCAN identifier — illustrates that the path through state-specific terminology is the user's actual workload, not a translation step that can be removed.
+Three additional regulatory frameworks set the outer wall. NIST Digital Identity Guidelines (SP 800-63-3 series) set the identity-assurance bar; directions that lower it to streamline the experience are non-viable, particularly because UI systems have been targeted by organized fraud at scale (US DOL Office of Inspector General reporting on pandemic-era UI fraud). The Federal Plain Writing Act of 2010 and equivalent state plain-language statutes apply to the government communications the design produces or relays. PII handling — SSNs, dates of birth, banking information, employment histories — is subject to state data-breach law and federal infrastructure frameworks (FedRAMP for federal-touching cloud). Section 508 applies to federal-touching technology and the strategic-accessibility component of it — the affirmative obligation to procure technology that does not exclude users with disabilities from federal programs — is not an execution-layer polish; a direction that fundamentally excludes disabled claimants from the federal benefit fails the procurement standard before it fails any rendering rule.
+Audience reach is shaped by who actually loses jobs. The claimant population disproportionately includes claimants with limited English proficiency in states required by Title VI to provide meaningful language access, smartphone-dependent claimants whose only internet access is the phone they're filing on (Pew Research on smartphone-dependent internet use), claimants reentering after incarceration whose work histories include gaps that the form's base-period logic does not represent well, claimants in variable-schedule work where the form's "precise dates and hours" requirement collides with how the work actually happened, ACP-eligible claimants whose address-confidentiality may be active, and claimants whose job loss is concurrent with a new disability. A direction whose default audience is the salaried W-2 claimant with a desktop and a saved pay-stub PDF is narrowing away from the population that most needs the benefit to land.
+Scarcity is the operational reality this user is filing under. The claimant is filing under acute financial stress — Mullainathan and Shafir's *Scarcity* (2013) documents the bandwidth tax that scarcity imposes on planning, follow-through, and absorption of procedural detail; the relevant mechanism here is that the cognitive bandwidth required to navigate a complex multi-document flow is exactly the bandwidth the claimant's situation is consuming. Directions that require sustained attention across one long sitting, that assume the claimant can return to the right place after an interruption without scaffolding, or that gate progress on documents the claimant cannot easily produce, do not survive contact with the audience.
+Connectivity and resumability are the data-and-access reality. The application has to hold progress across signal drops on the train, across device switches between the job-center desktop and the phone on the way home, across multi-day completion bracketed by caregiving and sleep. Directions that depend on continuous connectivity, single-session completion, or device-locked sessions do not exist as feasible. Post-submission, the claim-status reality is the second pain point and the most damaging part of the experience: paper letters arriving weeks late, portals showing stale information, phone lines with multi-hour holds. Money does not arrive on a schedule the claimant can plan around. Directions whose status-communication model assumes a working interagency status feed depend on infrastructure that varies state by state and that, where it exists, is often opaque to the claimant.</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1595,12 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>**Target surface: responsive-web.** The voter is encountering this task in the middle of the bureaucratic cascade that follows a name change — at a desk filling out the DMV form, on a phone between calls to Social Security, at the kitchen table sorting through mail. Native-app install friction is wrong for a once-or-twice-in-a-lifetime task; whether the experience also inhabits SMS for reminders, or partners with adjacent civic services (vote.org, TurboVote / Democracy Works), is open to direction exploration.
-Regulatory frameworks that constitute hard deal-breakers. The National Voter Registration Act of 1993 sets federal baselines for voter registration in most states; the Help America Vote Act of 2002 sets identification and provisional-ballot requirements; the Voting Rights Act prohibits discriminatory administration of the franchise. Each state's election code, administered by the Secretary of State or equivalent, sets the specific rules for what counts as a valid registration update, what documentation is accepted, and what the deadlines are. Some states require court orders for certain name changes; some accept marriage or divorce decrees; some require in-person updates; some allow online; some require re-registration entirely. Voter registration data is protected under state voter-registration confidentiality laws (which vary substantially); some states publish voter rolls and some do not. Directions that require uniform behavior across states, or that ignore federal-state regulatory boundaries, are not viable.
-Audience reach realities filter which directions can reach the voters this work serves. The population disproportionately includes voters with limited English proficiency (Title VI of the Civil Rights Act, plus state-level language-access rules in jurisdictions covered by Section 203 of the VRA), voters in low-income households whose internet access is mobile-only or intermittent (Pew Research on smartphone-dependent internet use), voters in inconsistent housing situations whose address may not be stable across the registration window, trans voters whose prior name and current identity documents may not align, and survivors of domestic violence enrolled in state address-confidentiality programs. Directions that fundamentally exclude any of these audiences are not viable. (Rendering-level accessibility specifics live in execution work, not here.)
-Information-integrity realities. Civic-tech operates in an adversarial information environment in which inaccurate guidance has direct election-day consequences. (Brennan Center reporting on election administration; Pew Research on voter roll accuracy) directions that rely on freshness of state-by-state procedural information without an explicit pathway to keeping that information current — that depend on a one-time content build — are not viable, because state rules change between cycles. The design must hold an authoritative-information posture against a backdrop where misinformation about voter eligibility is a documented adversarial pattern.
-Cognitive and operational realities at the viability level. (Inferred from established cognitive-load and decision-cost research, e.g., Sweller's Cognitive Load Theory; and from the documented pattern of registration updates being deferred past the deadline because they sit inside a long bureaucratic to-do list) the registration update arrives at the voter in a state of decision-fatigue, after they have already made dozens of name-change decisions for documents that have more immediate consequences. Directions that compete for the voter's full attention as if the voter has nothing else to do, or that require the voter to absorb procedural detail before they can begin, do not survive contact with the moment.
-Data and access realities. Most states do not expose machine-readable APIs that confirm a voter's registration record in real time; what the state surfaces publicly varies by jurisdiction. Directions that depend on real-time per-state registration-status lookups as a foundation are not feasible across the audience; the data the design can rely on is what the voter provides plus what state portals expose in their varying forms.</t>
+          <t>**Target surface: responsive-web.** The voter encounters this task in the middle of the bureaucratic cascade a name change triggers — at a desk filling out the DMV form, on a phone between calls to Social Security, at the kitchen table sorting mail. Native-app install friction is wrong for a once-or-twice-in-a-lifetime task. Whether the experience also inhabits SMS for deadline reminders, or partners with adjacent civic services (TurboVote/Democracy Works, vote.org), is open to direction exploration.
+Fifty state election codes, sitting on a federal floor, are the controlling regulatory shape. The National Voter Registration Act of 1993 and the Help America Vote Act of 2002 set federal baselines; the Voting Rights Act prohibits discriminatory administration of the franchise. Each state's election code, administered by the Secretary of State or equivalent, defines what counts as a valid name update for the voter roll, what documentation is accepted, what the deadlines are, and which channels the update can travel through. Some states accept any government-issued ID showing the new name; some require a court order; some accept a marriage or divorce decree specifically; some require in-person updates; some allow online; some require full re-registration. A direction that smooths the variance away — that produces a single national flow that asserts what the rule is rather than what the rule is *in this state for this name-change reason* — produces inaccurate civic guidance, which in this domain is the failure mode with election-day consequences.
+State voter-registration confidentiality law is the second regulatory layer, and it sits exactly where audience reach lands for two of this brief's audiences. Some states publish voter rolls and some do not; some states maintain Address Confidentiality Programs (ACPs) for survivors of domestic violence, stalking, and sexual assault. A direction that pulls registration records from public rolls without modeling ACP enrollment, or that surfaces prior-name information in a way that out-of-context exposes a voter's name-change history, is not a privacy bug to fix after launch — it is a structural risk to the DV-survivor and trans voters in the audience the brief names. Title VI of the Civil Rights Act and Section 203 of the VRA add a language-access regulatory layer in covered jurisdictions; a direction whose state coverage assumes English-only is non-viable in those jurisdictions.
+The audience composition this brief specifies is what filters reach. The voter is mid-life-transition (post-marriage, post-divorce, post-gender-transition, post-personal-choice change), which means the audience includes trans voters whose prior-name documents and current-identity documents may not align and for whom Voter ID laws layer additional friction, DV survivors enrolled in ACPs whose registration records are not publicly listed by design, voters in inconsistent housing whose address may not be stable across the registration window, smartphone-only voters whose internet access is mobile (Pew Research on smartphone-dependent internet use), and LEP voters in jurisdictions where Title VI and VRA Section 203 require meaningful language access. A direction whose default audience is the post-marriage middle-class voter with a stable address and an English-only flow is narrowing away from the audiences the brief explicitly addresses.
+The information-integrity posture is the strategic risk that distinguishes civic-tech from adjacent domains. Brennan Center reporting on election administration and Pew Research on voter-roll accuracy document an environment in which inaccurate guidance about registration has direct election-day consequences, and in which misinformation about voter eligibility is a documented adversarial pattern. A direction that ships state-by-state procedural content as a one-time build, without an ongoing pathway to keep it current as state rules change between cycles, fails on a maintenance posture that is operationally what holds the content honest — and a direction that depends on community-edited or unsourced procedural information is depending on something that does not survive the adversarial information environment around US elections.
+The data-and-access landscape is thin. Most states do not expose machine-readable APIs that confirm a voter's registration record in real time; what each state surfaces publicly varies by jurisdiction, and the registration update itself, once submitted, often disappears from the voter's view until a confirmation card arrives in the mail. The bureaucratic-cascade reality (Inferred from TurboVote's documented patterns and the Brennan Center analyses) is that the voter-registration update arrives at the voter after they have already made many name-change decisions for documents with more immediate consequence — driver's license, Social Security, employer records, banking — so the design has to inhabit a moment where the voter is not arriving fresh and is not arriving urgent. Directions that compete for the voter's full attention as if voter registration were the central errand of the day do not survive that reality.</t>
         </is>
       </c>
     </row>

--- a/experiments/corpus-content.xlsx
+++ b/experiments/corpus-content.xlsx
@@ -503,9 +503,10 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t># Apartment search for a renter with a past eviction — design exploration
-A person with an eviction record is looking for a new place to live. The eviction may have been after a job loss, a medical event, a dispute with a prior landlord — sometimes a dismissed filing, sometimes a filing-in-error, sometimes a completed eviction-for-cause. The renter has since rebuilt; they have a job, references, money for a deposit. None of that reaches the landlord. What reaches the landlord is a tenant-screening report — bundling rental, credit, employment, and criminal history into a score or a recommendation — on which the eviction filing looks the same whether the case was won, lost, or dismissed.
-The renter pays application fees at every listing they apply to and discovers, sometimes days later, that they have been declined. They get back a vague "did not meet screening criteria" or no explanation at all. They have no clear path to find out which factor on the report produced the decline, no clear path to contest a record they believe is inaccurate, no time to keep applying — they need to be housed in the weeks they have, not the months a dispute would take. What they confront in the landscape today is the rental-listing aggregators that take applications, the screening companies whose reports they cannot see, the consumer-bureau dispute processes that move slowly, and the legal-aid organizations whose capacity does not meet the volume of renters in this situation.
-The scope is the apartment search journey from "I'm looking" through "I've signed a lease." We want strategic directions that center the renter.</t>
+**Situation.** A person with an eviction record is looking for a new place to live. The eviction may have followed a job loss, a medical event, or a dispute with a prior landlord — sometimes a dismissed filing, sometimes a filing-in-error, sometimes a completed eviction-for-cause. The renter has since rebuilt: a job, references, money for a deposit. What reaches the landlord is a tenant-screening report — bundling rental, credit, employment, and criminal history into a score — on which the filing looks the same whether the case was won, lost, or dismissed.
+**Complication.** The renter pays application fees at every listing and discovers, sometimes days later, that they have been declined. They get back a vague "did not meet screening criteria" or no explanation at all. There is no path to find out which factor produced the decline, no path to contest a record they believe is inaccurate. They confront listing aggregators, screening companies whose reports they cannot see, bureau disputes that move slowly, and legal-aid offices whose capacity does not meet the volume.
+**Users.** The renter with the eviction record on their file. Landlords and screening companies are stakeholders, not the target — the design is for the renter with weeks, not months, and a stack of declined applications. Scope is "I'm looking" through "I've signed a lease."
+**Cost.** They need to be housed in the weeks they have, not the months a dispute would take. Fees stack up against a deposit they are trying to keep intact. Each decline arrives without enough information to act on, and the next listing goes up against the same report. The current housing is running out or already gone.</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -561,9 +562,10 @@
       <c r="B3" s="3" t="inlineStr">
         <is>
           <t># Coordinating care for an aging parent — design exploration
-An adult child is responsible for the day-to-day care of an aging parent. They live in a different city. They are working full-time, may be raising their own kids, and now are also managing their parent's medications, appointments, insurance disputes, in-home aide schedule, finances, and the longer-term decisions about home modifications, assisted living, or hospice. They are doing this with sibling involvement that ranges from supportive to fractious.
-The information lives everywhere — their own phone, their email, the parent's hand-written notes on a yellow pad by the kitchen phone, the parent's doctor's portals (one per doctor, often three or four with different logins), Medicare statements, the in-home aide's notebook, the pharmacy's text messages. No system holds the picture; the caregiver holds the picture, in their head, between work meetings and bedtime. The new prescription started last Thursday is supposed to be checked against the cardiologist's older prescription that may or may not have been discontinued. The PCP's portal does not show the cardiologist's prescriptions. The aide's notebook is in the parent's apartment, three hundred miles away. When something goes wrong — a missed medication, a duplicate dose, an ED visit that looks preventable in hindsight — the gap was between systems the caregiver was supposed to bridge across.
-The scope is the ongoing work of coordinating — not a single appointment but the rhythm of a month.</t>
+**Situation.** An adult child is responsible for the day-to-day care of an aging parent in another city. They are working full-time, may be raising their own kids, and are now also managing their parent's medications, appointments, insurance disputes, in-home aide schedule, finances, and longer-term decisions about home modifications, assisted living, or hospice — with sibling involvement that ranges from supportive to fractious.
+**Complication.** The information lives everywhere — their own phone, their email, the parent's hand-written notes on a yellow pad by the kitchen phone, the parent's doctor's portals (three or four, each with its own login), Medicare statements, the aide's notebook, the pharmacy's text messages. No system holds the picture; the caregiver holds it, in their head, between work meetings and bedtime. The new prescription started last Thursday is supposed to be checked against the cardiologist's older one that may or may not have been discontinued. The PCP's portal does not show the cardiologist's prescriptions. The aide's notebook is three hundred miles away.
+**Users.** The adult-child caregiver and the aging parent, as a dyad — the parent in their own apartment, the caregiver coordinating from three hundred miles away. Siblings, aides, doctors, and pharmacists are stakeholders the design accommodates, not optimizes for. Scope is the rhythm of a month, not a single appointment.
+**Cost.** When something goes wrong — a missed medication, a duplicate dose, an ED visit that looks preventable in hindsight — the gap was between systems the caregiver was supposed to bridge across. The parent absorbs the errors when the picture slips. The work eats evenings, weekends, and the bandwidth left for everything else in the caregiver's life.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -619,9 +621,10 @@
       <c r="B4" s="3" t="inlineStr">
         <is>
           <t># An adult learner re-entering community college — design exploration
-An adult — twenty-five, thirty-five, fifty — has enrolled at community college, often after years away from formal schooling. They've decided to re-enroll for a new credential, an industry switch, or developmental coursework before a four-year transfer. They've signed up; they haven't started.
-They are trying to read a college website built for eighteen-year-olds applying for fall. They are unsure where to park, what to bring to orientation, whether the FAFSA they filled out applies to summer term, whether they can register part-time without losing the financial-aid bracket, and how to reach an advisor who answers in less than two weeks. They have a job that won't easily flex, kids who need pick-up, and the cognitive disjuncture of being asked to think like a student again after years of not being one. The first month is where they either build a workable rhythm or quietly stop coming.
-The scope is the eight-week window from "I've enrolled" through "I've completed the first month of classes."</t>
+**Situation.** An adult — twenty-five, thirty-five, fifty — has enrolled at community college, often after years away from formal schooling. They've decided to re-enroll for a new credential, an industry switch, or developmental coursework before a four-year transfer. They've signed up; they haven't started. They have a job that won't easily flex, kids who need pick-up, and the cognitive disjuncture of being asked to think like a student again after years of not being one.
+**Complication.** They are trying to read a college website built for eighteen-year-olds applying for fall. They are unsure where to park, what to bring to orientation, whether the FAFSA they filled out applies to summer term, whether they can register part-time without losing the financial-aid bracket, and how to reach an advisor who answers in less than two weeks.
+**Users.** The adult learner re-entering community college after years away — not the eighteen-year-old applying for fall, and not the returner with a working campus rhythm. Advisors, financial-aid officers, and registrars are stakeholders the design encounters, not optimizes for. Scope is the eight-week window from "I've enrolled" through "I've completed the first month of classes."
+**Cost.** The first month is where the workable rhythm either gets built or doesn't. When the answers don't arrive in the window — when orientation feels alien, when the FAFSA question goes two weeks without a reply, when the parking and pick-up logistics don't line up — the learner quietly stops coming. The enrollment becomes another unfinished credential, the tuition becomes a sunk cost, and the next attempt is years out.</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -676,9 +679,10 @@
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t># Disputing a credit-report error — design exploration
-A person has been denied an apartment, a job, a loan, or an insurance rate because of something on their credit report — and the something is wrong. A debt they paid years ago. An account opened in their name fraudulently. Identity confusion with a relative who shares their name. They have proof — receipts, closure letters, identity-theft affidavits — and no clear path to get it to the right place.
-They face three different dispute interfaces, one per bureau, each demanding documentation in slightly different formats and each capable of returning a one-line "investigated, no change" weeks later. They are unsure whether to write a paper letter, use the online portals, file directly with the furnisher (their old creditor, the collections agency), file a complaint with the CFPB, or do all four. The process unfolds over thirty to ninety days while the apartment application sits in limbo and the new job offer is on hold. In many cases the original error reappears later from a different furnisher, and the consumer is back where they started, looking at the same three logins, the same documentation queue, the same wait. What they confront in the landscape is the bureaus' own dispute portals, free-credit-report sites that funnel toward paid monitoring, the CFPB consumer-complaint channel, the FTC's IdentityTheft.gov for fraud cases, and the patchwork of state attorney general offices and legal-aid organizations whose capacity does not meet the volume of consumers in this situation.
-The scope is from the moment someone notices an error through the resolution of the dispute.</t>
+**Situation.** A person has been denied an apartment, a job, a loan, or an insurance rate because of something on their credit report — and the something is wrong. A debt they paid years ago. An account opened in their name fraudulently. Identity confusion with a relative who shares their name. They have proof — receipts, closure letters, identity-theft affidavits — and no clear path to get it to the right place.
+**Complication.** They face three different dispute interfaces, one per bureau, each demanding documentation in slightly different formats and each capable of returning a one-line "investigated, no change" weeks later. They are unsure whether to write a paper letter, use the online portals, file directly with the furnisher, file a CFPB complaint, or do all four. The original error often reappears later from a different furnisher, and the consumer is back at the same three logins, the same documentation queue, the same wait. They confront the bureaus' portals, free-credit-report sites that funnel toward paid monitoring, the CFPB channel, IdentityTheft.gov, and legal-aid whose capacity does not meet the volume.
+**Users.** The consumer disputing the error — the one with receipts and closure letters in hand. Bureaus, furnishers, and CFPB intake staff are stakeholders, not the target. Scope is from noticing the error through resolution.
+**Cost.** The process unfolds over thirty to ninety days while the apartment application sits in limbo and the new job offer is on hold. The denial that prompted the dispute does not pause for resolution. When the error reappears from a different furnisher, the consumer is back at the same three logins, doing the work again on a life that has moved on.</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -733,9 +737,10 @@
       <c r="B6" s="3" t="inlineStr">
         <is>
           <t># First contact with 988, the crisis line — design exploration
-Someone is reaching out to the US crisis line — 988 — for the first time. They may be experiencing a suicidal crisis, an acute panic episode, a substance-use crisis, or distress around grief, abuse, or identity. They may be the person in crisis, or a friend or family member trying to help someone else. They are reaching out at a moment of acute vulnerability and they have a choice to make about whether to stay on the line.
-The first sixty seconds are determinative. What does this look like; will I be judged; what's about to happen; will police be sent to my address if I say the wrong thing. People who have heard from someone that police might be dispatched are hesitant in ways the system has to meet; people who have never reached out before are calibrating from the screen, the voice, the hold music. The decision to keep reaching, or to hang up and not try again, is being made before anyone has actually said anything.
-The scope is the first contact — call, text, or chat opening — plus the immediate next-step pathway. The crisis-counselor protocol itself is out of scope.</t>
+**Situation.** Someone is reaching out to the US crisis line — 988 — for the first time. They may be experiencing a suicidal crisis, an acute panic episode, a substance-use crisis, or distress around grief, abuse, or identity. They may be the person in crisis, or a friend or family member trying to help someone else. They are reaching out at a moment of acute vulnerability and have a choice to make about whether to stay on the line.
+**Complication.** The first sixty seconds are determinative. What does this look like; will I be judged; what's about to happen; will police be sent to my address if I say the wrong thing. People who have heard that police might be dispatched are hesitant in ways the system has to meet; people who have never reached out before are calibrating from the screen, the voice, the hold music. The decision to keep reaching, or to hang up and not try again, is made before anyone has said anything.
+**Users.** The first-time reacher — the person in crisis, or the friend or family member calling on their behalf — in the opening seconds before a counselor has spoken. Counselors and dispatchers are stakeholders the design hands off to, not optimizes for. Scope is the call, text, or chat opening plus the immediate next step; the counselor protocol itself is out of scope.
+**Cost.** When the first sixty seconds don't hold, the person hangs up and does not try again. The next acute moment arrives without a line they trust. The friend who was calling for someone else goes back with nothing to offer.</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -789,9 +794,10 @@
       <c r="B7" s="3" t="inlineStr">
         <is>
           <t># Closing a deceased family member's accounts — design exploration
-When a person dies, someone in the family inherits an administrative ordeal nobody trained them for. They are the executor or personal representative — spouse, adult child, sibling — and they now need to identify, contact, and close out dozens of accounts: banks, credit cards, utilities, mortgages, retirement accounts, insurance, Social Security, and a digital life of email and photos and subscriptions. Each institution has its own forms, its own definitions, its own staff. Debt collectors begin calling within days; most are wrong about what the survivor owes, but the conversations are intimidating and the rules vary by state.
-The user is grieving. They are the executor because someone had to be. They are doing this work in the evenings, between work meetings, between the funeral and the rest of life — often from a different city than the deceased, with a death certificate in hand and a stack of unopened mail. The process unfolds over months. The available resources are accurate and encyclopedic; they list eighty things this executor might need to do, with no way to know which twelve apply today.
-The scope is the full work of closing accounts and settling the estate — first week after death through final dissolution months later. We want strategic directions that take both the grief and the bureaucracy seriously.</t>
+**Situation.** When a person dies, someone in the family inherits an administrative ordeal nobody trained them for. They are the executor — spouse, adult child, sibling — and now need to identify, contact, and close out dozens of accounts: banks, credit cards, utilities, mortgages, retirement accounts, insurance, Social Security, and a digital life of email and photos and subscriptions. They are doing this in the evenings, between the funeral and the rest of life — often from a different city than the deceased, with a death certificate in hand and a stack of unopened mail.
+**Complication.** Each institution has its own forms, its own definitions, its own staff. Debt collectors begin calling within days; most are wrong about what the survivor owes, but the conversations are intimidating and the rules vary by state. The available resources are accurate and encyclopedic; they list eighty things the executor might need to do, with no way to know which twelve apply today.
+**Users.** The executor — spouse, adult child, or sibling — grieving and doing this because someone had to be. Institutions and debt collectors are stakeholders, not the design's target. Scope is from the first week through final dissolution.
+**Cost.** The work runs in the evenings on top of grief, on top of a job, on top of a household that did not pause. The encyclopedic list does not tell the executor which twelve of eighty steps belong to today, so the wrong ones get done first or none at all. The collectors' calls keep coming. The estate stays open, the mail keeps arriving, and the grief is interrupted every time the ordeal reasserts itself.</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -845,9 +851,10 @@
       <c r="B8" s="3" t="inlineStr">
         <is>
           <t># Driver's license transfer after a cross-state move — design exploration
-A person has moved from one US state to another. They have a job to start, an apartment to unpack, a kid in a new school. Somewhere on the list is "transfer the driver's license," and the new state's DMV site is a tangle of pages that don't quite match the user's situation: out-of-state transfer vs new resident vs non-citizen vs recently-licensed teen. They have a stack of documents — birth certificate, Social Security card, lease, utility bill, old license, marriage certificate — and aren't sure which the office will accept on the day. They want to know when to go, what to bring, what the visit will feel like, and what happens if something goes wrong. The DMV won't tell them ahead of time.
-The mover does the visit, leaves with a temporary paper printout, and waits weeks for the hard copy in the mail. In the meantime they aren't sure whether the paper is enough to fly, open a bank account, or pass any other ID check. The cost of getting any of this wrong is another visit, another day of work missed, and the same lack of information about what's next.
-The scope is the four-to-six-week window after a move during which the license needs to transfer.</t>
+**Situation.** A person has moved from one US state to another. They have a job to start, an apartment to unpack, a kid in a new school. Somewhere on the list is "transfer the driver's license," and the new state's DMV site is a tangle of pages that don't quite match the user's situation: out-of-state transfer vs new resident vs non-citizen vs recently-licensed teen. They have a stack of documents — birth certificate, Social Security card, lease, utility bill, old license, marriage certificate.
+**Complication.** They aren't sure which documents the office will accept on the day. They want to know when to go, what to bring, what the visit will feel like, and what happens if something goes wrong. The DMV won't tell them ahead of time. The mover does the visit, leaves with a temporary paper printout, and waits weeks for the hard copy in the mail. In the meantime they aren't sure whether the paper is enough to fly, open a bank account, or pass any other ID check.
+**Users.** A recent mover in the four-to-six-week window after a cross-state move, navigating the new state's DMV alone with a folder of documents and other life on fire.
+**Cost.** Getting any of this wrong costs another visit, another day of work missed, and the same lack of information about what's next. The scope is the four-to-six-week window after a move during which the license needs to transfer.</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -900,9 +907,10 @@
       <c r="B9" s="3" t="inlineStr">
         <is>
           <t># A first-time manager's first performance review — design exploration
-Someone who has been a people manager for less than a year sits down at midnight to write their first performance review of an employee. They have nine weeks of notes — most of them mental — and a template HR handed down with fifteen sections and a five-point rating scale. The person they are reviewing might be a former peer, someone they hired, or someone with more years in the industry than they have. They are alone with a form and a blinking cursor.
-They are scared of doing harm. Of giving feedback that lands wrong. Of being too soft and ducking the real issue. Of being too critical and damaging a working relationship. They are also navigating a calibration cycle in which their ratings will be compared against peer managers' ratings, with rules they only half-understand. The performance-management software they're using delivers prompts and templates but does not actually help them think through what to say to this specific person about this specific thing — and the cost of getting it wrong is paid both at the next 1:1 and across the year that follows.
-The scope is the act of writing the review — the hours between *I have to write this* and *I have a draft I'd send.*</t>
+**Situation.** Someone who has been a people manager for less than a year sits down at midnight to write their first performance review of an employee. They have nine weeks of notes — most of them mental — and a template HR handed down with fifteen sections and a five-point rating scale. They are also navigating a calibration cycle in which their ratings will be compared against peer managers' ratings, with rules they only half-understand.
+**Complication.** The performance-management software they're using delivers prompts and templates but does not actually help them think through what to say to this specific person about this specific thing. They are scared of doing harm. Of giving feedback that lands wrong. Of being too soft and ducking the real issue. Of being too critical and damaging a working relationship. They are alone with a form and a blinking cursor.
+**Users.** A first-time people manager writing their first review of a direct report — who might be a former peer, someone they hired, or someone with more years in the industry than they have. HR and the calibration committee are stakeholders the manager has to satisfy, but the design is for the manager in the moment of writing.
+**Cost.** The cost of getting this wrong is paid both at the next 1:1 and across the year that follows — a damaged working relationship, a real issue ducked, or feedback that lands so wrong it forecloses growth. The scope is the act of writing the review — the hours between *I have to write this* and *I have a draft I'd send.*</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -956,9 +964,10 @@
       <c r="B10" s="3" t="inlineStr">
         <is>
           <t># A grief-focused web app — design exploration
-We're scoping a web product for people in active grief. The space today splits roughly three ways: funeral logistics sites (transactional, mostly pre-funeral), peer support communities and subreddits (exposing or noisy for many), and journaling apps that bolt on a "feeling sad" mood tag (toothless). The users we keep hearing from describe wanting something different — something that respects them as someone grieving rather than treating them as a user to be moved through a funnel or a feed.
-Audience is anyone weeks-to-months out from a meaningful loss — recent enough that grief is shaping their day, not so recent that they're still in funeral logistics. The losses themselves vary widely: parent, partner, friend, pregnancy, pet, anticipatory loss with a terminal diagnosis. The support systems around people vary even more — some surrounded by attentive friends, others whose network has gone quiet at six weeks. People reach for a tool at the awkward moments: 3am, the anniversary, after a hard conversation with a sibling about settling the estate, on a Tuesday for no specific reason. At those moments, the funeral sites read transactional, the subreddits feel either welcoming or hostile depending on luck, and the mood-tag prompt asks "how are you feeling today?" as if grief were a state to log. Existing tools fail them either by being too prescriptive ("step 4 of 7: write a letter to your loved one") or too generic. The cost of failure isn't dramatic — it's the slow drift away from a tool that doesn't meet them, and the continued absence of a place that does.
-What we want from this round: distinct strategic directions for what "a web app for grief" could meaningfully be — real bets that could move the category, not convergent variants of the same idea.</t>
+**Situation.** We're scoping a web product for people in active grief. The space today splits roughly three ways: funeral logistics sites (transactional, mostly pre-funeral), peer support communities and subreddits (exposing or noisy for many), and journaling apps that bolt on a "feeling sad" mood tag (toothless). The users we keep hearing from describe wanting something different — something that respects them as someone grieving rather than treating them as a user to be moved through a funnel or a feed.
+**Complication.** People reach for a tool at the awkward moments: 3am, the anniversary, after a hard conversation with a sibling about settling the estate, on a Tuesday for no specific reason. At those moments, the funeral sites read transactional, the subreddits feel either welcoming or hostile depending on luck, and the mood-tag prompt asks "how are you feeling today?" as if grief were a state to log. Existing tools fail them by being too prescriptive ("step 4 of 7: write a letter to your loved one") or too generic.
+**Users.** Anyone weeks-to-months out from a meaningful loss — recent enough that grief is shaping the day, not so recent that they're still in funeral logistics. The losses vary: parent, partner, friend, pregnancy, pet, anticipatory loss with a terminal diagnosis. The support systems around them vary more — some surrounded by attentive friends, others whose network has gone quiet at six weeks.
+**Cost.** The cost of failure isn't dramatic — it's the slow drift away from a tool that doesn't meet them, and the continued absence of a place that does. What we want from this round: distinct strategic directions for what "a web app for grief" could meaningfully be — real bets that could move the category, not convergent variants.</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1013,9 +1022,10 @@
       <c r="B11" s="3" t="inlineStr">
         <is>
           <t># Discharge instructions for older adults going home — design exploration
-An older adult is being discharged from the hospital this afternoon after a heart-failure exacerbation, a stroke, a fall, or pneumonia. A family caregiver — often an adult child who has travelled in — will run the first week or two at home. The nurse has roughly fifteen minutes to walk through six pages of paperwork before the next admission needs the room. The patient is in pain, on medications that affect cognition, exhausted and emotionally activated; what they remember of those fifteen minutes once they get home is fragmentary. The caregiver who will actually administer the next thirty days is sometimes in the room and sometimes not.
-At home a few days later, the patient is trying to figure out which white pill is the new beta-blocker and which is the one they were already taking, what "weigh yourself daily and call if you gain more than three pounds in a week" actually means in practice, whether the swelling in their ankle today counts as a warning sign, and what the printed phone number is for if they call after hours. The discharge instructions are face-down on the kitchen table next to the medication bottles. The follow-up appointment is in eleven days. Between now and then it is the patient and the caregiver and the paperwork.
-The scope is the discharge moment plus the first 7–14 days at home. The clinical care plan itself is out of scope; we are looking at the transition, not the medicine.</t>
+**Situation.** An older adult is being discharged from the hospital this afternoon after a heart-failure exacerbation, a stroke, a fall, or pneumonia. A family caregiver — often an adult child who has travelled in — will run the first week or two at home. The nurse has roughly fifteen minutes to walk through six pages of paperwork before the next admission needs the room.
+**Complication.** The patient is in pain, on medications that affect cognition, exhausted and emotionally activated; what they remember of those fifteen minutes once home is fragmentary. The caregiver who will administer the next thirty days is sometimes in the room and sometimes not. A few days later, the patient is trying to figure out which white pill is the new beta-blocker, what "weigh yourself daily and call if you gain more than three pounds in a week" means in practice, whether today's ankle swelling is a warning sign, and what the printed phone number is for after hours. The discharge papers are face-down on the kitchen table next to the medication bottles. The follow-up is in eleven days.
+**Users.** The dyad post-discharge: the older adult patient recovering at home, and the family caregiver — often an adult child — running the first week or two of medications, warning signs, and follow-up logistics. The discharging nurse and follow-up clinic are stakeholders the design accommodates; the design is for the dyad once paperwork has come home.
+**Cost.** Between now and the follow-up, it is the patient and the caregiver and the paperwork. The cost of getting it wrong is a missed warning sign, a doubled medication, a readmission. Scope is the discharge moment plus the first 7–14 days at home; the clinical care plan is out of scope.</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1072,9 +1082,10 @@
       <c r="B12" s="3" t="inlineStr">
         <is>
           <t># Self-representation in housing court — design exploration
-A tenant has received an eviction notice. Their landlord has filed in housing court. They have a court date in two to three weeks. They cannot afford an attorney; the legal-aid clinic in their county is at capacity. The available self-help resources are accurate, thorough, and unusable in their situation: long PDFs of legalese for someone who is working two jobs and putting kids to bed at the same time.
-The tenant may or may not have a legal defense. The landlord may not have given proper notice; the rent claim may be wrong; the unit may be uninhabitable; the landlord may have engaged in unlawful self-help. Or the tenant may not have a defense and needs to negotiate time, settle, or simply file an answer to preserve options. They have a stack of papers in three different formats, a phone, and an internet connection. They cannot tell which of the eighty pieces of available advice apply to their facts and which don't.
-The scope is from "I got a notice" through "I have prepared for court." What they need is to walk into court understanding what is about to happen and what they should say.</t>
+**Situation.** A tenant has received an eviction notice. Their landlord has filed in housing court. They have a court date in two to three weeks. They cannot afford an attorney; the legal-aid clinic in their county is at capacity. The available self-help resources are accurate, thorough, and unusable in their situation: long PDFs of legalese for someone who is working two jobs and putting kids to bed at the same time.
+**Complication.** The tenant may or may not have a legal defense. The landlord may not have given proper notice; the rent claim may be wrong; the unit may be uninhabitable; the landlord may have engaged in unlawful self-help. Or the tenant may not have a defense and needs to negotiate time, settle, or simply file an answer to preserve options. They have a stack of papers in three different formats, a phone, and an internet connection. They cannot tell which of the eighty pieces of available advice apply to their facts and which don't.
+**Users.** A pro-se tenant facing an eviction filing with a court date two to three weeks out, navigating the case alone. Legal-aid attorneys, court clerks, and the landlord's counsel are stakeholders the tenant encounters; the design is for the tenant doing the work between notice and hearing.
+**Cost.** What they need is to walk into court understanding what is about to happen and what they should say. The cost of falling short is a default judgment, a lost home, and a record that follows them to the next lease application. The scope is from "I got a notice" through "I have prepared for court."</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1129,9 +1140,10 @@
       <c r="B13" s="3" t="inlineStr">
         <is>
           <t># Multi-currency expense report submission — design exploration
-A traveler is home for two days between business trips. They need to submit an expense report from the trip that just ended — three countries, receipts in five formats, photos of meals in a foreign language, an airline charge that hit their card in USD but was billed in EUR, a hotel charge pre-authorized at one amount and posted at another, an Uber auto-uploaded but mis-categorized as personal, a cash tip paid because the card terminal was broken. They have policy questions — was the upgraded flight reimbursable, what counts as a client meal — and no one to ask quickly.
-They submit. Finance rejects it for a single category mismatch and asks them to redo. Each round of back-and-forth is another evening they don't have. The available tools — Concur, Ramp, Brex, Emburse — each present their own version of categorization screens, FX-rate prompts, and approval flows, all built around finance-side review queues and policy enforcement. The traveler does the work because they have to, not because the tool helps. The finance team, on the other side, is working from the same submission and frequently sending it back; the gap between what the traveler can produce on a Saturday afternoon and what finance needs to approve is where the loop lives.
-The scope is from the moment a trip ends to the moment the report is approved. The traveler is leaving for São Paulo on Sunday.</t>
+**Situation.** A traveler is home for two days between business trips. The trip that just ended ran through three countries, with receipts in five formats, photos of meals in a foreign language, an airline charge that hit their card in USD but was billed in EUR, a hotel charge pre-authorized at one amount and posted at another, an Uber auto-uploaded but mis-categorized as personal, and a cash tip paid because the card terminal was broken. They have policy questions — was the upgraded flight reimbursable, what counts as a client meal — and no one to ask quickly.
+**Complication.** They submit. Finance rejects it for a single category mismatch and asks them to redo. Each round of back-and-forth is another evening they don't have. The available expense tools present categorization screens, FX-rate prompts, and approval flows; the gap between what the traveler can produce on a Saturday afternoon and what finance needs to approve is where the loop lives.
+**Users.** The business traveler reconciling between trips — competent, time-starved, working from a kitchen table with a phone full of receipts. The finance reviewer reads what was submitted and often sends it back; they are a stakeholder, not the target.
+**Cost.** Evenings lost to resubmissions, the next trip approaching with last trip's report still open, reimbursements that lag for weeks, and the slow erosion of any sense that this part of the job is tractable. The traveler is leaving for São Paulo on Sunday. The scope is from the moment a trip ends to the moment the report is approved.</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1187,9 +1199,10 @@
       <c r="B14" s="3" t="inlineStr">
         <is>
           <t># A parent finding tutoring for a child struggling in math — design exploration
-A parent has a child in 4th, 6th, or 8th grade who is struggling in math. The grades have slipped; the teacher has sent a note; the standardized test result came back lower than expected. The parent has a few hours over the next two weeks to set something up.
-They are facing a tangle of options: the local tutoring chain (predictable but expensive, small-group, weekly); a private tutor matched through a friend (variable quality and availability); online services (Wyzant, Varsity Tutors, Khan Academy + Schoolhouse.world); the school's own intervention program if the kid qualifies; AI-tutor apps that promise personalization. The parent cannot easily tell which option is matched to what works versus what's marketing. They are not the math expert. The child is sensitive to the framing — *you need a tutor* can feel like a judgment, and a kid who closes off doesn't learn from anyone. Cost is real.
-The scope is from "we need help" through "we have a plan and a tutor we trust."</t>
+**Situation.** A child in 4th, 6th, or 8th grade is struggling in math. The grades have slipped; the teacher has sent a note; the standardized test result came back lower than expected. The parent has a few hours over the next two weeks to set something up, working evenings around their own job and the rest of the family's calendar.
+**Complication.** The parent is facing a tangle of options the landscape currently presents: the local tutoring chain (predictable but expensive, small-group, weekly); a private tutor matched through a friend (variable quality and availability); online tutoring marketplaces and free practice platforms; the school's own intervention program if the kid qualifies; AI-tutor apps that promise personalization. The parent cannot easily tell which option is matched to what works versus what's marketing. They are not the math expert.
+**Users.** A parent–child dyad at the moment of choosing help. The parent is the procurer and decider — scheduling, paying, reading reviews, judging fit. The child is the recipient and the one whose engagement determines whether any of this works; they are sensitive to the framing, since *you need a tutor* can feel like a judgment, and a kid who closes off doesn't learn from anyone. Tutor candidates and school staff are stakeholders the design accommodates, not the target.
+**Cost.** Weeks pass while the parent stalls between bad options; the child falls further behind in a subject that compounds; the wrong choice burns money and the child's willingness to try again. The scope is from "we need help" through "we have a plan and a tutor we trust."</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1244,9 +1257,10 @@
       <c r="B15" s="3" t="inlineStr">
         <is>
           <t># Pre-travel prescription preparation — design exploration
-A person is preparing for a long international trip. They take regular prescription medication — an SSRI, an ADHD stimulant, a blood thinner, hormone therapy, a controlled-substance painkiller. They are two weeks out and just realized this is harder than they thought. US prescriptions can't be filled at overseas pharmacies. Several common US medications are restricted or illegal in the country they're going to, with consequences that range from confiscation at customs to denial of entry to arrest. To carry enough for the trip, they need a vacation override from their insurance, weeks in advance, and probably a prescriber letter. None of that is one phone call.
-They are working it out across pharmacy phone trees, the insurer's app, the State Department's site, and Reddit threads. Their PCP's office is not set up to answer travel-medication questions. The pharmacy can fill the script if the doctor authorizes the override; the doctor will authorize the override if asked correctly. Nobody owns the work of getting this person across the world with their medication intact, legal, and packaged the way customs expects.
-The scope is the four-week window before international departure.</t>
+**Situation.** A person is preparing for a long international trip. They take regular prescription medication — an SSRI, an ADHD stimulant, a blood thinner, hormone therapy, a controlled-substance painkiller. They are two weeks out and just realized this is harder than they thought. US prescriptions can't be filled at overseas pharmacies. Several common US medications are restricted or illegal in the country they're going to.
+**Complication.** To carry enough for the trip, they need a vacation override from their insurance, weeks in advance, and probably a prescriber letter. None of that is one phone call. They are working it out across pharmacy phone trees, the insurer's app, the State Department's site, and Reddit threads. Their PCP's office is not set up to answer travel-medication questions. The pharmacy can fill the script if the doctor authorizes the override; the doctor will authorize the override if asked correctly. Nobody owns the work of getting this person across the world with their medication intact, legal, and packaged the way customs expects.
+**Users.** An international traveler on regular, often controlled, prescription medication — a person managing real conditions who needs to keep managing them on the other side of a border. Prescriber, pharmacist, insurer, and customs are stakeholders this work moves through, not the target.
+**Cost.** Consequences run from confiscation at customs to denial of entry to arrest in stricter jurisdictions, plus the quieter failure of running out of medication mid-trip and the destabilization that follows. The scope is the four-week window before international departure.</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1286,9 +1300,10 @@
       <c r="B16" s="3" t="inlineStr">
         <is>
           <t># Finding a primary care doctor after relocating — design exploration
-A person has moved to a new city and needs a primary care doctor. They have insurance, and their plan's website hands them an in-network directory — several hundred names, sorted by ZIP code. The directory shows specialties and addresses. It rarely shows which practices are accepting new patients, what the next available appointment actually is, which clinicians speak the languages spoken in the patient's household, whether the office is wheelchair-accessible, or how the practice handles diabetes care, mental-health needs, or pregnancy. The patient calls one office, sits on hold for ten minutes, navigates a phone tree, and is told the next opening is in five months — or that the practice isn't accepting new patients at all. Then the next call. Then the next.
-People with active conditions — chronic pain, diabetes, anxiety — need to start care now. The five-month appointments don't serve them, and many stop calling. People establishing routine care give up earlier and only re-engage when something is wrong. The options the patient is choosing between in the landscape today include the in-network directory itself, telehealth services their plan covers, federally-qualified health centers in the area, and direct primary care practices that bill outside insurance — none of which the directory surfaces side-by-side. The cost of failure is delayed care, undiagnosed conditions, and emergency visits that should have been clinic visits.
-The scope is from "I need a new doctor" through "I have an appointment booked." We want strategic directions that center the patient.</t>
+**Situation.** A person has moved to a new city and needs a primary care doctor. They have insurance, and their plan's website hands them an in-network directory — several hundred names, sorted by ZIP code. The directory shows specialties and addresses. It rarely shows which practices are accepting new patients, what the next available appointment actually is, which clinicians speak the languages spoken in the patient's household, whether the office is wheelchair-accessible, or how the practice handles diabetes care, mental-health needs, or pregnancy.
+**Complication.** The patient calls one office, sits on hold for ten minutes, navigates a phone tree, and is told the next opening is in five months — or that the practice isn't accepting new patients at all. Then the next call. Then the next. The options they are choosing between in the landscape today include the in-network directory itself, telehealth services their plan covers, federally-qualified health centers in the area, and direct primary care practices that bill outside insurance — none of which the directory surfaces side-by-side.
+**Users.** A patient looking for a primary care doctor in a new city. Some have active conditions — chronic pain, diabetes, anxiety — and need to start care now; others are establishing routine care and re-engage only when something goes wrong. The insurance plan, the in-network directory, the practices, and telehealth providers are stakeholder context the design accommodates, not the target.
+**Cost.** Delayed care for people who need it now; undiagnosed conditions for those who give up early; emergency visits for what should have been clinic visits. The scope is from "I need a new doctor" through "I have an appointment booked."</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1329,9 +1344,10 @@
       <c r="B17" s="3" t="inlineStr">
         <is>
           <t># Remote new-hire onboarding, week one — design exploration
-A competent professional joins a remote-first company on Monday. They have never met their team in person. They've done this before — they know how to set up a laptop and learn a new codebase. What's hard isn't the work; it's everything around it. They don't know this team's norms, this manager's actual (not stated) preferences, who is the person you actually ask about benefits, whether it's normal that they still can't access Notion. They are exhausted by the day HR built for them — nine meetings Monday, six Tuesday — and anxious about asking questions that would mark them as not-yet-onboard.
-Remote replaces the watercooler, the lunch tag-along, the overheard standup with calendar invites — which aren't the same thing. By Wednesday the orientation rush slows; by Thursday they're alone with documentation and unsure who to ask what. The five-day window from joining to belonging is where the relationship is made or lost; companies bleed early-tenure hires at exactly this point.
-The scope is the first five working days, Monday morning to Friday afternoon.</t>
+**Situation.** A competent professional joins a remote-first company on Monday. They have never met their team in person. They've done this before — they know how to set up a laptop and learn a new codebase. The HR-built first week is nine meetings Monday, six Tuesday; a stack of documentation; a Notion they still can't fully access; benefits links, security trainings, and a Slack workspace with a hundred channels.
+**Complication.** What's hard isn't the work; it's everything around it. They don't know this team's norms, this manager's actual (not stated) preferences, who is the person you actually ask about benefits. Remote replaces the watercooler, the lunch tag-along, and the overheard standup with calendar invites — which aren't the same thing. By Wednesday the orientation rush slows; by Thursday they're alone with documentation and unsure who to ask what, anxious about asking questions that would mark them as not-yet-onboard.
+**Users.** The new hire — a competent professional starting cold inside a remote-first company, navigating their first five working days from a home desk. The hiring manager, peers on the team, HR, and IT provisioning are stakeholders whose work shapes the week but who are not the target of the design.
+**Cost.** The five-day window from joining to belonging is where the relationship is made or lost; new hires who don't feel onboard by Friday carry that uncertainty into the next month, hesitate to ask, and quietly disengage. Companies bleed early-tenure hires at exactly this point. The scope is the first five working days, Monday morning to Friday afternoon.</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1386,10 +1402,10 @@
       <c r="B18" s="3" t="inlineStr">
         <is>
           <t># A sprint retro after a missed target — design exploration
-A product team has just finished a two-week sprint and missed what they committed to. The scrum master has forty-five minutes booked on Friday afternoon for the retrospective. The team is tired, the engineer who carried the cancelled feature is quiet on the call, the PM is reading their phone, and the VP of Engineering is on the line listening in. The scrum master has a Miro board with three columns and a stack of sticky notes their team has used in some version for the last two years.
-The scrum master is the user. They want a conversation about what actually went wrong this sprint and what the team will try differently next sprint. They want action items the team will still remember on Monday. The team itself is uneven: some members will say what they think directly, some won't say anything that could read as criticism with the PM in the room, and some will narrate the sprint as if it went fine. The tools the team already reaches for — Miro templates, FunRetro, EasyRetro, the Jira retro module — capture sticky notes and let people upvote them. What happens between "sticky notes captured" and "the team had a real conversation" lives outside those tools.
-A retro that doesn't land after a missed sprint compounds: the same patterns carry into the next sprint, and the team grows a little more cynical about whether retros are worth showing up to. A retro that does land is something the team can feel for weeks.
-The scope is the retrospective meeting itself, the prep before it, and the follow-through.</t>
+**Situation.** A product team has just finished a two-week sprint and missed what they committed to. The scrum master has forty-five minutes booked on Friday afternoon for the retrospective. The team is tired, the engineer who carried the cancelled feature is quiet on the call, the PM is reading their phone, and the VP of Engineering is on the line listening in. The scrum master has a Miro board with three columns and a stack of sticky notes their team has used in some version for the last two years.
+**Complication.** The team's existing tools — Miro templates, FunRetro, EasyRetro, the Jira retro module — capture sticky notes and let people upvote them. What happens between "sticky notes captured" and "the team had a real conversation" sits outside those tools. The team itself is uneven: some members will say what they think directly, some won't say anything that could read as criticism with the PM in the room, and some will narrate the sprint as if it went fine.
+**Users.** The scrum master is the target user — the one prepping the meeting, holding the room, and chasing follow-through. The team is the design's audience; the PM in the room and the VP listening in are stakeholders the meeting accommodates.
+**Cost.** A retro that doesn't land after a missed sprint compounds: the same patterns carry into the next sprint, action items are forgotten by Monday, and the team grows a little more cynical about whether retros are worth showing up to. A retro that does land is something the team can feel for weeks. The scope is the retrospective meeting itself, the prep before it, and the follow-through.</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1430,9 +1446,10 @@
       <c r="B19" s="3" t="inlineStr">
         <is>
           <t># Applying for food assistance — design exploration
-Someone who needs food assistance now is sitting down to apply for SNAP. They've lost a job, had hours cut, gotten sick, or are raising a kid on inconsistent income. The form in front of them asks branching questions whose answers depend on context the form does not let them explain, requires documents they can't easily produce in the moment (a recent pay stub from a gig that pays inconsistently, a lease they don't have a copy of, a Social Security card from a drawer at a place they no longer live), and was built to be filled out on a desktop computer they don't own. They are working from a phone, sometimes a shared one, often on intermittent data.
-After they submit, the experience goes quiet. They don't know if their application was received, is being processed, is waiting on a document the system has not asked for, or has already been denied. Days pass. The food situation that brought them here doesn't pause. Many people in this position get one attempt before they stop trying — not from a single rejection, but from the cumulative weight of submitting into silence while the rest of their life keeps moving. Some are first-time applicants who have never used the safety net before; some are mixed-status families weighing whether the application itself will be used against them; some have been disconnected for years and are returning under worse circumstances than the first time.
-What we want from this round: distinct strategic directions for what a humane food-assistance application could be when designed around the applicant.</t>
+**Situation.** Someone who needs food assistance now is sitting down to apply for SNAP. They've lost a job, had hours cut, gotten sick, or are raising a kid on inconsistent income. They are working from a phone, sometimes a shared one, often on intermittent data.
+**Complication.** The form in front of them asks branching questions whose answers depend on context the form does not let them explain, requires documents they can't easily produce in the moment (a recent pay stub from a gig that pays inconsistently, a lease they don't have a copy of, a Social Security card from a drawer at a place they no longer live), and was built to be filled out on a desktop computer they don't own. After they submit, the experience goes quiet. They don't know if the application was received, is being processed, is waiting on a document the system has not asked for, or has already been denied.
+**Users.** The target user is the applicant: a first-time applicant who has never used the safety net, a mixed-status family weighing whether the application itself will be used against them, or someone returning under worse circumstances than the first time. State eligibility workers who process and adjudicate these applications are stakeholders, not the target.
+**Cost.** Days pass. The food situation that brought them here doesn't pause. Many people in this position get one attempt before they stop trying — not from a single rejection, but from the cumulative weight of submitting into silence while the rest of their life keeps moving. What we want: distinct strategic directions for what a humane food-assistance application could be when designed around the applicant.</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1487,9 +1504,10 @@
       <c r="B20" s="3" t="inlineStr">
         <is>
           <t># The first 90 days after a Type 2 diabetes diagnosis — design exploration
-A person has just been told they have Type 2 diabetes. The diagnosis arrived in a fifteen-minute appointment with a handout, a prescription for metformin, and instructions to "watch your sugars" and to "see a nutritionist." They walk out scared, ashamed, confused about whether they caused this, and facing a slate of changes — diet, exercise, medication, glucose monitoring, A1c labs every three months — without anyone helping them sequence those changes. The nutritionist referral is a phone number on the printout. The diabetes self-management education and support sessions their insurance covers are not mentioned at the appointment.
-By the end of the next ninety days they will have either built a workable rhythm — meals, walking, the morning metformin, the glucose meter sitting on the kitchen counter — or they will have drifted: meter in a drawer, prescription unfilled at refill time, weight unchanged, and no further appointment booked until the next labs flag something. The landscape they encounter when they look for help includes glucose-logging utilities, coaching platforms (Livongo, Virta, Omada), peer-support communities, and YouTube videos from creators of varying authority. The app the patient lands on tends to ask them to log their glucose on day one. None of it is shaped around the moment of diagnosis itself — the week they are still telling family, the week they are deciding whether they want to tell work.
-The scope is from diagnosis through the 90-day mark.</t>
+**Situation.** A person has just been told they have Type 2 diabetes. The diagnosis arrived in a fifteen-minute appointment with a handout, a prescription for metformin, and instructions to "watch your sugars" and to "see a nutritionist." They walk out scared, ashamed, confused about whether they caused this, and facing a slate of changes — diet, exercise, medication, glucose monitoring, A1c labs every three months.
+**Complication.** No one helps them sequence those changes. The nutritionist referral is a phone number on the printout. The diabetes self-management education and support sessions their insurance covers are not mentioned at the appointment. The landscape they encounter when they look for help — glucose-logging utilities, coaching platforms (Livongo, Virta, Omada), peer-support communities, and YouTube videos from creators of varying authority — tends to ask them to log their glucose on day one. None of it is shaped around the moment of diagnosis itself: the week they are still telling family, the week they are deciding whether to tell work.
+**Users.** The target user is the newly-diagnosed patient in the first 90 days. The clinician and the nutritionist are stakeholders the design accommodates — referrals come from them, labs route through them — but are not who the design is for.
+**Cost.** By the end of the next ninety days they will have either built a workable rhythm — meals, walking, the morning metformin, the glucose meter sitting on the kitchen counter — or they will have drifted: meter in a drawer, prescription unfilled at refill time, weight unchanged, and no further appointment booked until the next labs flag something. The scope is from diagnosis through the 90-day mark.</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1529,9 +1547,10 @@
       <c r="B21" s="3" t="inlineStr">
         <is>
           <t># Filing for unemployment insurance — design exploration
-A person has just lost their job and is filing for unemployment insurance through their state's labor agency. They may have a few weeks of rent in the bank or none. They are filling out the application on a phone, in line at a job center, between caregiving shifts, or late at night after the kids are asleep. The application asks for an EDDCAN number they have never heard of, for pay stubs from the last eighteen months they may not have saved, for the precise dates and hours of every job worked in a base period that doesn't match how variable-schedule work happens. The legalese is dense. A wrong answer on any of dozens of questions delays or denies the claim, and the appeal that follows takes weeks the person doesn't have.
-Once the claim is filed, the channels they can use to find out what's happening with it are a state portal that often shows information weeks out of date, paper letters that arrive after the next pay period would have been due, and a phone line that holds for hours. The portal will sometimes say the claim is being processed; sometimes it will say nothing at all. Money does not arrive on a schedule the person can plan around. Meanwhile rent is due, the car insurance lapses, the kid needs school supplies. The benefit is something the person is entitled to under state and federal law; the gap between filing the application and the first payment landing in the account is where the urgency of the situation collides with what the system communicates.
-The scope is the filing flow plus the first thirty days of claim-status communication.</t>
+**Situation.** A person has just lost their job and is filing for unemployment insurance through their state's labor agency. They may have a few weeks of rent in the bank or none. They are filling out the application on a phone — in line at a job center, between caregiving shifts, or late at night after the kids are asleep.
+**Complication.** The application asks for an EDDCAN number they have never heard of, pay stubs from the last eighteen months they may not have saved, and the precise dates and hours of every job worked in a base period that doesn't match how variable-schedule work happens. The legalese is dense. A wrong answer on any of dozens of questions delays or denies the claim, and the appeal that follows takes weeks. Once filed, the channels for finding out what's happening are a state portal that often shows information weeks out of date, paper letters that arrive after the next pay period would have been due, and a phone line that holds for hours. The portal sometimes says the claim is being processed; sometimes nothing at all.
+**Users.** The target user is the claimant — filing and waiting on benefits they are entitled to under state and federal law. State eligibility workers and adjudicators are stakeholders, not the target.
+**Cost.** Money does not arrive on a schedule the person can plan around. Rent is due, the car insurance lapses, the kid needs school supplies. The gap between filing and the first payment landing is where the urgency of the situation collides with what the system communicates. The scope is the filing flow plus the first thirty days of claim-status communication.</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1571,9 +1590,10 @@
       <c r="B22" s="3" t="inlineStr">
         <is>
           <t># Updating voter registration after a name change — design exploration
-A person has changed their legal name — after marriage, divorce, gender transition, or by personal choice. Their old name is on the voter roll. The next election is months away. They've heard from someone that they should update their registration; they don't know whether they need to, by when, what proof, or how the rules in their state differ from the rules a friend in another state explained. The state election-board website is a tangle of pages and PDFs that don't quite match their situation.
-The voter is mid-life-transition with a long list of bureaucratic to-dos the name change has triggered — driver's license, Social Security card, employer records, banking, passports, professional credentials. Voter registration is on the list, somewhere, and is the one most likely to be skipped until election day, when the name fails the poll-book check and they're asked to cast a provisional ballot they may not return for.
-The scope is the act of updating registration plus the ambiguity around it — *do I need to, when by, what proof, will this be wrong on election day.*</t>
+**Situation.** A person has changed their legal name — after marriage, divorce, gender transition, leaving an abusive relationship, or by personal choice. Their old name is on the voter roll. The next election is months away. Someone told them they should update their registration; they don't know whether they need to, by when, what proof, or how their state's rules differ from a friend's in another state.
+**Complication.** The state election-board website is a tangle of pages and PDFs that don't quite match their situation. Voter registration sits inside a long list of bureaucratic to-dos the name change has triggered — driver's license, Social Security card, employer records, banking, passports — and is the one most likely to be skipped until election day.
+**Users.** The target user is the voter mid-name-change: a trans person whose ID is finally catching up to their name, a domestic-violence survivor who changed their name for safety, a recently-married or recently-divorced voter, or someone who chose a new name. Each comes with different proof, different timelines, and different concerns about who sees the old name during the update. Election-board staff and poll workers are stakeholders, not the target.
+**Cost.** On election day, the name fails the poll-book check and they're asked to cast a provisional ballot they may not return to cure. A vote they were entitled to cast doesn't count, and being challenged at the table — especially for trans voters or survivors whose old name is read aloud — can make them less likely to return. The scope is updating registration plus the ambiguity around it — *do I need to, when by, what proof, will this be wrong on election day.*</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">

--- a/experiments/corpus-content.xlsx
+++ b/experiments/corpus-content.xlsx
@@ -503,10 +503,14 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t># Apartment search for a renter with a past eviction — design exploration
-**Situation.** A person with an eviction record is looking for a new place to live. The eviction may have followed a job loss, a medical event, or a dispute with a prior landlord — sometimes a dismissed filing, sometimes a filing-in-error, sometimes a completed eviction-for-cause. The renter has since rebuilt: a job, references, money for a deposit. What reaches the landlord is a tenant-screening report — bundling rental, credit, employment, and criminal history into a score — on which the filing looks the same whether the case was won, lost, or dismissed.
-**Complication.** The renter pays application fees at every listing and discovers, sometimes days later, that they have been declined. They get back a vague "did not meet screening criteria" or no explanation at all. There is no path to find out which factor produced the decline, no path to contest a record they believe is inaccurate. They confront listing aggregators, screening companies whose reports they cannot see, bureau disputes that move slowly, and legal-aid offices whose capacity does not meet the volume.
-**Users.** The renter with the eviction record on their file. Landlords and screening companies are stakeholders, not the target — the design is for the renter with weeks, not months, and a stack of declined applications. Scope is "I'm looking" through "I've signed a lease."
-**Cost.** They need to be housed in the weeks they have, not the months a dispute would take. Fees stack up against a deposit they are trying to keep intact. Each decline arrives without enough information to act on, and the next listing goes up against the same report. The current housing is running out or already gone.</t>
+## Situation
+A person with an eviction record is looking for a new place to live. The eviction may have followed a job loss, a medical event, or a dispute with a prior landlord — sometimes a dismissed filing, sometimes a filing-in-error, sometimes a completed eviction-for-cause. The renter has since rebuilt: a job, references, money for a deposit. What reaches the landlord is a tenant-screening report — bundling rental, credit, employment, and criminal history into a score — on which the filing looks the same whether the case was won, lost, or dismissed.
+## Complication
+The renter pays application fees at every listing and discovers, sometimes days later, that they have been declined. They get back a vague "did not meet screening criteria" or no explanation at all. There is no path to find out which factor produced the decline, no path to contest a record they believe is inaccurate. They confront listing aggregators, screening companies whose reports they cannot see, bureau disputes that move slowly, and legal-aid offices whose capacity does not meet the volume.
+## Users
+The renter with the eviction record on their file. Landlords and screening companies are stakeholders, not the target — the design is for the renter with weeks, not months, and a stack of declined applications. Scope is "I'm looking" through "I've signed a lease."
+## Cost
+They need to be housed in the weeks they have, not the months a dispute would take. Fees stack up against a deposit they are trying to keep intact. Each decline arrives without enough information to act on, and the next listing goes up against the same report. The current housing is running out or already gone.</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -562,10 +566,14 @@
       <c r="B3" s="3" t="inlineStr">
         <is>
           <t># Coordinating care for an aging parent — design exploration
-**Situation.** An adult child is responsible for the day-to-day care of an aging parent in another city. They are working full-time, may be raising their own kids, and are now also managing their parent's medications, appointments, insurance disputes, in-home aide schedule, finances, and longer-term decisions about home modifications, assisted living, or hospice — with sibling involvement that ranges from supportive to fractious.
-**Complication.** The information lives everywhere — their own phone, their email, the parent's hand-written notes on a yellow pad by the kitchen phone, the parent's doctor's portals (three or four, each with its own login), Medicare statements, the aide's notebook, the pharmacy's text messages. No system holds the picture; the caregiver holds it, in their head, between work meetings and bedtime. The new prescription started last Thursday is supposed to be checked against the cardiologist's older one that may or may not have been discontinued. The PCP's portal does not show the cardiologist's prescriptions. The aide's notebook is three hundred miles away.
-**Users.** The adult-child caregiver and the aging parent, as a dyad — the parent in their own apartment, the caregiver coordinating from three hundred miles away. Siblings, aides, doctors, and pharmacists are stakeholders the design accommodates, not optimizes for. Scope is the rhythm of a month, not a single appointment.
-**Cost.** When something goes wrong — a missed medication, a duplicate dose, an ED visit that looks preventable in hindsight — the gap was between systems the caregiver was supposed to bridge across. The parent absorbs the errors when the picture slips. The work eats evenings, weekends, and the bandwidth left for everything else in the caregiver's life.</t>
+## Situation
+An adult child is responsible for the day-to-day care of an aging parent in another city. They are working full-time, may be raising their own kids, and are now also managing their parent's medications, appointments, insurance disputes, in-home aide schedule, finances, and longer-term decisions about home modifications, assisted living, or hospice — with sibling involvement that ranges from supportive to fractious.
+## Complication
+The information lives everywhere — their own phone, their email, the parent's hand-written notes on a yellow pad by the kitchen phone, the parent's doctor's portals (three or four, each with its own login), Medicare statements, the aide's notebook, the pharmacy's text messages. No system holds the picture; the caregiver holds it, in their head, between work meetings and bedtime. The new prescription started last Thursday is supposed to be checked against the cardiologist's older one that may or may not have been discontinued. The PCP's portal does not show the cardiologist's prescriptions. The aide's notebook is three hundred miles away.
+## Users
+The adult-child caregiver and the aging parent, as a dyad — the parent in their own apartment, the caregiver coordinating from three hundred miles away. Siblings, aides, doctors, and pharmacists are stakeholders the design accommodates, not optimizes for. Scope is the rhythm of a month, not a single appointment.
+## Cost
+When something goes wrong — a missed medication, a duplicate dose, an ED visit that looks preventable in hindsight — the gap was between systems the caregiver was supposed to bridge across. The parent absorbs the errors when the picture slips. The work eats evenings, weekends, and the bandwidth left for everything else in the caregiver's life.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -621,10 +629,14 @@
       <c r="B4" s="3" t="inlineStr">
         <is>
           <t># An adult learner re-entering community college — design exploration
-**Situation.** An adult — twenty-five, thirty-five, fifty — has enrolled at community college, often after years away from formal schooling. They've decided to re-enroll for a new credential, an industry switch, or developmental coursework before a four-year transfer. They've signed up; they haven't started. They have a job that won't easily flex, kids who need pick-up, and the cognitive disjuncture of being asked to think like a student again after years of not being one.
-**Complication.** They are trying to read a college website built for eighteen-year-olds applying for fall. They are unsure where to park, what to bring to orientation, whether the FAFSA they filled out applies to summer term, whether they can register part-time without losing the financial-aid bracket, and how to reach an advisor who answers in less than two weeks.
-**Users.** The adult learner re-entering community college after years away — not the eighteen-year-old applying for fall, and not the returner with a working campus rhythm. Advisors, financial-aid officers, and registrars are stakeholders the design encounters, not optimizes for. Scope is the eight-week window from "I've enrolled" through "I've completed the first month of classes."
-**Cost.** The first month is where the workable rhythm either gets built or doesn't. When the answers don't arrive in the window — when orientation feels alien, when the FAFSA question goes two weeks without a reply, when the parking and pick-up logistics don't line up — the learner quietly stops coming. The enrollment becomes another unfinished credential, the tuition becomes a sunk cost, and the next attempt is years out.</t>
+## Situation
+An adult — twenty-five, thirty-five, fifty — has enrolled at community college, often after years away from formal schooling. They've decided to re-enroll for a new credential, an industry switch, or developmental coursework before a four-year transfer. They've signed up; they haven't started. They have a job that won't easily flex, kids who need pick-up, and the cognitive disjuncture of being asked to think like a student again after years of not being one.
+## Complication
+They are trying to read a college website built for eighteen-year-olds applying for fall. They are unsure where to park, what to bring to orientation, whether the FAFSA they filled out applies to summer term, whether they can register part-time without losing the financial-aid bracket, and how to reach an advisor who answers in less than two weeks.
+## Users
+The adult learner re-entering community college after years away — not the eighteen-year-old applying for fall, and not the returner with a working campus rhythm. Advisors, financial-aid officers, and registrars are stakeholders the design encounters, not optimizes for. Scope is the eight-week window from "I've enrolled" through "I've completed the first month of classes."
+## Cost
+The first month is where the workable rhythm either gets built or doesn't. When the answers don't arrive in the window — when orientation feels alien, when the FAFSA question goes two weeks without a reply, when the parking and pick-up logistics don't line up — the learner quietly stops coming. The enrollment becomes another unfinished credential, the tuition becomes a sunk cost, and the next attempt is years out.</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -679,10 +691,14 @@
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t># Disputing a credit-report error — design exploration
-**Situation.** A person has been denied an apartment, a job, a loan, or an insurance rate because of something on their credit report — and the something is wrong. A debt they paid years ago. An account opened in their name fraudulently. Identity confusion with a relative who shares their name. They have proof — receipts, closure letters, identity-theft affidavits — and no clear path to get it to the right place.
-**Complication.** They face three different dispute interfaces, one per bureau, each demanding documentation in slightly different formats and each capable of returning a one-line "investigated, no change" weeks later. They are unsure whether to write a paper letter, use the online portals, file directly with the furnisher, file a CFPB complaint, or do all four. The original error often reappears later from a different furnisher, and the consumer is back at the same three logins, the same documentation queue, the same wait. They confront the bureaus' portals, free-credit-report sites that funnel toward paid monitoring, the CFPB channel, IdentityTheft.gov, and legal-aid whose capacity does not meet the volume.
-**Users.** The consumer disputing the error — the one with receipts and closure letters in hand. Bureaus, furnishers, and CFPB intake staff are stakeholders, not the target. Scope is from noticing the error through resolution.
-**Cost.** The process unfolds over thirty to ninety days while the apartment application sits in limbo and the new job offer is on hold. The denial that prompted the dispute does not pause for resolution. When the error reappears from a different furnisher, the consumer is back at the same three logins, doing the work again on a life that has moved on.</t>
+## Situation
+A person has been denied an apartment, a job, a loan, or an insurance rate because of something on their credit report — and the something is wrong. A debt they paid years ago. An account opened in their name fraudulently. Identity confusion with a relative who shares their name. They have proof — receipts, closure letters, identity-theft affidavits — and no clear path to get it to the right place.
+## Complication
+They face three different dispute interfaces, one per bureau, each demanding documentation in slightly different formats and each capable of returning a one-line "investigated, no change" weeks later. They are unsure whether to write a paper letter, use the online portals, file directly with the furnisher, file a CFPB complaint, or do all four. The original error often reappears later from a different furnisher, and the consumer is back at the same three logins, the same documentation queue, the same wait. They confront the bureaus' portals, free-credit-report sites that funnel toward paid monitoring, the CFPB channel, IdentityTheft.gov, and legal-aid whose capacity does not meet the volume.
+## Users
+The consumer disputing the error — the one with receipts and closure letters in hand. Bureaus, furnishers, and CFPB intake staff are stakeholders, not the target. Scope is from noticing the error through resolution.
+## Cost
+The process unfolds over thirty to ninety days while the apartment application sits in limbo and the new job offer is on hold. The denial that prompted the dispute does not pause for resolution. When the error reappears from a different furnisher, the consumer is back at the same three logins, doing the work again on a life that has moved on.</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -737,10 +753,14 @@
       <c r="B6" s="3" t="inlineStr">
         <is>
           <t># First contact with 988, the crisis line — design exploration
-**Situation.** Someone is reaching out to the US crisis line — 988 — for the first time. They may be experiencing a suicidal crisis, an acute panic episode, a substance-use crisis, or distress around grief, abuse, or identity. They may be the person in crisis, or a friend or family member trying to help someone else. They are reaching out at a moment of acute vulnerability and have a choice to make about whether to stay on the line.
-**Complication.** The first sixty seconds are determinative. What does this look like; will I be judged; what's about to happen; will police be sent to my address if I say the wrong thing. People who have heard that police might be dispatched are hesitant in ways the system has to meet; people who have never reached out before are calibrating from the screen, the voice, the hold music. The decision to keep reaching, or to hang up and not try again, is made before anyone has said anything.
-**Users.** The first-time reacher — the person in crisis, or the friend or family member calling on their behalf — in the opening seconds before a counselor has spoken. Counselors and dispatchers are stakeholders the design hands off to, not optimizes for. Scope is the call, text, or chat opening plus the immediate next step; the counselor protocol itself is out of scope.
-**Cost.** When the first sixty seconds don't hold, the person hangs up and does not try again. The next acute moment arrives without a line they trust. The friend who was calling for someone else goes back with nothing to offer.</t>
+## Situation
+Someone is reaching out to the US crisis line — 988 — for the first time. They may be experiencing a suicidal crisis, an acute panic episode, a substance-use crisis, or distress around grief, abuse, or identity. They may be the person in crisis, or a friend or family member trying to help someone else. They are reaching out at a moment of acute vulnerability and have a choice to make about whether to stay on the line.
+## Complication
+The first sixty seconds are determinative. What does this look like; will I be judged; what's about to happen; will police be sent to my address if I say the wrong thing. People who have heard that police might be dispatched are hesitant in ways the system has to meet; people who have never reached out before are calibrating from the screen, the voice, the hold music. The decision to keep reaching, or to hang up and not try again, is made before anyone has said anything.
+## Users
+The first-time reacher — the person in crisis, or the friend or family member calling on their behalf — in the opening seconds before a counselor has spoken. Counselors and dispatchers are stakeholders the design hands off to, not optimizes for. Scope is the call, text, or chat opening plus the immediate next step; the counselor protocol itself is out of scope.
+## Cost
+When the first sixty seconds don't hold, the person hangs up and does not try again. The next acute moment arrives without a line they trust. The friend who was calling for someone else goes back with nothing to offer.</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -794,10 +814,14 @@
       <c r="B7" s="3" t="inlineStr">
         <is>
           <t># Closing a deceased family member's accounts — design exploration
-**Situation.** When a person dies, someone in the family inherits an administrative ordeal nobody trained them for. They are the executor — spouse, adult child, sibling — and now need to identify, contact, and close out dozens of accounts: banks, credit cards, utilities, mortgages, retirement accounts, insurance, Social Security, and a digital life of email and photos and subscriptions. They are doing this in the evenings, between the funeral and the rest of life — often from a different city than the deceased, with a death certificate in hand and a stack of unopened mail.
-**Complication.** Each institution has its own forms, its own definitions, its own staff. Debt collectors begin calling within days; most are wrong about what the survivor owes, but the conversations are intimidating and the rules vary by state. The available resources are accurate and encyclopedic; they list eighty things the executor might need to do, with no way to know which twelve apply today.
-**Users.** The executor — spouse, adult child, or sibling — grieving and doing this because someone had to be. Institutions and debt collectors are stakeholders, not the design's target. Scope is from the first week through final dissolution.
-**Cost.** The work runs in the evenings on top of grief, on top of a job, on top of a household that did not pause. The encyclopedic list does not tell the executor which twelve of eighty steps belong to today, so the wrong ones get done first or none at all. The collectors' calls keep coming. The estate stays open, the mail keeps arriving, and the grief is interrupted every time the ordeal reasserts itself.</t>
+## Situation
+When a person dies, someone in the family inherits an administrative ordeal nobody trained them for. They are the executor — spouse, adult child, sibling — and now need to identify, contact, and close out dozens of accounts: banks, credit cards, utilities, mortgages, retirement accounts, insurance, Social Security, and a digital life of email and photos and subscriptions. They are doing this in the evenings, between the funeral and the rest of life — often from a different city than the deceased, with a death certificate in hand and a stack of unopened mail.
+## Complication
+Each institution has its own forms, its own definitions, its own staff. Debt collectors begin calling within days; most are wrong about what the survivor owes, but the conversations are intimidating and the rules vary by state. The available resources are accurate and encyclopedic; they list eighty things the executor might need to do, with no way to know which twelve apply today.
+## Users
+The executor — spouse, adult child, or sibling — grieving and doing this because someone had to be. Institutions and debt collectors are stakeholders, not the design's target. Scope is from the first week through final dissolution.
+## Cost
+The work runs in the evenings on top of grief, on top of a job, on top of a household that did not pause. The encyclopedic list does not tell the executor which twelve of eighty steps belong to today, so the wrong ones get done first or none at all. The collectors' calls keep coming. The estate stays open, the mail keeps arriving, and the grief is interrupted every time the ordeal reasserts itself.</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -851,10 +875,14 @@
       <c r="B8" s="3" t="inlineStr">
         <is>
           <t># Driver's license transfer after a cross-state move — design exploration
-**Situation.** A person has moved from one US state to another. They have a job to start, an apartment to unpack, a kid in a new school. Somewhere on the list is "transfer the driver's license," and the new state's DMV site is a tangle of pages that don't quite match the user's situation: out-of-state transfer vs new resident vs non-citizen vs recently-licensed teen. They have a stack of documents — birth certificate, Social Security card, lease, utility bill, old license, marriage certificate.
-**Complication.** They aren't sure which documents the office will accept on the day. They want to know when to go, what to bring, what the visit will feel like, and what happens if something goes wrong. The DMV won't tell them ahead of time. The mover does the visit, leaves with a temporary paper printout, and waits weeks for the hard copy in the mail. In the meantime they aren't sure whether the paper is enough to fly, open a bank account, or pass any other ID check.
-**Users.** A recent mover in the four-to-six-week window after a cross-state move, navigating the new state's DMV alone with a folder of documents and other life on fire.
-**Cost.** Getting any of this wrong costs another visit, another day of work missed, and the same lack of information about what's next. The scope is the four-to-six-week window after a move during which the license needs to transfer.</t>
+## Situation
+A person has moved from one US state to another. They have a job to start, an apartment to unpack, a kid in a new school. Somewhere on the list is "transfer the driver's license," and the new state's DMV site is a tangle of pages that don't quite match the user's situation: out-of-state transfer vs new resident vs non-citizen vs recently-licensed teen. They have a stack of documents — birth certificate, Social Security card, lease, utility bill, old license, marriage certificate.
+## Complication
+They aren't sure which documents the office will accept on the day. They want to know when to go, what to bring, what the visit will feel like, and what happens if something goes wrong. The DMV won't tell them ahead of time. The mover does the visit, leaves with a temporary paper printout, and waits weeks for the hard copy in the mail. In the meantime they aren't sure whether the paper is enough to fly, open a bank account, or pass any other ID check.
+## Users
+A recent mover in the four-to-six-week window after a cross-state move, navigating the new state's DMV alone with a folder of documents and other life on fire.
+## Cost
+Getting any of this wrong costs another visit, another day of work missed, and the same lack of information about what's next. The scope is the four-to-six-week window after a move during which the license needs to transfer.</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -907,10 +935,14 @@
       <c r="B9" s="3" t="inlineStr">
         <is>
           <t># A first-time manager's first performance review — design exploration
-**Situation.** Someone who has been a people manager for less than a year sits down at midnight to write their first performance review of an employee. They have nine weeks of notes — most of them mental — and a template HR handed down with fifteen sections and a five-point rating scale. They are also navigating a calibration cycle in which their ratings will be compared against peer managers' ratings, with rules they only half-understand.
-**Complication.** The performance-management software they're using delivers prompts and templates but does not actually help them think through what to say to this specific person about this specific thing. They are scared of doing harm. Of giving feedback that lands wrong. Of being too soft and ducking the real issue. Of being too critical and damaging a working relationship. They are alone with a form and a blinking cursor.
-**Users.** A first-time people manager writing their first review of a direct report — who might be a former peer, someone they hired, or someone with more years in the industry than they have. HR and the calibration committee are stakeholders the manager has to satisfy, but the design is for the manager in the moment of writing.
-**Cost.** The cost of getting this wrong is paid both at the next 1:1 and across the year that follows — a damaged working relationship, a real issue ducked, or feedback that lands so wrong it forecloses growth. The scope is the act of writing the review — the hours between *I have to write this* and *I have a draft I'd send.*</t>
+## Situation
+Someone who has been a people manager for less than a year sits down at midnight to write their first performance review of an employee. They have nine weeks of notes — most of them mental — and a template HR handed down with fifteen sections and a five-point rating scale. They are also navigating a calibration cycle in which their ratings will be compared against peer managers' ratings, with rules they only half-understand.
+## Complication
+The performance-management software they're using delivers prompts and templates but does not actually help them think through what to say to this specific person about this specific thing. They are scared of doing harm. Of giving feedback that lands wrong. Of being too soft and ducking the real issue. Of being too critical and damaging a working relationship. They are alone with a form and a blinking cursor.
+## Users
+A first-time people manager writing their first review of a direct report — who might be a former peer, someone they hired, or someone with more years in the industry than they have. HR and the calibration committee are stakeholders the manager has to satisfy, but the design is for the manager in the moment of writing.
+## Cost
+The cost of getting this wrong is paid both at the next 1:1 and across the year that follows — a damaged working relationship, a real issue ducked, or feedback that lands so wrong it forecloses growth. The scope is the act of writing the review — the hours between *I have to write this* and *I have a draft I'd send.*</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -964,10 +996,14 @@
       <c r="B10" s="3" t="inlineStr">
         <is>
           <t># A grief-focused web app — design exploration
-**Situation.** We're scoping a web product for people in active grief. The space today splits roughly three ways: funeral logistics sites (transactional, mostly pre-funeral), peer support communities and subreddits (exposing or noisy for many), and journaling apps that bolt on a "feeling sad" mood tag (toothless). The users we keep hearing from describe wanting something different — something that respects them as someone grieving rather than treating them as a user to be moved through a funnel or a feed.
-**Complication.** People reach for a tool at the awkward moments: 3am, the anniversary, after a hard conversation with a sibling about settling the estate, on a Tuesday for no specific reason. At those moments, the funeral sites read transactional, the subreddits feel either welcoming or hostile depending on luck, and the mood-tag prompt asks "how are you feeling today?" as if grief were a state to log. Existing tools fail them by being too prescriptive ("step 4 of 7: write a letter to your loved one") or too generic.
-**Users.** Anyone weeks-to-months out from a meaningful loss — recent enough that grief is shaping the day, not so recent that they're still in funeral logistics. The losses vary: parent, partner, friend, pregnancy, pet, anticipatory loss with a terminal diagnosis. The support systems around them vary more — some surrounded by attentive friends, others whose network has gone quiet at six weeks.
-**Cost.** The cost of failure isn't dramatic — it's the slow drift away from a tool that doesn't meet them, and the continued absence of a place that does. What we want from this round: distinct strategic directions for what "a web app for grief" could meaningfully be — real bets that could move the category, not convergent variants.</t>
+## Situation
+We're scoping a web product for people in active grief. The space today splits roughly three ways: funeral logistics sites (transactional, mostly pre-funeral), peer support communities and subreddits (exposing or noisy for many), and journaling apps that bolt on a "feeling sad" mood tag (toothless). The users we keep hearing from describe wanting something different — something that respects them as someone grieving rather than treating them as a user to be moved through a funnel or a feed.
+## Complication
+People reach for a tool at the awkward moments: 3am, the anniversary, after a hard conversation with a sibling about settling the estate, on a Tuesday for no specific reason. At those moments, the funeral sites read transactional, the subreddits feel either welcoming or hostile depending on luck, and the mood-tag prompt asks "how are you feeling today?" as if grief were a state to log. Existing tools fail them by being too prescriptive ("step 4 of 7: write a letter to your loved one") or too generic.
+## Users
+Anyone weeks-to-months out from a meaningful loss — recent enough that grief is shaping the day, not so recent that they're still in funeral logistics. The losses vary: parent, partner, friend, pregnancy, pet, anticipatory loss with a terminal diagnosis. The support systems around them vary more — some surrounded by attentive friends, others whose network has gone quiet at six weeks.
+## Cost
+The cost of failure isn't dramatic — it's the slow drift away from a tool that doesn't meet them, and the continued absence of a place that does. What we want from this round: distinct strategic directions for what "a web app for grief" could meaningfully be — real bets that could move the category, not convergent variants.</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1022,10 +1058,14 @@
       <c r="B11" s="3" t="inlineStr">
         <is>
           <t># Discharge instructions for older adults going home — design exploration
-**Situation.** An older adult is being discharged from the hospital this afternoon after a heart-failure exacerbation, a stroke, a fall, or pneumonia. A family caregiver — often an adult child who has travelled in — will run the first week or two at home. The nurse has roughly fifteen minutes to walk through six pages of paperwork before the next admission needs the room.
-**Complication.** The patient is in pain, on medications that affect cognition, exhausted and emotionally activated; what they remember of those fifteen minutes once home is fragmentary. The caregiver who will administer the next thirty days is sometimes in the room and sometimes not. A few days later, the patient is trying to figure out which white pill is the new beta-blocker, what "weigh yourself daily and call if you gain more than three pounds in a week" means in practice, whether today's ankle swelling is a warning sign, and what the printed phone number is for after hours. The discharge papers are face-down on the kitchen table next to the medication bottles. The follow-up is in eleven days.
-**Users.** The dyad post-discharge: the older adult patient recovering at home, and the family caregiver — often an adult child — running the first week or two of medications, warning signs, and follow-up logistics. The discharging nurse and follow-up clinic are stakeholders the design accommodates; the design is for the dyad once paperwork has come home.
-**Cost.** Between now and the follow-up, it is the patient and the caregiver and the paperwork. The cost of getting it wrong is a missed warning sign, a doubled medication, a readmission. Scope is the discharge moment plus the first 7–14 days at home; the clinical care plan is out of scope.</t>
+## Situation
+An older adult is being discharged from the hospital this afternoon after a heart-failure exacerbation, a stroke, a fall, or pneumonia. A family caregiver — often an adult child who has travelled in — will run the first week or two at home. The nurse has roughly fifteen minutes to walk through six pages of paperwork before the next admission needs the room.
+## Complication
+The patient is in pain, on medications that affect cognition, exhausted and emotionally activated; what they remember of those fifteen minutes once home is fragmentary. The caregiver who will administer the next thirty days is sometimes in the room and sometimes not. A few days later, the patient is trying to figure out which white pill is the new beta-blocker, what "weigh yourself daily and call if you gain more than three pounds in a week" means in practice, whether today's ankle swelling is a warning sign, and what the printed phone number is for after hours. The discharge papers are face-down on the kitchen table next to the medication bottles. The follow-up is in eleven days.
+## Users
+The dyad post-discharge: the older adult patient recovering at home, and the family caregiver — often an adult child — running the first week or two of medications, warning signs, and follow-up logistics. The discharging nurse and follow-up clinic are stakeholders the design accommodates; the design is for the dyad once paperwork has come home.
+## Cost
+Between now and the follow-up, it is the patient and the caregiver and the paperwork. The cost of getting it wrong is a missed warning sign, a doubled medication, a readmission. Scope is the discharge moment plus the first 7–14 days at home; the clinical care plan is out of scope.</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1082,10 +1122,14 @@
       <c r="B12" s="3" t="inlineStr">
         <is>
           <t># Self-representation in housing court — design exploration
-**Situation.** A tenant has received an eviction notice. Their landlord has filed in housing court. They have a court date in two to three weeks. They cannot afford an attorney; the legal-aid clinic in their county is at capacity. The available self-help resources are accurate, thorough, and unusable in their situation: long PDFs of legalese for someone who is working two jobs and putting kids to bed at the same time.
-**Complication.** The tenant may or may not have a legal defense. The landlord may not have given proper notice; the rent claim may be wrong; the unit may be uninhabitable; the landlord may have engaged in unlawful self-help. Or the tenant may not have a defense and needs to negotiate time, settle, or simply file an answer to preserve options. They have a stack of papers in three different formats, a phone, and an internet connection. They cannot tell which of the eighty pieces of available advice apply to their facts and which don't.
-**Users.** A pro-se tenant facing an eviction filing with a court date two to three weeks out, navigating the case alone. Legal-aid attorneys, court clerks, and the landlord's counsel are stakeholders the tenant encounters; the design is for the tenant doing the work between notice and hearing.
-**Cost.** What they need is to walk into court understanding what is about to happen and what they should say. The cost of falling short is a default judgment, a lost home, and a record that follows them to the next lease application. The scope is from "I got a notice" through "I have prepared for court."</t>
+## Situation
+A tenant has received an eviction notice. Their landlord has filed in housing court. They have a court date in two to three weeks. They cannot afford an attorney; the legal-aid clinic in their county is at capacity. The available self-help resources are accurate, thorough, and unusable in their situation: long PDFs of legalese for someone who is working two jobs and putting kids to bed at the same time.
+## Complication
+The tenant may or may not have a legal defense. The landlord may not have given proper notice; the rent claim may be wrong; the unit may be uninhabitable; the landlord may have engaged in unlawful self-help. Or the tenant may not have a defense and needs to negotiate time, settle, or simply file an answer to preserve options. They have a stack of papers in three different formats, a phone, and an internet connection. They cannot tell which of the eighty pieces of available advice apply to their facts and which don't.
+## Users
+A pro-se tenant facing an eviction filing with a court date two to three weeks out, navigating the case alone. Legal-aid attorneys, court clerks, and the landlord's counsel are stakeholders the tenant encounters; the design is for the tenant doing the work between notice and hearing.
+## Cost
+What they need is to walk into court understanding what is about to happen and what they should say. The cost of falling short is a default judgment, a lost home, and a record that follows them to the next lease application. The scope is from "I got a notice" through "I have prepared for court."</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1140,10 +1184,14 @@
       <c r="B13" s="3" t="inlineStr">
         <is>
           <t># Multi-currency expense report submission — design exploration
-**Situation.** A traveler is home for two days between business trips. The trip that just ended ran through three countries, with receipts in five formats, photos of meals in a foreign language, an airline charge that hit their card in USD but was billed in EUR, a hotel charge pre-authorized at one amount and posted at another, an Uber auto-uploaded but mis-categorized as personal, and a cash tip paid because the card terminal was broken. They have policy questions — was the upgraded flight reimbursable, what counts as a client meal — and no one to ask quickly.
-**Complication.** They submit. Finance rejects it for a single category mismatch and asks them to redo. Each round of back-and-forth is another evening they don't have. The available expense tools present categorization screens, FX-rate prompts, and approval flows; the gap between what the traveler can produce on a Saturday afternoon and what finance needs to approve is where the loop lives.
-**Users.** The business traveler reconciling between trips — competent, time-starved, working from a kitchen table with a phone full of receipts. The finance reviewer reads what was submitted and often sends it back; they are a stakeholder, not the target.
-**Cost.** Evenings lost to resubmissions, the next trip approaching with last trip's report still open, reimbursements that lag for weeks, and the slow erosion of any sense that this part of the job is tractable. The traveler is leaving for São Paulo on Sunday. The scope is from the moment a trip ends to the moment the report is approved.</t>
+## Situation
+A traveler is home for two days between business trips. The trip that just ended ran through three countries, with receipts in five formats, photos of meals in a foreign language, an airline charge that hit their card in USD but was billed in EUR, a hotel charge pre-authorized at one amount and posted at another, an Uber auto-uploaded but mis-categorized as personal, and a cash tip paid because the card terminal was broken. They have policy questions — was the upgraded flight reimbursable, what counts as a client meal — and no one to ask quickly.
+## Complication
+They submit. Finance rejects it for a single category mismatch and asks them to redo. Each round of back-and-forth is another evening they don't have. The available expense tools present categorization screens, FX-rate prompts, and approval flows; the gap between what the traveler can produce on a Saturday afternoon and what finance needs to approve is where the loop lives.
+## Users
+The business traveler reconciling between trips — competent, time-starved, working from a kitchen table with a phone full of receipts. The finance reviewer reads what was submitted and often sends it back; they are a stakeholder, not the target.
+## Cost
+Evenings lost to resubmissions, the next trip approaching with last trip's report still open, reimbursements that lag for weeks, and the slow erosion of any sense that this part of the job is tractable. The traveler is leaving for São Paulo on Sunday. The scope is from the moment a trip ends to the moment the report is approved.</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1199,10 +1247,14 @@
       <c r="B14" s="3" t="inlineStr">
         <is>
           <t># A parent finding tutoring for a child struggling in math — design exploration
-**Situation.** A child in 4th, 6th, or 8th grade is struggling in math. The grades have slipped; the teacher has sent a note; the standardized test result came back lower than expected. The parent has a few hours over the next two weeks to set something up, working evenings around their own job and the rest of the family's calendar.
-**Complication.** The parent is facing a tangle of options the landscape currently presents: the local tutoring chain (predictable but expensive, small-group, weekly); a private tutor matched through a friend (variable quality and availability); online tutoring marketplaces and free practice platforms; the school's own intervention program if the kid qualifies; AI-tutor apps that promise personalization. The parent cannot easily tell which option is matched to what works versus what's marketing. They are not the math expert.
-**Users.** A parent–child dyad at the moment of choosing help. The parent is the procurer and decider — scheduling, paying, reading reviews, judging fit. The child is the recipient and the one whose engagement determines whether any of this works; they are sensitive to the framing, since *you need a tutor* can feel like a judgment, and a kid who closes off doesn't learn from anyone. Tutor candidates and school staff are stakeholders the design accommodates, not the target.
-**Cost.** Weeks pass while the parent stalls between bad options; the child falls further behind in a subject that compounds; the wrong choice burns money and the child's willingness to try again. The scope is from "we need help" through "we have a plan and a tutor we trust."</t>
+## Situation
+A child in 4th, 6th, or 8th grade is struggling in math. The grades have slipped; the teacher has sent a note; the standardized test result came back lower than expected. The parent has a few hours over the next two weeks to set something up, working evenings around their own job and the rest of the family's calendar.
+## Complication
+The parent is facing a tangle of options the landscape currently presents: the local tutoring chain (predictable but expensive, small-group, weekly); a private tutor matched through a friend (variable quality and availability); online tutoring marketplaces and free practice platforms; the school's own intervention program if the kid qualifies; AI-tutor apps that promise personalization. The parent cannot easily tell which option is matched to what works versus what's marketing. They are not the math expert.
+## Users
+A parent–child dyad at the moment of choosing help. The parent is the procurer and decider — scheduling, paying, reading reviews, judging fit. The child is the recipient and the one whose engagement determines whether any of this works; they are sensitive to the framing, since *you need a tutor* can feel like a judgment, and a kid who closes off doesn't learn from anyone. Tutor candidates and school staff are stakeholders the design accommodates, not the target.
+## Cost
+Weeks pass while the parent stalls between bad options; the child falls further behind in a subject that compounds; the wrong choice burns money and the child's willingness to try again. The scope is from "we need help" through "we have a plan and a tutor we trust."</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1257,10 +1309,14 @@
       <c r="B15" s="3" t="inlineStr">
         <is>
           <t># Pre-travel prescription preparation — design exploration
-**Situation.** A person is preparing for a long international trip. They take regular prescription medication — an SSRI, an ADHD stimulant, a blood thinner, hormone therapy, a controlled-substance painkiller. They are two weeks out and just realized this is harder than they thought. US prescriptions can't be filled at overseas pharmacies. Several common US medications are restricted or illegal in the country they're going to.
-**Complication.** To carry enough for the trip, they need a vacation override from their insurance, weeks in advance, and probably a prescriber letter. None of that is one phone call. They are working it out across pharmacy phone trees, the insurer's app, the State Department's site, and Reddit threads. Their PCP's office is not set up to answer travel-medication questions. The pharmacy can fill the script if the doctor authorizes the override; the doctor will authorize the override if asked correctly. Nobody owns the work of getting this person across the world with their medication intact, legal, and packaged the way customs expects.
-**Users.** An international traveler on regular, often controlled, prescription medication — a person managing real conditions who needs to keep managing them on the other side of a border. Prescriber, pharmacist, insurer, and customs are stakeholders this work moves through, not the target.
-**Cost.** Consequences run from confiscation at customs to denial of entry to arrest in stricter jurisdictions, plus the quieter failure of running out of medication mid-trip and the destabilization that follows. The scope is the four-week window before international departure.</t>
+## Situation
+A person is preparing for a long international trip. They take regular prescription medication — an SSRI, an ADHD stimulant, a blood thinner, hormone therapy, a controlled-substance painkiller. They are two weeks out and just realized this is harder than they thought. US prescriptions can't be filled at overseas pharmacies. Several common US medications are restricted or illegal in the country they're going to.
+## Complication
+To carry enough for the trip, they need a vacation override from their insurance, weeks in advance, and probably a prescriber letter. None of that is one phone call. They are working it out across pharmacy phone trees, the insurer's app, the State Department's site, and Reddit threads. Their PCP's office is not set up to answer travel-medication questions. The pharmacy can fill the script if the doctor authorizes the override; the doctor will authorize the override if asked correctly. Nobody owns the work of getting this person across the world with their medication intact, legal, and packaged the way customs expects.
+## Users
+An international traveler on regular, often controlled, prescription medication — a person managing real conditions who needs to keep managing them on the other side of a border. Prescriber, pharmacist, insurer, and customs are stakeholders this work moves through, not the target.
+## Cost
+Consequences run from confiscation at customs to denial of entry to arrest in stricter jurisdictions, plus the quieter failure of running out of medication mid-trip and the destabilization that follows. The scope is the four-week window before international departure.</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1300,10 +1356,14 @@
       <c r="B16" s="3" t="inlineStr">
         <is>
           <t># Finding a primary care doctor after relocating — design exploration
-**Situation.** A person has moved to a new city and needs a primary care doctor. They have insurance, and their plan's website hands them an in-network directory — several hundred names, sorted by ZIP code. The directory shows specialties and addresses. It rarely shows which practices are accepting new patients, what the next available appointment actually is, which clinicians speak the languages spoken in the patient's household, whether the office is wheelchair-accessible, or how the practice handles diabetes care, mental-health needs, or pregnancy.
-**Complication.** The patient calls one office, sits on hold for ten minutes, navigates a phone tree, and is told the next opening is in five months — or that the practice isn't accepting new patients at all. Then the next call. Then the next. The options they are choosing between in the landscape today include the in-network directory itself, telehealth services their plan covers, federally-qualified health centers in the area, and direct primary care practices that bill outside insurance — none of which the directory surfaces side-by-side.
-**Users.** A patient looking for a primary care doctor in a new city. Some have active conditions — chronic pain, diabetes, anxiety — and need to start care now; others are establishing routine care and re-engage only when something goes wrong. The insurance plan, the in-network directory, the practices, and telehealth providers are stakeholder context the design accommodates, not the target.
-**Cost.** Delayed care for people who need it now; undiagnosed conditions for those who give up early; emergency visits for what should have been clinic visits. The scope is from "I need a new doctor" through "I have an appointment booked."</t>
+## Situation
+A person has moved to a new city and needs a primary care doctor. They have insurance, and their plan's website hands them an in-network directory — several hundred names, sorted by ZIP code. The directory shows specialties and addresses. It rarely shows which practices are accepting new patients, what the next available appointment actually is, which clinicians speak the languages spoken in the patient's household, whether the office is wheelchair-accessible, or how the practice handles diabetes care, mental-health needs, or pregnancy.
+## Complication
+The patient calls one office, sits on hold for ten minutes, navigates a phone tree, and is told the next opening is in five months — or that the practice isn't accepting new patients at all. Then the next call. Then the next. The options they are choosing between in the landscape today include the in-network directory itself, telehealth services their plan covers, federally-qualified health centers in the area, and direct primary care practices that bill outside insurance — none of which the directory surfaces side-by-side.
+## Users
+A patient looking for a primary care doctor in a new city. Some have active conditions — chronic pain, diabetes, anxiety — and need to start care now; others are establishing routine care and re-engage only when something goes wrong. The insurance plan, the in-network directory, the practices, and telehealth providers are stakeholder context the design accommodates, not the target.
+## Cost
+Delayed care for people who need it now; undiagnosed conditions for those who give up early; emergency visits for what should have been clinic visits. The scope is from "I need a new doctor" through "I have an appointment booked."</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1344,10 +1404,14 @@
       <c r="B17" s="3" t="inlineStr">
         <is>
           <t># Remote new-hire onboarding, week one — design exploration
-**Situation.** A competent professional joins a remote-first company on Monday. They have never met their team in person. They've done this before — they know how to set up a laptop and learn a new codebase. The HR-built first week is nine meetings Monday, six Tuesday; a stack of documentation; a Notion they still can't fully access; benefits links, security trainings, and a Slack workspace with a hundred channels.
-**Complication.** What's hard isn't the work; it's everything around it. They don't know this team's norms, this manager's actual (not stated) preferences, who is the person you actually ask about benefits. Remote replaces the watercooler, the lunch tag-along, and the overheard standup with calendar invites — which aren't the same thing. By Wednesday the orientation rush slows; by Thursday they're alone with documentation and unsure who to ask what, anxious about asking questions that would mark them as not-yet-onboard.
-**Users.** The new hire — a competent professional starting cold inside a remote-first company, navigating their first five working days from a home desk. The hiring manager, peers on the team, HR, and IT provisioning are stakeholders whose work shapes the week but who are not the target of the design.
-**Cost.** The five-day window from joining to belonging is where the relationship is made or lost; new hires who don't feel onboard by Friday carry that uncertainty into the next month, hesitate to ask, and quietly disengage. Companies bleed early-tenure hires at exactly this point. The scope is the first five working days, Monday morning to Friday afternoon.</t>
+## Situation
+A competent professional joins a remote-first company on Monday. They have never met their team in person. They've done this before — they know how to set up a laptop and learn a new codebase. The HR-built first week is nine meetings Monday, six Tuesday; a stack of documentation; a Notion they still can't fully access; benefits links, security trainings, and a Slack workspace with a hundred channels.
+## Complication
+What's hard isn't the work; it's everything around it. They don't know this team's norms, this manager's actual (not stated) preferences, who is the person you actually ask about benefits. Remote replaces the watercooler, the lunch tag-along, and the overheard standup with calendar invites — which aren't the same thing. By Wednesday the orientation rush slows; by Thursday they're alone with documentation and unsure who to ask what, anxious about asking questions that would mark them as not-yet-onboard.
+## Users
+The new hire — a competent professional starting cold inside a remote-first company, navigating their first five working days from a home desk. The hiring manager, peers on the team, HR, and IT provisioning are stakeholders whose work shapes the week but who are not the target of the design.
+## Cost
+The five-day window from joining to belonging is where the relationship is made or lost; new hires who don't feel onboard by Friday carry that uncertainty into the next month, hesitate to ask, and quietly disengage. Companies bleed early-tenure hires at exactly this point. The scope is the first five working days, Monday morning to Friday afternoon.</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1402,10 +1466,14 @@
       <c r="B18" s="3" t="inlineStr">
         <is>
           <t># A sprint retro after a missed target — design exploration
-**Situation.** A product team has just finished a two-week sprint and missed what they committed to. The scrum master has forty-five minutes booked on Friday afternoon for the retrospective. The team is tired, the engineer who carried the cancelled feature is quiet on the call, the PM is reading their phone, and the VP of Engineering is on the line listening in. The scrum master has a Miro board with three columns and a stack of sticky notes their team has used in some version for the last two years.
-**Complication.** The team's existing tools — Miro templates, FunRetro, EasyRetro, the Jira retro module — capture sticky notes and let people upvote them. What happens between "sticky notes captured" and "the team had a real conversation" sits outside those tools. The team itself is uneven: some members will say what they think directly, some won't say anything that could read as criticism with the PM in the room, and some will narrate the sprint as if it went fine.
-**Users.** The scrum master is the target user — the one prepping the meeting, holding the room, and chasing follow-through. The team is the design's audience; the PM in the room and the VP listening in are stakeholders the meeting accommodates.
-**Cost.** A retro that doesn't land after a missed sprint compounds: the same patterns carry into the next sprint, action items are forgotten by Monday, and the team grows a little more cynical about whether retros are worth showing up to. A retro that does land is something the team can feel for weeks. The scope is the retrospective meeting itself, the prep before it, and the follow-through.</t>
+## Situation
+A product team has just finished a two-week sprint and missed what they committed to. The scrum master has forty-five minutes booked on Friday afternoon for the retrospective. The team is tired, the engineer who carried the cancelled feature is quiet on the call, the PM is reading their phone, and the VP of Engineering is on the line listening in. The scrum master has a Miro board with three columns and a stack of sticky notes their team has used in some version for the last two years.
+## Complication
+The team's existing tools — Miro templates, FunRetro, EasyRetro, the Jira retro module — capture sticky notes and let people upvote them. What happens between "sticky notes captured" and "the team had a real conversation" sits outside those tools. The team itself is uneven: some members will say what they think directly, some won't say anything that could read as criticism with the PM in the room, and some will narrate the sprint as if it went fine.
+## Users
+The scrum master is the target user — the one prepping the meeting, holding the room, and chasing follow-through. The team is the design's audience; the PM in the room and the VP listening in are stakeholders the meeting accommodates.
+## Cost
+A retro that doesn't land after a missed sprint compounds: the same patterns carry into the next sprint, action items are forgotten by Monday, and the team grows a little more cynical about whether retros are worth showing up to. A retro that does land is something the team can feel for weeks. The scope is the retrospective meeting itself, the prep before it, and the follow-through.</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1446,10 +1514,14 @@
       <c r="B19" s="3" t="inlineStr">
         <is>
           <t># Applying for food assistance — design exploration
-**Situation.** Someone who needs food assistance now is sitting down to apply for SNAP. They've lost a job, had hours cut, gotten sick, or are raising a kid on inconsistent income. They are working from a phone, sometimes a shared one, often on intermittent data.
-**Complication.** The form in front of them asks branching questions whose answers depend on context the form does not let them explain, requires documents they can't easily produce in the moment (a recent pay stub from a gig that pays inconsistently, a lease they don't have a copy of, a Social Security card from a drawer at a place they no longer live), and was built to be filled out on a desktop computer they don't own. After they submit, the experience goes quiet. They don't know if the application was received, is being processed, is waiting on a document the system has not asked for, or has already been denied.
-**Users.** The target user is the applicant: a first-time applicant who has never used the safety net, a mixed-status family weighing whether the application itself will be used against them, or someone returning under worse circumstances than the first time. State eligibility workers who process and adjudicate these applications are stakeholders, not the target.
-**Cost.** Days pass. The food situation that brought them here doesn't pause. Many people in this position get one attempt before they stop trying — not from a single rejection, but from the cumulative weight of submitting into silence while the rest of their life keeps moving. What we want: distinct strategic directions for what a humane food-assistance application could be when designed around the applicant.</t>
+## Situation
+Someone who needs food assistance now is sitting down to apply for SNAP. They've lost a job, had hours cut, gotten sick, or are raising a kid on inconsistent income. They are working from a phone, sometimes a shared one, often on intermittent data.
+## Complication
+The form in front of them asks branching questions whose answers depend on context the form does not let them explain, requires documents they can't easily produce in the moment (a recent pay stub from a gig that pays inconsistently, a lease they don't have a copy of, a Social Security card from a drawer at a place they no longer live), and was built to be filled out on a desktop computer they don't own. After they submit, the experience goes quiet. They don't know if the application was received, is being processed, is waiting on a document the system has not asked for, or has already been denied.
+## Users
+The target user is the applicant: a first-time applicant who has never used the safety net, a mixed-status family weighing whether the application itself will be used against them, or someone returning under worse circumstances than the first time. State eligibility workers who process and adjudicate these applications are stakeholders, not the target.
+## Cost
+Days pass. The food situation that brought them here doesn't pause. Many people in this position get one attempt before they stop trying — not from a single rejection, but from the cumulative weight of submitting into silence while the rest of their life keeps moving. What we want: distinct strategic directions for what a humane food-assistance application could be when designed around the applicant.</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1504,10 +1576,14 @@
       <c r="B20" s="3" t="inlineStr">
         <is>
           <t># The first 90 days after a Type 2 diabetes diagnosis — design exploration
-**Situation.** A person has just been told they have Type 2 diabetes. The diagnosis arrived in a fifteen-minute appointment with a handout, a prescription for metformin, and instructions to "watch your sugars" and to "see a nutritionist." They walk out scared, ashamed, confused about whether they caused this, and facing a slate of changes — diet, exercise, medication, glucose monitoring, A1c labs every three months.
-**Complication.** No one helps them sequence those changes. The nutritionist referral is a phone number on the printout. The diabetes self-management education and support sessions their insurance covers are not mentioned at the appointment. The landscape they encounter when they look for help — glucose-logging utilities, coaching platforms (Livongo, Virta, Omada), peer-support communities, and YouTube videos from creators of varying authority — tends to ask them to log their glucose on day one. None of it is shaped around the moment of diagnosis itself: the week they are still telling family, the week they are deciding whether to tell work.
-**Users.** The target user is the newly-diagnosed patient in the first 90 days. The clinician and the nutritionist are stakeholders the design accommodates — referrals come from them, labs route through them — but are not who the design is for.
-**Cost.** By the end of the next ninety days they will have either built a workable rhythm — meals, walking, the morning metformin, the glucose meter sitting on the kitchen counter — or they will have drifted: meter in a drawer, prescription unfilled at refill time, weight unchanged, and no further appointment booked until the next labs flag something. The scope is from diagnosis through the 90-day mark.</t>
+## Situation
+A person has just been told they have Type 2 diabetes. The diagnosis arrived in a fifteen-minute appointment with a handout, a prescription for metformin, and instructions to "watch your sugars" and to "see a nutritionist." They walk out scared, ashamed, confused about whether they caused this, and facing a slate of changes — diet, exercise, medication, glucose monitoring, A1c labs every three months.
+## Complication
+No one helps them sequence those changes. The nutritionist referral is a phone number on the printout. The diabetes self-management education and support sessions their insurance covers are not mentioned at the appointment. The landscape they encounter when they look for help — glucose-logging utilities, coaching platforms (Livongo, Virta, Omada), peer-support communities, and YouTube videos from creators of varying authority — tends to ask them to log their glucose on day one. None of it is shaped around the moment of diagnosis itself: the week they are still telling family, the week they are deciding whether to tell work.
+## Users
+The target user is the newly-diagnosed patient in the first 90 days. The clinician and the nutritionist are stakeholders the design accommodates — referrals come from them, labs route through them — but are not who the design is for.
+## Cost
+By the end of the next ninety days they will have either built a workable rhythm — meals, walking, the morning metformin, the glucose meter sitting on the kitchen counter — or they will have drifted: meter in a drawer, prescription unfilled at refill time, weight unchanged, and no further appointment booked until the next labs flag something. The scope is from diagnosis through the 90-day mark.</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1547,10 +1623,14 @@
       <c r="B21" s="3" t="inlineStr">
         <is>
           <t># Filing for unemployment insurance — design exploration
-**Situation.** A person has just lost their job and is filing for unemployment insurance through their state's labor agency. They may have a few weeks of rent in the bank or none. They are filling out the application on a phone — in line at a job center, between caregiving shifts, or late at night after the kids are asleep.
-**Complication.** The application asks for an EDDCAN number they have never heard of, pay stubs from the last eighteen months they may not have saved, and the precise dates and hours of every job worked in a base period that doesn't match how variable-schedule work happens. The legalese is dense. A wrong answer on any of dozens of questions delays or denies the claim, and the appeal that follows takes weeks. Once filed, the channels for finding out what's happening are a state portal that often shows information weeks out of date, paper letters that arrive after the next pay period would have been due, and a phone line that holds for hours. The portal sometimes says the claim is being processed; sometimes nothing at all.
-**Users.** The target user is the claimant — filing and waiting on benefits they are entitled to under state and federal law. State eligibility workers and adjudicators are stakeholders, not the target.
-**Cost.** Money does not arrive on a schedule the person can plan around. Rent is due, the car insurance lapses, the kid needs school supplies. The gap between filing and the first payment landing is where the urgency of the situation collides with what the system communicates. The scope is the filing flow plus the first thirty days of claim-status communication.</t>
+## Situation
+A person has just lost their job and is filing for unemployment insurance through their state's labor agency. They may have a few weeks of rent in the bank or none. They are filling out the application on a phone — in line at a job center, between caregiving shifts, or late at night after the kids are asleep.
+## Complication
+The application asks for an EDDCAN number they have never heard of, pay stubs from the last eighteen months they may not have saved, and the precise dates and hours of every job worked in a base period that doesn't match how variable-schedule work happens. The legalese is dense. A wrong answer on any of dozens of questions delays or denies the claim, and the appeal that follows takes weeks. Once filed, the channels for finding out what's happening are a state portal that often shows information weeks out of date, paper letters that arrive after the next pay period would have been due, and a phone line that holds for hours. The portal sometimes says the claim is being processed; sometimes nothing at all.
+## Users
+The target user is the claimant — filing and waiting on benefits they are entitled to under state and federal law. State eligibility workers and adjudicators are stakeholders, not the target.
+## Cost
+Money does not arrive on a schedule the person can plan around. Rent is due, the car insurance lapses, the kid needs school supplies. The gap between filing and the first payment landing is where the urgency of the situation collides with what the system communicates. The scope is the filing flow plus the first thirty days of claim-status communication.</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1590,10 +1670,14 @@
       <c r="B22" s="3" t="inlineStr">
         <is>
           <t># Updating voter registration after a name change — design exploration
-**Situation.** A person has changed their legal name — after marriage, divorce, gender transition, leaving an abusive relationship, or by personal choice. Their old name is on the voter roll. The next election is months away. Someone told them they should update their registration; they don't know whether they need to, by when, what proof, or how their state's rules differ from a friend's in another state.
-**Complication.** The state election-board website is a tangle of pages and PDFs that don't quite match their situation. Voter registration sits inside a long list of bureaucratic to-dos the name change has triggered — driver's license, Social Security card, employer records, banking, passports — and is the one most likely to be skipped until election day.
-**Users.** The target user is the voter mid-name-change: a trans person whose ID is finally catching up to their name, a domestic-violence survivor who changed their name for safety, a recently-married or recently-divorced voter, or someone who chose a new name. Each comes with different proof, different timelines, and different concerns about who sees the old name during the update. Election-board staff and poll workers are stakeholders, not the target.
-**Cost.** On election day, the name fails the poll-book check and they're asked to cast a provisional ballot they may not return to cure. A vote they were entitled to cast doesn't count, and being challenged at the table — especially for trans voters or survivors whose old name is read aloud — can make them less likely to return. The scope is updating registration plus the ambiguity around it — *do I need to, when by, what proof, will this be wrong on election day.*</t>
+## Situation
+A person has changed their legal name — after marriage, divorce, gender transition, leaving an abusive relationship, or by personal choice. Their old name is on the voter roll. The next election is months away. Someone told them they should update their registration; they don't know whether they need to, by when, what proof, or how their state's rules differ from a friend's in another state.
+## Complication
+The state election-board website is a tangle of pages and PDFs that don't quite match their situation. Voter registration sits inside a long list of bureaucratic to-dos the name change has triggered — driver's license, Social Security card, employer records, banking, passports — and is the one most likely to be skipped until election day.
+## Users
+The target user is the voter mid-name-change: a trans person whose ID is finally catching up to their name, a domestic-violence survivor who changed their name for safety, a recently-married or recently-divorced voter, or someone who chose a new name. Each comes with different proof, different timelines, and different concerns about who sees the old name during the update. Election-board staff and poll workers are stakeholders, not the target.
+## Cost
+On election day, the name fails the poll-book check and they're asked to cast a provisional ballot they may not return to cure. A vote they were entitled to cast doesn't count, and being challenged at the table — especially for trans voters or survivors whose old name is read aloud — can make them less likely to return. The scope is updating registration plus the ambiguity around it — *do I need to, when by, what proof, will this be wrong on election day.*</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">

--- a/experiments/corpus-content.xlsx
+++ b/experiments/corpus-content.xlsx
@@ -503,14 +503,10 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t># Apartment search for a renter with a past eviction — design exploration
-## Situation
-A person with an eviction record is looking for a new place to live. The eviction may have followed a job loss, a medical event, or a dispute with a prior landlord — sometimes a dismissed filing, sometimes a filing-in-error, sometimes a completed eviction-for-cause. The renter has since rebuilt: a job, references, money for a deposit. What reaches the landlord is a tenant-screening report — bundling rental, credit, employment, and criminal history into a score — on which the filing looks the same whether the case was won, lost, or dismissed.
-## Complication
-The renter pays application fees at every listing and discovers, sometimes days later, that they have been declined. They get back a vague "did not meet screening criteria" or no explanation at all. There is no path to find out which factor produced the decline, no path to contest a record they believe is inaccurate. They confront listing aggregators, screening companies whose reports they cannot see, bureau disputes that move slowly, and legal-aid offices whose capacity does not meet the volume.
-## Users
-The renter with the eviction record on their file. Landlords and screening companies are stakeholders, not the target — the design is for the renter with weeks, not months, and a stack of declined applications. Scope is "I'm looking" through "I've signed a lease."
-## Cost
-They need to be housed in the weeks they have, not the months a dispute would take. Fees stack up against a deposit they are trying to keep intact. Each decline arrives without enough information to act on, and the next listing goes up against the same report. The current housing is running out or already gone.</t>
+**Situation.** A person with an eviction record is looking for a new place to live. The eviction may have followed a job loss, a medical event, or a dispute with a prior landlord — sometimes a dismissed filing, sometimes a filing-in-error, sometimes a completed eviction-for-cause. The renter has since rebuilt: a job, references, money for a deposit. What reaches the landlord is a tenant-screening report — bundling rental, credit, employment, and criminal history into a score — on which the filing looks the same whether the case was won, lost, or dismissed.
+**Complication.** The renter pays application fees at every listing and discovers, sometimes days later, that they have been declined. They get back a vague "did not meet screening criteria" or no explanation at all. There is no path to find out which factor produced the decline, no path to contest a record they believe is inaccurate. They confront listing aggregators, screening companies whose reports they cannot see, bureau disputes that move slowly, and legal-aid offices whose capacity does not meet the volume.
+**Users.** The renter with the eviction record on their file. Landlords and screening companies are stakeholders, not the target — the design is for the renter with weeks, not months, and a stack of declined applications. Scope is "I'm looking" through "I've signed a lease."
+**Cost.** They need to be housed in the weeks they have, not the months a dispute would take. Fees stack up against a deposit they are trying to keep intact. Each decline arrives without enough information to act on, and the next listing goes up against the same report. The current housing is running out or already gone.</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -566,14 +562,10 @@
       <c r="B3" s="3" t="inlineStr">
         <is>
           <t># Coordinating care for an aging parent — design exploration
-## Situation
-An adult child is responsible for the day-to-day care of an aging parent in another city. They are working full-time, may be raising their own kids, and are now also managing their parent's medications, appointments, insurance disputes, in-home aide schedule, finances, and longer-term decisions about home modifications, assisted living, or hospice — with sibling involvement that ranges from supportive to fractious.
-## Complication
-The information lives everywhere — their own phone, their email, the parent's hand-written notes on a yellow pad by the kitchen phone, the parent's doctor's portals (three or four, each with its own login), Medicare statements, the aide's notebook, the pharmacy's text messages. No system holds the picture; the caregiver holds it, in their head, between work meetings and bedtime. The new prescription started last Thursday is supposed to be checked against the cardiologist's older one that may or may not have been discontinued. The PCP's portal does not show the cardiologist's prescriptions. The aide's notebook is three hundred miles away.
-## Users
-The adult-child caregiver and the aging parent, as a dyad — the parent in their own apartment, the caregiver coordinating from three hundred miles away. Siblings, aides, doctors, and pharmacists are stakeholders the design accommodates, not optimizes for. Scope is the rhythm of a month, not a single appointment.
-## Cost
-When something goes wrong — a missed medication, a duplicate dose, an ED visit that looks preventable in hindsight — the gap was between systems the caregiver was supposed to bridge across. The parent absorbs the errors when the picture slips. The work eats evenings, weekends, and the bandwidth left for everything else in the caregiver's life.</t>
+**Situation.** An adult child is responsible for the day-to-day care of an aging parent in another city. They are working full-time, may be raising their own kids, and are now also managing their parent's medications, appointments, insurance disputes, in-home aide schedule, finances, and longer-term decisions about home modifications, assisted living, or hospice — with sibling involvement that ranges from supportive to fractious.
+**Complication.** The information lives everywhere — their own phone, their email, the parent's hand-written notes on a yellow pad by the kitchen phone, the parent's doctor's portals (three or four, each with its own login), Medicare statements, the aide's notebook, the pharmacy's text messages. No system holds the picture; the caregiver holds it, in their head, between work meetings and bedtime. The new prescription started last Thursday is supposed to be checked against the cardiologist's older one that may or may not have been discontinued. The PCP's portal does not show the cardiologist's prescriptions. The aide's notebook is three hundred miles away.
+**Users.** The adult-child caregiver and the aging parent, as a dyad — the parent in their own apartment, the caregiver coordinating from three hundred miles away. Siblings, aides, doctors, and pharmacists are stakeholders the design accommodates, not optimizes for. Scope is the rhythm of a month, not a single appointment.
+**Cost.** When something goes wrong — a missed medication, a duplicate dose, an ED visit that looks preventable in hindsight — the gap was between systems the caregiver was supposed to bridge across. The parent absorbs the errors when the picture slips. The work eats evenings, weekends, and the bandwidth left for everything else in the caregiver's life.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -629,14 +621,10 @@
       <c r="B4" s="3" t="inlineStr">
         <is>
           <t># An adult learner re-entering community college — design exploration
-## Situation
-An adult — twenty-five, thirty-five, fifty — has enrolled at community college, often after years away from formal schooling. They've decided to re-enroll for a new credential, an industry switch, or developmental coursework before a four-year transfer. They've signed up; they haven't started. They have a job that won't easily flex, kids who need pick-up, and the cognitive disjuncture of being asked to think like a student again after years of not being one.
-## Complication
-They are trying to read a college website built for eighteen-year-olds applying for fall. They are unsure where to park, what to bring to orientation, whether the FAFSA they filled out applies to summer term, whether they can register part-time without losing the financial-aid bracket, and how to reach an advisor who answers in less than two weeks.
-## Users
-The adult learner re-entering community college after years away — not the eighteen-year-old applying for fall, and not the returner with a working campus rhythm. Advisors, financial-aid officers, and registrars are stakeholders the design encounters, not optimizes for. Scope is the eight-week window from "I've enrolled" through "I've completed the first month of classes."
-## Cost
-The first month is where the workable rhythm either gets built or doesn't. When the answers don't arrive in the window — when orientation feels alien, when the FAFSA question goes two weeks without a reply, when the parking and pick-up logistics don't line up — the learner quietly stops coming. The enrollment becomes another unfinished credential, the tuition becomes a sunk cost, and the next attempt is years out.</t>
+**Situation.** An adult — twenty-five, thirty-five, fifty — has enrolled at community college, often after years away from formal schooling. They've decided to re-enroll for a new credential, an industry switch, or developmental coursework before a four-year transfer. They've signed up; they haven't started. They have a job that won't easily flex, kids who need pick-up, and the cognitive disjuncture of being asked to think like a student again after years of not being one.
+**Complication.** They are trying to read a college website built for eighteen-year-olds applying for fall. They are unsure where to park, what to bring to orientation, whether the FAFSA they filled out applies to summer term, whether they can register part-time without losing the financial-aid bracket, and how to reach an advisor who answers in less than two weeks.
+**Users.** The adult learner re-entering community college after years away — not the eighteen-year-old applying for fall, and not the returner with a working campus rhythm. Advisors, financial-aid officers, and registrars are stakeholders the design encounters, not optimizes for. Scope is the eight-week window from "I've enrolled" through "I've completed the first month of classes."
+**Cost.** The first month is where the workable rhythm either gets built or doesn't. When the answers don't arrive in the window — when orientation feels alien, when the FAFSA question goes two weeks without a reply, when the parking and pick-up logistics don't line up — the learner quietly stops coming. The enrollment becomes another unfinished credential, the tuition becomes a sunk cost, and the next attempt is years out.</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -691,14 +679,10 @@
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t># Disputing a credit-report error — design exploration
-## Situation
-A person has been denied an apartment, a job, a loan, or an insurance rate because of something on their credit report — and the something is wrong. A debt they paid years ago. An account opened in their name fraudulently. Identity confusion with a relative who shares their name. They have proof — receipts, closure letters, identity-theft affidavits — and no clear path to get it to the right place.
-## Complication
-They face three different dispute interfaces, one per bureau, each demanding documentation in slightly different formats and each capable of returning a one-line "investigated, no change" weeks later. They are unsure whether to write a paper letter, use the online portals, file directly with the furnisher, file a CFPB complaint, or do all four. The original error often reappears later from a different furnisher, and the consumer is back at the same three logins, the same documentation queue, the same wait. They confront the bureaus' portals, free-credit-report sites that funnel toward paid monitoring, the CFPB channel, IdentityTheft.gov, and legal-aid whose capacity does not meet the volume.
-## Users
-The consumer disputing the error — the one with receipts and closure letters in hand. Bureaus, furnishers, and CFPB intake staff are stakeholders, not the target. Scope is from noticing the error through resolution.
-## Cost
-The process unfolds over thirty to ninety days while the apartment application sits in limbo and the new job offer is on hold. The denial that prompted the dispute does not pause for resolution. When the error reappears from a different furnisher, the consumer is back at the same three logins, doing the work again on a life that has moved on.</t>
+**Situation.** A person has been denied an apartment, a job, a loan, or an insurance rate because of something on their credit report — and the something is wrong. A debt they paid years ago. An account opened in their name fraudulently. Identity confusion with a relative who shares their name. They have proof — receipts, closure letters, identity-theft affidavits — and no clear path to get it to the right place.
+**Complication.** They face three different dispute interfaces, one per bureau, each demanding documentation in slightly different formats and each capable of returning a one-line "investigated, no change" weeks later. They are unsure whether to write a paper letter, use the online portals, file directly with the furnisher, file a CFPB complaint, or do all four. The original error often reappears later from a different furnisher, and the consumer is back at the same three logins, the same documentation queue, the same wait. They confront the bureaus' portals, free-credit-report sites that funnel toward paid monitoring, the CFPB channel, IdentityTheft.gov, and legal-aid whose capacity does not meet the volume.
+**Users.** The consumer disputing the error — the one with receipts and closure letters in hand. Bureaus, furnishers, and CFPB intake staff are stakeholders, not the target. Scope is from noticing the error through resolution.
+**Cost.** The process unfolds over thirty to ninety days while the apartment application sits in limbo and the new job offer is on hold. The denial that prompted the dispute does not pause for resolution. When the error reappears from a different furnisher, the consumer is back at the same three logins, doing the work again on a life that has moved on.</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -753,14 +737,10 @@
       <c r="B6" s="3" t="inlineStr">
         <is>
           <t># First contact with 988, the crisis line — design exploration
-## Situation
-Someone is reaching out to the US crisis line — 988 — for the first time. They may be experiencing a suicidal crisis, an acute panic episode, a substance-use crisis, or distress around grief, abuse, or identity. They may be the person in crisis, or a friend or family member trying to help someone else. They are reaching out at a moment of acute vulnerability and have a choice to make about whether to stay on the line.
-## Complication
-The first sixty seconds are determinative. What does this look like; will I be judged; what's about to happen; will police be sent to my address if I say the wrong thing. People who have heard that police might be dispatched are hesitant in ways the system has to meet; people who have never reached out before are calibrating from the screen, the voice, the hold music. The decision to keep reaching, or to hang up and not try again, is made before anyone has said anything.
-## Users
-The first-time reacher — the person in crisis, or the friend or family member calling on their behalf — in the opening seconds before a counselor has spoken. Counselors and dispatchers are stakeholders the design hands off to, not optimizes for. Scope is the call, text, or chat opening plus the immediate next step; the counselor protocol itself is out of scope.
-## Cost
-When the first sixty seconds don't hold, the person hangs up and does not try again. The next acute moment arrives without a line they trust. The friend who was calling for someone else goes back with nothing to offer.</t>
+**Situation.** Someone is reaching out to the US crisis line — 988 — for the first time. They may be experiencing a suicidal crisis, an acute panic episode, a substance-use crisis, or distress around grief, abuse, or identity. They may be the person in crisis, or a friend or family member trying to help someone else. They are reaching out at a moment of acute vulnerability and have a choice to make about whether to stay on the line.
+**Complication.** The first sixty seconds are determinative. What does this look like; will I be judged; what's about to happen; will police be sent to my address if I say the wrong thing. People who have heard that police might be dispatched are hesitant in ways the system has to meet; people who have never reached out before are calibrating from the screen, the voice, the hold music. The decision to keep reaching, or to hang up and not try again, is made before anyone has said anything.
+**Users.** The first-time reacher — the person in crisis, or the friend or family member calling on their behalf — in the opening seconds before a counselor has spoken. Counselors and dispatchers are stakeholders the design hands off to, not optimizes for. Scope is the call, text, or chat opening plus the immediate next step; the counselor protocol itself is out of scope.
+**Cost.** When the first sixty seconds don't hold, the person hangs up and does not try again. The next acute moment arrives without a line they trust. The friend who was calling for someone else goes back with nothing to offer.</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -814,14 +794,10 @@
       <c r="B7" s="3" t="inlineStr">
         <is>
           <t># Closing a deceased family member's accounts — design exploration
-## Situation
-When a person dies, someone in the family inherits an administrative ordeal nobody trained them for. They are the executor — spouse, adult child, sibling — and now need to identify, contact, and close out dozens of accounts: banks, credit cards, utilities, mortgages, retirement accounts, insurance, Social Security, and a digital life of email and photos and subscriptions. They are doing this in the evenings, between the funeral and the rest of life — often from a different city than the deceased, with a death certificate in hand and a stack of unopened mail.
-## Complication
-Each institution has its own forms, its own definitions, its own staff. Debt collectors begin calling within days; most are wrong about what the survivor owes, but the conversations are intimidating and the rules vary by state. The available resources are accurate and encyclopedic; they list eighty things the executor might need to do, with no way to know which twelve apply today.
-## Users
-The executor — spouse, adult child, or sibling — grieving and doing this because someone had to be. Institutions and debt collectors are stakeholders, not the design's target. Scope is from the first week through final dissolution.
-## Cost
-The work runs in the evenings on top of grief, on top of a job, on top of a household that did not pause. The encyclopedic list does not tell the executor which twelve of eighty steps belong to today, so the wrong ones get done first or none at all. The collectors' calls keep coming. The estate stays open, the mail keeps arriving, and the grief is interrupted every time the ordeal reasserts itself.</t>
+**Situation.** When a person dies, someone in the family inherits an administrative ordeal nobody trained them for. They are the executor — spouse, adult child, sibling — and now need to identify, contact, and close out dozens of accounts: banks, credit cards, utilities, mortgages, retirement accounts, insurance, Social Security, and a digital life of email and photos and subscriptions. They are doing this in the evenings, between the funeral and the rest of life — often from a different city than the deceased, with a death certificate in hand and a stack of unopened mail.
+**Complication.** Each institution has its own forms, its own definitions, its own staff. Debt collectors begin calling within days; most are wrong about what the survivor owes, but the conversations are intimidating and the rules vary by state. The available resources are accurate and encyclopedic; they list eighty things the executor might need to do, with no way to know which twelve apply today.
+**Users.** The executor — spouse, adult child, or sibling — grieving and doing this because someone had to be. Institutions and debt collectors are stakeholders, not the design's target. Scope is from the first week through final dissolution.
+**Cost.** The work runs in the evenings on top of grief, on top of a job, on top of a household that did not pause. The encyclopedic list does not tell the executor which twelve of eighty steps belong to today, so the wrong ones get done first or none at all. The collectors' calls keep coming. The estate stays open, the mail keeps arriving, and the grief is interrupted every time the ordeal reasserts itself.</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -875,14 +851,10 @@
       <c r="B8" s="3" t="inlineStr">
         <is>
           <t># Driver's license transfer after a cross-state move — design exploration
-## Situation
-A person has moved from one US state to another. They have a job to start, an apartment to unpack, a kid in a new school. Somewhere on the list is "transfer the driver's license," and the new state's DMV site is a tangle of pages that don't quite match the user's situation: out-of-state transfer vs new resident vs non-citizen vs recently-licensed teen. They have a stack of documents — birth certificate, Social Security card, lease, utility bill, old license, marriage certificate.
-## Complication
-They aren't sure which documents the office will accept on the day. They want to know when to go, what to bring, what the visit will feel like, and what happens if something goes wrong. The DMV won't tell them ahead of time. The mover does the visit, leaves with a temporary paper printout, and waits weeks for the hard copy in the mail. In the meantime they aren't sure whether the paper is enough to fly, open a bank account, or pass any other ID check.
-## Users
-A recent mover in the four-to-six-week window after a cross-state move, navigating the new state's DMV alone with a folder of documents and other life on fire.
-## Cost
-Getting any of this wrong costs another visit, another day of work missed, and the same lack of information about what's next. The scope is the four-to-six-week window after a move during which the license needs to transfer.</t>
+**Situation.** A person has moved from one US state to another. They have a job to start, an apartment to unpack, a kid in a new school. Somewhere on the list is "transfer the driver's license," and the new state's DMV site is a tangle of pages that don't quite match the user's situation: out-of-state transfer vs new resident vs non-citizen vs recently-licensed teen. They have a stack of documents — birth certificate, Social Security card, lease, utility bill, old license, marriage certificate.
+**Complication.** They aren't sure which documents the office will accept on the day. They want to know when to go, what to bring, what the visit will feel like, and what happens if something goes wrong. The DMV won't tell them ahead of time. The mover does the visit, leaves with a temporary paper printout, and waits weeks for the hard copy in the mail. In the meantime they aren't sure whether the paper is enough to fly, open a bank account, or pass any other ID check.
+**Users.** A recent mover in the four-to-six-week window after a cross-state move, navigating the new state's DMV alone with a folder of documents and other life on fire.
+**Cost.** Getting any of this wrong costs another visit, another day of work missed, and the same lack of information about what's next. The scope is the four-to-six-week window after a move during which the license needs to transfer.</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -935,14 +907,10 @@
       <c r="B9" s="3" t="inlineStr">
         <is>
           <t># A first-time manager's first performance review — design exploration
-## Situation
-Someone who has been a people manager for less than a year sits down at midnight to write their first performance review of an employee. They have nine weeks of notes — most of them mental — and a template HR handed down with fifteen sections and a five-point rating scale. They are also navigating a calibration cycle in which their ratings will be compared against peer managers' ratings, with rules they only half-understand.
-## Complication
-The performance-management software they're using delivers prompts and templates but does not actually help them think through what to say to this specific person about this specific thing. They are scared of doing harm. Of giving feedback that lands wrong. Of being too soft and ducking the real issue. Of being too critical and damaging a working relationship. They are alone with a form and a blinking cursor.
-## Users
-A first-time people manager writing their first review of a direct report — who might be a former peer, someone they hired, or someone with more years in the industry than they have. HR and the calibration committee are stakeholders the manager has to satisfy, but the design is for the manager in the moment of writing.
-## Cost
-The cost of getting this wrong is paid both at the next 1:1 and across the year that follows — a damaged working relationship, a real issue ducked, or feedback that lands so wrong it forecloses growth. The scope is the act of writing the review — the hours between *I have to write this* and *I have a draft I'd send.*</t>
+**Situation.** Someone who has been a people manager for less than a year sits down at midnight to write their first performance review of an employee. They have nine weeks of notes — most of them mental — and a template HR handed down with fifteen sections and a five-point rating scale. They are also navigating a calibration cycle in which their ratings will be compared against peer managers' ratings, with rules they only half-understand.
+**Complication.** The performance-management software they're using delivers prompts and templates but does not actually help them think through what to say to this specific person about this specific thing. They are scared of doing harm. Of giving feedback that lands wrong. Of being too soft and ducking the real issue. Of being too critical and damaging a working relationship. They are alone with a form and a blinking cursor.
+**Users.** A first-time people manager writing their first review of a direct report — who might be a former peer, someone they hired, or someone with more years in the industry than they have. HR and the calibration committee are stakeholders the manager has to satisfy, but the design is for the manager in the moment of writing.
+**Cost.** The cost of getting this wrong is paid both at the next 1:1 and across the year that follows — a damaged working relationship, a real issue ducked, or feedback that lands so wrong it forecloses growth. The scope is the act of writing the review — the hours between *I have to write this* and *I have a draft I'd send.*</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -996,14 +964,10 @@
       <c r="B10" s="3" t="inlineStr">
         <is>
           <t># A grief-focused web app — design exploration
-## Situation
-We're scoping a web product for people in active grief. The space today splits roughly three ways: funeral logistics sites (transactional, mostly pre-funeral), peer support communities and subreddits (exposing or noisy for many), and journaling apps that bolt on a "feeling sad" mood tag (toothless). The users we keep hearing from describe wanting something different — something that respects them as someone grieving rather than treating them as a user to be moved through a funnel or a feed.
-## Complication
-People reach for a tool at the awkward moments: 3am, the anniversary, after a hard conversation with a sibling about settling the estate, on a Tuesday for no specific reason. At those moments, the funeral sites read transactional, the subreddits feel either welcoming or hostile depending on luck, and the mood-tag prompt asks "how are you feeling today?" as if grief were a state to log. Existing tools fail them by being too prescriptive ("step 4 of 7: write a letter to your loved one") or too generic.
-## Users
-Anyone weeks-to-months out from a meaningful loss — recent enough that grief is shaping the day, not so recent that they're still in funeral logistics. The losses vary: parent, partner, friend, pregnancy, pet, anticipatory loss with a terminal diagnosis. The support systems around them vary more — some surrounded by attentive friends, others whose network has gone quiet at six weeks.
-## Cost
-The cost of failure isn't dramatic — it's the slow drift away from a tool that doesn't meet them, and the continued absence of a place that does. What we want from this round: distinct strategic directions for what "a web app for grief" could meaningfully be — real bets that could move the category, not convergent variants.</t>
+**Situation.** We're scoping a web product for people in active grief. The space today splits roughly three ways: funeral logistics sites (transactional, mostly pre-funeral), peer support communities and subreddits (exposing or noisy for many), and journaling apps that bolt on a "feeling sad" mood tag (toothless). The users we keep hearing from describe wanting something different — something that respects them as someone grieving rather than treating them as a user to be moved through a funnel or a feed.
+**Complication.** People reach for a tool at the awkward moments: 3am, the anniversary, after a hard conversation with a sibling about settling the estate, on a Tuesday for no specific reason. At those moments, the funeral sites read transactional, the subreddits feel either welcoming or hostile depending on luck, and the mood-tag prompt asks "how are you feeling today?" as if grief were a state to log. Existing tools fail them by being too prescriptive ("step 4 of 7: write a letter to your loved one") or too generic.
+**Users.** Anyone weeks-to-months out from a meaningful loss — recent enough that grief is shaping the day, not so recent that they're still in funeral logistics. The losses vary: parent, partner, friend, pregnancy, pet, anticipatory loss with a terminal diagnosis. The support systems around them vary more — some surrounded by attentive friends, others whose network has gone quiet at six weeks.
+**Cost.** The cost of failure isn't dramatic — it's the slow drift away from a tool that doesn't meet them, and the continued absence of a place that does. What we want from this round: distinct strategic directions for what "a web app for grief" could meaningfully be — real bets that could move the category, not convergent variants.</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1058,14 +1022,10 @@
       <c r="B11" s="3" t="inlineStr">
         <is>
           <t># Discharge instructions for older adults going home — design exploration
-## Situation
-An older adult is being discharged from the hospital this afternoon after a heart-failure exacerbation, a stroke, a fall, or pneumonia. A family caregiver — often an adult child who has travelled in — will run the first week or two at home. The nurse has roughly fifteen minutes to walk through six pages of paperwork before the next admission needs the room.
-## Complication
-The patient is in pain, on medications that affect cognition, exhausted and emotionally activated; what they remember of those fifteen minutes once home is fragmentary. The caregiver who will administer the next thirty days is sometimes in the room and sometimes not. A few days later, the patient is trying to figure out which white pill is the new beta-blocker, what "weigh yourself daily and call if you gain more than three pounds in a week" means in practice, whether today's ankle swelling is a warning sign, and what the printed phone number is for after hours. The discharge papers are face-down on the kitchen table next to the medication bottles. The follow-up is in eleven days.
-## Users
-The dyad post-discharge: the older adult patient recovering at home, and the family caregiver — often an adult child — running the first week or two of medications, warning signs, and follow-up logistics. The discharging nurse and follow-up clinic are stakeholders the design accommodates; the design is for the dyad once paperwork has come home.
-## Cost
-Between now and the follow-up, it is the patient and the caregiver and the paperwork. The cost of getting it wrong is a missed warning sign, a doubled medication, a readmission. Scope is the discharge moment plus the first 7–14 days at home; the clinical care plan is out of scope.</t>
+**Situation.** An older adult is being discharged from the hospital this afternoon after a heart-failure exacerbation, a stroke, a fall, or pneumonia. A family caregiver — often an adult child who has travelled in — will run the first week or two at home. The nurse has roughly fifteen minutes to walk through six pages of paperwork before the next admission needs the room.
+**Complication.** The patient is in pain, on medications that affect cognition, exhausted and emotionally activated; what they remember of those fifteen minutes once home is fragmentary. The caregiver who will administer the next thirty days is sometimes in the room and sometimes not. A few days later, the patient is trying to figure out which white pill is the new beta-blocker, what "weigh yourself daily and call if you gain more than three pounds in a week" means in practice, whether today's ankle swelling is a warning sign, and what the printed phone number is for after hours. The discharge papers are face-down on the kitchen table next to the medication bottles. The follow-up is in eleven days.
+**Users.** The dyad post-discharge: the older adult patient recovering at home, and the family caregiver — often an adult child — running the first week or two of medications, warning signs, and follow-up logistics. The discharging nurse and follow-up clinic are stakeholders the design accommodates; the design is for the dyad once paperwork has come home.
+**Cost.** Between now and the follow-up, it is the patient and the caregiver and the paperwork. The cost of getting it wrong is a missed warning sign, a doubled medication, a readmission. Scope is the discharge moment plus the first 7–14 days at home; the clinical care plan is out of scope.</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1122,14 +1082,10 @@
       <c r="B12" s="3" t="inlineStr">
         <is>
           <t># Self-representation in housing court — design exploration
-## Situation
-A tenant has received an eviction notice. Their landlord has filed in housing court. They have a court date in two to three weeks. They cannot afford an attorney; the legal-aid clinic in their county is at capacity. The available self-help resources are accurate, thorough, and unusable in their situation: long PDFs of legalese for someone who is working two jobs and putting kids to bed at the same time.
-## Complication
-The tenant may or may not have a legal defense. The landlord may not have given proper notice; the rent claim may be wrong; the unit may be uninhabitable; the landlord may have engaged in unlawful self-help. Or the tenant may not have a defense and needs to negotiate time, settle, or simply file an answer to preserve options. They have a stack of papers in three different formats, a phone, and an internet connection. They cannot tell which of the eighty pieces of available advice apply to their facts and which don't.
-## Users
-A pro-se tenant facing an eviction filing with a court date two to three weeks out, navigating the case alone. Legal-aid attorneys, court clerks, and the landlord's counsel are stakeholders the tenant encounters; the design is for the tenant doing the work between notice and hearing.
-## Cost
-What they need is to walk into court understanding what is about to happen and what they should say. The cost of falling short is a default judgment, a lost home, and a record that follows them to the next lease application. The scope is from "I got a notice" through "I have prepared for court."</t>
+**Situation.** A tenant has received an eviction notice. Their landlord has filed in housing court. They have a court date in two to three weeks. They cannot afford an attorney; the legal-aid clinic in their county is at capacity. The available self-help resources are accurate, thorough, and unusable in their situation: long PDFs of legalese for someone who is working two jobs and putting kids to bed at the same time.
+**Complication.** The tenant may or may not have a legal defense. The landlord may not have given proper notice; the rent claim may be wrong; the unit may be uninhabitable; the landlord may have engaged in unlawful self-help. Or the tenant may not have a defense and needs to negotiate time, settle, or simply file an answer to preserve options. They have a stack of papers in three different formats, a phone, and an internet connection. They cannot tell which of the eighty pieces of available advice apply to their facts and which don't.
+**Users.** A pro-se tenant facing an eviction filing with a court date two to three weeks out, navigating the case alone. Legal-aid attorneys, court clerks, and the landlord's counsel are stakeholders the tenant encounters; the design is for the tenant doing the work between notice and hearing.
+**Cost.** What they need is to walk into court understanding what is about to happen and what they should say. The cost of falling short is a default judgment, a lost home, and a record that follows them to the next lease application. The scope is from "I got a notice" through "I have prepared for court."</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1184,14 +1140,10 @@
       <c r="B13" s="3" t="inlineStr">
         <is>
           <t># Multi-currency expense report submission — design exploration
-## Situation
-A traveler is home for two days between business trips. The trip that just ended ran through three countries, with receipts in five formats, photos of meals in a foreign language, an airline charge that hit their card in USD but was billed in EUR, a hotel charge pre-authorized at one amount and posted at another, an Uber auto-uploaded but mis-categorized as personal, and a cash tip paid because the card terminal was broken. They have policy questions — was the upgraded flight reimbursable, what counts as a client meal — and no one to ask quickly.
-## Complication
-They submit. Finance rejects it for a single category mismatch and asks them to redo. Each round of back-and-forth is another evening they don't have. The available expense tools present categorization screens, FX-rate prompts, and approval flows; the gap between what the traveler can produce on a Saturday afternoon and what finance needs to approve is where the loop lives.
-## Users
-The business traveler reconciling between trips — competent, time-starved, working from a kitchen table with a phone full of receipts. The finance reviewer reads what was submitted and often sends it back; they are a stakeholder, not the target.
-## Cost
-Evenings lost to resubmissions, the next trip approaching with last trip's report still open, reimbursements that lag for weeks, and the slow erosion of any sense that this part of the job is tractable. The traveler is leaving for São Paulo on Sunday. The scope is from the moment a trip ends to the moment the report is approved.</t>
+**Situation.** A traveler is home for two days between business trips. The trip that just ended ran through three countries, with receipts in five formats, photos of meals in a foreign language, an airline charge that hit their card in USD but was billed in EUR, a hotel charge pre-authorized at one amount and posted at another, an Uber auto-uploaded but mis-categorized as personal, and a cash tip paid because the card terminal was broken. They have policy questions — was the upgraded flight reimbursable, what counts as a client meal — and no one to ask quickly.
+**Complication.** They submit. Finance rejects it for a single category mismatch and asks them to redo. Each round of back-and-forth is another evening they don't have. The available expense tools present categorization screens, FX-rate prompts, and approval flows; the gap between what the traveler can produce on a Saturday afternoon and what finance needs to approve is where the loop lives.
+**Users.** The business traveler reconciling between trips — competent, time-starved, working from a kitchen table with a phone full of receipts. The finance reviewer reads what was submitted and often sends it back; they are a stakeholder, not the target.
+**Cost.** Evenings lost to resubmissions, the next trip approaching with last trip's report still open, reimbursements that lag for weeks, and the slow erosion of any sense that this part of the job is tractable. The traveler is leaving for São Paulo on Sunday. The scope is from the moment a trip ends to the moment the report is approved.</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1247,14 +1199,10 @@
       <c r="B14" s="3" t="inlineStr">
         <is>
           <t># A parent finding tutoring for a child struggling in math — design exploration
-## Situation
-A child in 4th, 6th, or 8th grade is struggling in math. The grades have slipped; the teacher has sent a note; the standardized test result came back lower than expected. The parent has a few hours over the next two weeks to set something up, working evenings around their own job and the rest of the family's calendar.
-## Complication
-The parent is facing a tangle of options the landscape currently presents: the local tutoring chain (predictable but expensive, small-group, weekly); a private tutor matched through a friend (variable quality and availability); online tutoring marketplaces and free practice platforms; the school's own intervention program if the kid qualifies; AI-tutor apps that promise personalization. The parent cannot easily tell which option is matched to what works versus what's marketing. They are not the math expert.
-## Users
-A parent–child dyad at the moment of choosing help. The parent is the procurer and decider — scheduling, paying, reading reviews, judging fit. The child is the recipient and the one whose engagement determines whether any of this works; they are sensitive to the framing, since *you need a tutor* can feel like a judgment, and a kid who closes off doesn't learn from anyone. Tutor candidates and school staff are stakeholders the design accommodates, not the target.
-## Cost
-Weeks pass while the parent stalls between bad options; the child falls further behind in a subject that compounds; the wrong choice burns money and the child's willingness to try again. The scope is from "we need help" through "we have a plan and a tutor we trust."</t>
+**Situation.** A child in 4th, 6th, or 8th grade is struggling in math. The grades have slipped; the teacher has sent a note; the standardized test result came back lower than expected. The parent has a few hours over the next two weeks to set something up, working evenings around their own job and the rest of the family's calendar.
+**Complication.** The parent is facing a tangle of options the landscape currently presents: the local tutoring chain (predictable but expensive, small-group, weekly); a private tutor matched through a friend (variable quality and availability); online tutoring marketplaces and free practice platforms; the school's own intervention program if the kid qualifies; AI-tutor apps that promise personalization. The parent cannot easily tell which option is matched to what works versus what's marketing. They are not the math expert.
+**Users.** A parent–child dyad at the moment of choosing help. The parent is the procurer and decider — scheduling, paying, reading reviews, judging fit. The child is the recipient and the one whose engagement determines whether any of this works; they are sensitive to the framing, since *you need a tutor* can feel like a judgment, and a kid who closes off doesn't learn from anyone. Tutor candidates and school staff are stakeholders the design accommodates, not the target.
+**Cost.** Weeks pass while the parent stalls between bad options; the child falls further behind in a subject that compounds; the wrong choice burns money and the child's willingness to try again. The scope is from "we need help" through "we have a plan and a tutor we trust."</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1309,14 +1257,10 @@
       <c r="B15" s="3" t="inlineStr">
         <is>
           <t># Pre-travel prescription preparation — design exploration
-## Situation
-A person is preparing for a long international trip. They take regular prescription medication — an SSRI, an ADHD stimulant, a blood thinner, hormone therapy, a controlled-substance painkiller. They are two weeks out and just realized this is harder than they thought. US prescriptions can't be filled at overseas pharmacies. Several common US medications are restricted or illegal in the country they're going to.
-## Complication
-To carry enough for the trip, they need a vacation override from their insurance, weeks in advance, and probably a prescriber letter. None of that is one phone call. They are working it out across pharmacy phone trees, the insurer's app, the State Department's site, and Reddit threads. Their PCP's office is not set up to answer travel-medication questions. The pharmacy can fill the script if the doctor authorizes the override; the doctor will authorize the override if asked correctly. Nobody owns the work of getting this person across the world with their medication intact, legal, and packaged the way customs expects.
-## Users
-An international traveler on regular, often controlled, prescription medication — a person managing real conditions who needs to keep managing them on the other side of a border. Prescriber, pharmacist, insurer, and customs are stakeholders this work moves through, not the target.
-## Cost
-Consequences run from confiscation at customs to denial of entry to arrest in stricter jurisdictions, plus the quieter failure of running out of medication mid-trip and the destabilization that follows. The scope is the four-week window before international departure.</t>
+**Situation.** A person is preparing for a long international trip. They take regular prescription medication — an SSRI, an ADHD stimulant, a blood thinner, hormone therapy, a controlled-substance painkiller. They are two weeks out and just realized this is harder than they thought. US prescriptions can't be filled at overseas pharmacies. Several common US medications are restricted or illegal in the country they're going to.
+**Complication.** To carry enough for the trip, they need a vacation override from their insurance, weeks in advance, and probably a prescriber letter. None of that is one phone call. They are working it out across pharmacy phone trees, the insurer's app, the State Department's site, and Reddit threads. Their PCP's office is not set up to answer travel-medication questions. The pharmacy can fill the script if the doctor authorizes the override; the doctor will authorize the override if asked correctly. Nobody owns the work of getting this person across the world with their medication intact, legal, and packaged the way customs expects.
+**Users.** An international traveler on regular, often controlled, prescription medication — a person managing real conditions who needs to keep managing them on the other side of a border. Prescriber, pharmacist, insurer, and customs are stakeholders this work moves through, not the target.
+**Cost.** Consequences run from confiscation at customs to denial of entry to arrest in stricter jurisdictions, plus the quieter failure of running out of medication mid-trip and the destabilization that follows. The scope is the four-week window before international departure.</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1356,14 +1300,10 @@
       <c r="B16" s="3" t="inlineStr">
         <is>
           <t># Finding a primary care doctor after relocating — design exploration
-## Situation
-A person has moved to a new city and needs a primary care doctor. They have insurance, and their plan's website hands them an in-network directory — several hundred names, sorted by ZIP code. The directory shows specialties and addresses. It rarely shows which practices are accepting new patients, what the next available appointment actually is, which clinicians speak the languages spoken in the patient's household, whether the office is wheelchair-accessible, or how the practice handles diabetes care, mental-health needs, or pregnancy.
-## Complication
-The patient calls one office, sits on hold for ten minutes, navigates a phone tree, and is told the next opening is in five months — or that the practice isn't accepting new patients at all. Then the next call. Then the next. The options they are choosing between in the landscape today include the in-network directory itself, telehealth services their plan covers, federally-qualified health centers in the area, and direct primary care practices that bill outside insurance — none of which the directory surfaces side-by-side.
-## Users
-A patient looking for a primary care doctor in a new city. Some have active conditions — chronic pain, diabetes, anxiety — and need to start care now; others are establishing routine care and re-engage only when something goes wrong. The insurance plan, the in-network directory, the practices, and telehealth providers are stakeholder context the design accommodates, not the target.
-## Cost
-Delayed care for people who need it now; undiagnosed conditions for those who give up early; emergency visits for what should have been clinic visits. The scope is from "I need a new doctor" through "I have an appointment booked."</t>
+**Situation.** A person has moved to a new city and needs a primary care doctor. They have insurance, and their plan's website hands them an in-network directory — several hundred names, sorted by ZIP code. The directory shows specialties and addresses. It rarely shows which practices are accepting new patients, what the next available appointment actually is, which clinicians speak the languages spoken in the patient's household, whether the office is wheelchair-accessible, or how the practice handles diabetes care, mental-health needs, or pregnancy.
+**Complication.** The patient calls one office, sits on hold for ten minutes, navigates a phone tree, and is told the next opening is in five months — or that the practice isn't accepting new patients at all. Then the next call. Then the next. The options they are choosing between in the landscape today include the in-network directory itself, telehealth services their plan covers, federally-qualified health centers in the area, and direct primary care practices that bill outside insurance — none of which the directory surfaces side-by-side.
+**Users.** A patient looking for a primary care doctor in a new city. Some have active conditions — chronic pain, diabetes, anxiety — and need to start care now; others are establishing routine care and re-engage only when something goes wrong. The insurance plan, the in-network directory, the practices, and telehealth providers are stakeholder context the design accommodates, not the target.
+**Cost.** Delayed care for people who need it now; undiagnosed conditions for those who give up early; emergency visits for what should have been clinic visits. The scope is from "I need a new doctor" through "I have an appointment booked."</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1404,14 +1344,10 @@
       <c r="B17" s="3" t="inlineStr">
         <is>
           <t># Remote new-hire onboarding, week one — design exploration
-## Situation
-A competent professional joins a remote-first company on Monday. They have never met their team in person. They've done this before — they know how to set up a laptop and learn a new codebase. The HR-built first week is nine meetings Monday, six Tuesday; a stack of documentation; a Notion they still can't fully access; benefits links, security trainings, and a Slack workspace with a hundred channels.
-## Complication
-What's hard isn't the work; it's everything around it. They don't know this team's norms, this manager's actual (not stated) preferences, who is the person you actually ask about benefits. Remote replaces the watercooler, the lunch tag-along, and the overheard standup with calendar invites — which aren't the same thing. By Wednesday the orientation rush slows; by Thursday they're alone with documentation and unsure who to ask what, anxious about asking questions that would mark them as not-yet-onboard.
-## Users
-The new hire — a competent professional starting cold inside a remote-first company, navigating their first five working days from a home desk. The hiring manager, peers on the team, HR, and IT provisioning are stakeholders whose work shapes the week but who are not the target of the design.
-## Cost
-The five-day window from joining to belonging is where the relationship is made or lost; new hires who don't feel onboard by Friday carry that uncertainty into the next month, hesitate to ask, and quietly disengage. Companies bleed early-tenure hires at exactly this point. The scope is the first five working days, Monday morning to Friday afternoon.</t>
+**Situation.** A competent professional joins a remote-first company on Monday. They have never met their team in person. They've done this before — they know how to set up a laptop and learn a new codebase. The HR-built first week is nine meetings Monday, six Tuesday; a stack of documentation; a Notion they still can't fully access; benefits links, security trainings, and a Slack workspace with a hundred channels.
+**Complication.** What's hard isn't the work; it's everything around it. They don't know this team's norms, this manager's actual (not stated) preferences, who is the person you actually ask about benefits. Remote replaces the watercooler, the lunch tag-along, and the overheard standup with calendar invites — which aren't the same thing. By Wednesday the orientation rush slows; by Thursday they're alone with documentation and unsure who to ask what, anxious about asking questions that would mark them as not-yet-onboard.
+**Users.** The new hire — a competent professional starting cold inside a remote-first company, navigating their first five working days from a home desk. The hiring manager, peers on the team, HR, and IT provisioning are stakeholders whose work shapes the week but who are not the target of the design.
+**Cost.** The five-day window from joining to belonging is where the relationship is made or lost; new hires who don't feel onboard by Friday carry that uncertainty into the next month, hesitate to ask, and quietly disengage. Companies bleed early-tenure hires at exactly this point. The scope is the first five working days, Monday morning to Friday afternoon.</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1466,14 +1402,10 @@
       <c r="B18" s="3" t="inlineStr">
         <is>
           <t># A sprint retro after a missed target — design exploration
-## Situation
-A product team has just finished a two-week sprint and missed what they committed to. The scrum master has forty-five minutes booked on Friday afternoon for the retrospective. The team is tired, the engineer who carried the cancelled feature is quiet on the call, the PM is reading their phone, and the VP of Engineering is on the line listening in. The scrum master has a Miro board with three columns and a stack of sticky notes their team has used in some version for the last two years.
-## Complication
-The team's existing tools — Miro templates, FunRetro, EasyRetro, the Jira retro module — capture sticky notes and let people upvote them. What happens between "sticky notes captured" and "the team had a real conversation" sits outside those tools. The team itself is uneven: some members will say what they think directly, some won't say anything that could read as criticism with the PM in the room, and some will narrate the sprint as if it went fine.
-## Users
-The scrum master is the target user — the one prepping the meeting, holding the room, and chasing follow-through. The team is the design's audience; the PM in the room and the VP listening in are stakeholders the meeting accommodates.
-## Cost
-A retro that doesn't land after a missed sprint compounds: the same patterns carry into the next sprint, action items are forgotten by Monday, and the team grows a little more cynical about whether retros are worth showing up to. A retro that does land is something the team can feel for weeks. The scope is the retrospective meeting itself, the prep before it, and the follow-through.</t>
+**Situation.** A product team has just finished a two-week sprint and missed what they committed to. The scrum master has forty-five minutes booked on Friday afternoon for the retrospective. The team is tired, the engineer who carried the cancelled feature is quiet on the call, the PM is reading their phone, and the VP of Engineering is on the line listening in. The scrum master has a Miro board with three columns and a stack of sticky notes their team has used in some version for the last two years.
+**Complication.** The team's existing tools — Miro templates, FunRetro, EasyRetro, the Jira retro module — capture sticky notes and let people upvote them. What happens between "sticky notes captured" and "the team had a real conversation" sits outside those tools. The team itself is uneven: some members will say what they think directly, some won't say anything that could read as criticism with the PM in the room, and some will narrate the sprint as if it went fine.
+**Users.** The scrum master is the target user — the one prepping the meeting, holding the room, and chasing follow-through. The team is the design's audience; the PM in the room and the VP listening in are stakeholders the meeting accommodates.
+**Cost.** A retro that doesn't land after a missed sprint compounds: the same patterns carry into the next sprint, action items are forgotten by Monday, and the team grows a little more cynical about whether retros are worth showing up to. A retro that does land is something the team can feel for weeks. The scope is the retrospective meeting itself, the prep before it, and the follow-through.</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1514,14 +1446,10 @@
       <c r="B19" s="3" t="inlineStr">
         <is>
           <t># Applying for food assistance — design exploration
-## Situation
-Someone who needs food assistance now is sitting down to apply for SNAP. They've lost a job, had hours cut, gotten sick, or are raising a kid on inconsistent income. They are working from a phone, sometimes a shared one, often on intermittent data.
-## Complication
-The form in front of them asks branching questions whose answers depend on context the form does not let them explain, requires documents they can't easily produce in the moment (a recent pay stub from a gig that pays inconsistently, a lease they don't have a copy of, a Social Security card from a drawer at a place they no longer live), and was built to be filled out on a desktop computer they don't own. After they submit, the experience goes quiet. They don't know if the application was received, is being processed, is waiting on a document the system has not asked for, or has already been denied.
-## Users
-The target user is the applicant: a first-time applicant who has never used the safety net, a mixed-status family weighing whether the application itself will be used against them, or someone returning under worse circumstances than the first time. State eligibility workers who process and adjudicate these applications are stakeholders, not the target.
-## Cost
-Days pass. The food situation that brought them here doesn't pause. Many people in this position get one attempt before they stop trying — not from a single rejection, but from the cumulative weight of submitting into silence while the rest of their life keeps moving. What we want: distinct strategic directions for what a humane food-assistance application could be when designed around the applicant.</t>
+**Situation.** Someone who needs food assistance now is sitting down to apply for SNAP. They've lost a job, had hours cut, gotten sick, or are raising a kid on inconsistent income. They are working from a phone, sometimes a shared one, often on intermittent data.
+**Complication.** The form in front of them asks branching questions whose answers depend on context the form does not let them explain, requires documents they can't easily produce in the moment (a recent pay stub from a gig that pays inconsistently, a lease they don't have a copy of, a Social Security card from a drawer at a place they no longer live), and was built to be filled out on a desktop computer they don't own. After they submit, the experience goes quiet. They don't know if the application was received, is being processed, is waiting on a document the system has not asked for, or has already been denied.
+**Users.** The target user is the applicant: a first-time applicant who has never used the safety net, a mixed-status family weighing whether the application itself will be used against them, or someone returning under worse circumstances than the first time. State eligibility workers who process and adjudicate these applications are stakeholders, not the target.
+**Cost.** Days pass. The food situation that brought them here doesn't pause. Many people in this position get one attempt before they stop trying — not from a single rejection, but from the cumulative weight of submitting into silence while the rest of their life keeps moving. What we want: distinct strategic directions for what a humane food-assistance application could be when designed around the applicant.</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1576,14 +1504,10 @@
       <c r="B20" s="3" t="inlineStr">
         <is>
           <t># The first 90 days after a Type 2 diabetes diagnosis — design exploration
-## Situation
-A person has just been told they have Type 2 diabetes. The diagnosis arrived in a fifteen-minute appointment with a handout, a prescription for metformin, and instructions to "watch your sugars" and to "see a nutritionist." They walk out scared, ashamed, confused about whether they caused this, and facing a slate of changes — diet, exercise, medication, glucose monitoring, A1c labs every three months.
-## Complication
-No one helps them sequence those changes. The nutritionist referral is a phone number on the printout. The diabetes self-management education and support sessions their insurance covers are not mentioned at the appointment. The landscape they encounter when they look for help — glucose-logging utilities, coaching platforms (Livongo, Virta, Omada), peer-support communities, and YouTube videos from creators of varying authority — tends to ask them to log their glucose on day one. None of it is shaped around the moment of diagnosis itself: the week they are still telling family, the week they are deciding whether to tell work.
-## Users
-The target user is the newly-diagnosed patient in the first 90 days. The clinician and the nutritionist are stakeholders the design accommodates — referrals come from them, labs route through them — but are not who the design is for.
-## Cost
-By the end of the next ninety days they will have either built a workable rhythm — meals, walking, the morning metformin, the glucose meter sitting on the kitchen counter — or they will have drifted: meter in a drawer, prescription unfilled at refill time, weight unchanged, and no further appointment booked until the next labs flag something. The scope is from diagnosis through the 90-day mark.</t>
+**Situation.** A person has just been told they have Type 2 diabetes. The diagnosis arrived in a fifteen-minute appointment with a handout, a prescription for metformin, and instructions to "watch your sugars" and to "see a nutritionist." They walk out scared, ashamed, confused about whether they caused this, and facing a slate of changes — diet, exercise, medication, glucose monitoring, A1c labs every three months.
+**Complication.** No one helps them sequence those changes. The nutritionist referral is a phone number on the printout. The diabetes self-management education and support sessions their insurance covers are not mentioned at the appointment. The landscape they encounter when they look for help — glucose-logging utilities, coaching platforms (Livongo, Virta, Omada), peer-support communities, and YouTube videos from creators of varying authority — tends to ask them to log their glucose on day one. None of it is shaped around the moment of diagnosis itself: the week they are still telling family, the week they are deciding whether to tell work.
+**Users.** The target user is the newly-diagnosed patient in the first 90 days. The clinician and the nutritionist are stakeholders the design accommodates — referrals come from them, labs route through them — but are not who the design is for.
+**Cost.** By the end of the next ninety days they will have either built a workable rhythm — meals, walking, the morning metformin, the glucose meter sitting on the kitchen counter — or they will have drifted: meter in a drawer, prescription unfilled at refill time, weight unchanged, and no further appointment booked until the next labs flag something. The scope is from diagnosis through the 90-day mark.</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1623,14 +1547,10 @@
       <c r="B21" s="3" t="inlineStr">
         <is>
           <t># Filing for unemployment insurance — design exploration
-## Situation
-A person has just lost their job and is filing for unemployment insurance through their state's labor agency. They may have a few weeks of rent in the bank or none. They are filling out the application on a phone — in line at a job center, between caregiving shifts, or late at night after the kids are asleep.
-## Complication
-The application asks for an EDDCAN number they have never heard of, pay stubs from the last eighteen months they may not have saved, and the precise dates and hours of every job worked in a base period that doesn't match how variable-schedule work happens. The legalese is dense. A wrong answer on any of dozens of questions delays or denies the claim, and the appeal that follows takes weeks. Once filed, the channels for finding out what's happening are a state portal that often shows information weeks out of date, paper letters that arrive after the next pay period would have been due, and a phone line that holds for hours. The portal sometimes says the claim is being processed; sometimes nothing at all.
-## Users
-The target user is the claimant — filing and waiting on benefits they are entitled to under state and federal law. State eligibility workers and adjudicators are stakeholders, not the target.
-## Cost
-Money does not arrive on a schedule the person can plan around. Rent is due, the car insurance lapses, the kid needs school supplies. The gap between filing and the first payment landing is where the urgency of the situation collides with what the system communicates. The scope is the filing flow plus the first thirty days of claim-status communication.</t>
+**Situation.** A person has just lost their job and is filing for unemployment insurance through their state's labor agency. They may have a few weeks of rent in the bank or none. They are filling out the application on a phone — in line at a job center, between caregiving shifts, or late at night after the kids are asleep.
+**Complication.** The application asks for an EDDCAN number they have never heard of, pay stubs from the last eighteen months they may not have saved, and the precise dates and hours of every job worked in a base period that doesn't match how variable-schedule work happens. The legalese is dense. A wrong answer on any of dozens of questions delays or denies the claim, and the appeal that follows takes weeks. Once filed, the channels for finding out what's happening are a state portal that often shows information weeks out of date, paper letters that arrive after the next pay period would have been due, and a phone line that holds for hours. The portal sometimes says the claim is being processed; sometimes nothing at all.
+**Users.** The target user is the claimant — filing and waiting on benefits they are entitled to under state and federal law. State eligibility workers and adjudicators are stakeholders, not the target.
+**Cost.** Money does not arrive on a schedule the person can plan around. Rent is due, the car insurance lapses, the kid needs school supplies. The gap between filing and the first payment landing is where the urgency of the situation collides with what the system communicates. The scope is the filing flow plus the first thirty days of claim-status communication.</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1670,14 +1590,10 @@
       <c r="B22" s="3" t="inlineStr">
         <is>
           <t># Updating voter registration after a name change — design exploration
-## Situation
-A person has changed their legal name — after marriage, divorce, gender transition, leaving an abusive relationship, or by personal choice. Their old name is on the voter roll. The next election is months away. Someone told them they should update their registration; they don't know whether they need to, by when, what proof, or how their state's rules differ from a friend's in another state.
-## Complication
-The state election-board website is a tangle of pages and PDFs that don't quite match their situation. Voter registration sits inside a long list of bureaucratic to-dos the name change has triggered — driver's license, Social Security card, employer records, banking, passports — and is the one most likely to be skipped until election day.
-## Users
-The target user is the voter mid-name-change: a trans person whose ID is finally catching up to their name, a domestic-violence survivor who changed their name for safety, a recently-married or recently-divorced voter, or someone who chose a new name. Each comes with different proof, different timelines, and different concerns about who sees the old name during the update. Election-board staff and poll workers are stakeholders, not the target.
-## Cost
-On election day, the name fails the poll-book check and they're asked to cast a provisional ballot they may not return to cure. A vote they were entitled to cast doesn't count, and being challenged at the table — especially for trans voters or survivors whose old name is read aloud — can make them less likely to return. The scope is updating registration plus the ambiguity around it — *do I need to, when by, what proof, will this be wrong on election day.*</t>
+**Situation.** A person has changed their legal name — after marriage, divorce, gender transition, leaving an abusive relationship, or by personal choice. Their old name is on the voter roll. The next election is months away. Someone told them they should update their registration; they don't know whether they need to, by when, what proof, or how their state's rules differ from a friend's in another state.
+**Complication.** The state election-board website is a tangle of pages and PDFs that don't quite match their situation. Voter registration sits inside a long list of bureaucratic to-dos the name change has triggered — driver's license, Social Security card, employer records, banking, passports — and is the one most likely to be skipped until election day.
+**Users.** The target user is the voter mid-name-change: a trans person whose ID is finally catching up to their name, a domestic-violence survivor who changed their name for safety, a recently-married or recently-divorced voter, or someone who chose a new name. Each comes with different proof, different timelines, and different concerns about who sees the old name during the update. Election-board staff and poll workers are stakeholders, not the target.
+**Cost.** On election day, the name fails the poll-book check and they're asked to cast a provisional ballot they may not return to cure. A vote they were entitled to cast doesn't count, and being challenged at the table — especially for trans voters or survivors whose old name is read aloud — can make them less likely to return. The scope is updating registration plus the ambiguity around it — *do I need to, when by, what proof, will this be wrong on election day.*</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
